--- a/data/imports/personal-assets.xlsx
+++ b/data/imports/personal-assets.xlsx
@@ -15,39 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="96">
-  <si>
-    <t>币种</t>
-  </si>
-  <si>
-    <t>股票名</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="98">
   <si>
     <t>年份</t>
   </si>
   <si>
-    <t>对人民币汇率</t>
-  </si>
-  <si>
-    <t>美元 (USD)</t>
-  </si>
-  <si>
-    <t>股数</t>
-  </si>
-  <si>
-    <t>每股分红</t>
-  </si>
-  <si>
     <t>总和</t>
-  </si>
-  <si>
-    <t>港币 (HKD)</t>
-  </si>
-  <si>
-    <t>招商银行</t>
-  </si>
-  <si>
-    <t>https://script.google.com/macros/s/AKfycbz2hNKJr6FuC-yhKilPyIgOmavrKYhcZkhnVJhXgCn-YlpCgVDe_igUmpnFOyFqwnk/exec</t>
   </si>
   <si>
     <t>工资</t>
@@ -65,10 +38,16 @@
     <t>股票总额</t>
   </si>
   <si>
+    <t>币种</t>
+  </si>
+  <si>
     <t>股票A股</t>
   </si>
   <si>
     <t>历史B股(人民币)</t>
+  </si>
+  <si>
+    <t>股票名</t>
   </si>
   <si>
     <t>B股(美元)</t>
@@ -86,10 +65,16 @@
     <t>基金 + 支付宝</t>
   </si>
   <si>
+    <t>对人民币汇率</t>
+  </si>
+  <si>
     <t>数字货币</t>
   </si>
   <si>
     <t>公积金</t>
+  </si>
+  <si>
+    <t>美元 (USD)</t>
   </si>
   <si>
     <t>A本月涨幅</t>
@@ -104,16 +89,31 @@
     <t>备注</t>
   </si>
   <si>
+    <t>股数</t>
+  </si>
+  <si>
     <t>总资产增量</t>
   </si>
   <si>
-    <t>苏泊尔</t>
+    <t>港币 (HKD)</t>
+  </si>
+  <si>
+    <t>每股分红</t>
+  </si>
+  <si>
+    <t>https://script.google.com/macros/s/AKfycbz2hNKJr6FuC-yhKilPyIgOmavrKYhcZkhnVJhXgCn-YlpCgVDe_igUmpnFOyFqwnk/exec</t>
+  </si>
+  <si>
+    <t>招商银行</t>
   </si>
   <si>
     <t>总资产涨幅</t>
   </si>
   <si>
     <t>2022/9</t>
+  </si>
+  <si>
+    <t>苏泊尔</t>
   </si>
   <si>
     <t>五粮液</t>
@@ -304,6 +304,12 @@
   <si>
     <t>2026/7.8</t>
   </si>
+  <si>
+    <t>4w A 股</t>
+  </si>
+  <si>
+    <t>转入3w到A股</t>
+  </si>
 </sst>
 </file>
 
@@ -320,13 +326,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -499,33 +505,33 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -548,37 +554,37 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -815,76 +821,76 @@
   </cols>
   <sheetData>
     <row r="1" ht="27.0" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="M1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="N1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="O1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="P1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="S1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="T1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q1" s="5" t="s">
+      <c r="U1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="U1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="A2" s="8" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>32</v>
       </c>
       <c r="B2" s="18">
         <f t="array" ref="B2:B1000">IF((D2:D1000&lt;&gt;"")+(E2:E1000&lt;&gt;"")+(F2:F1000&lt;&gt;"")+(G2:G1000&lt;&gt;"")+(M2:M1000&lt;&gt;"")+(N2:N1000&lt;&gt;"")+(O2:O1000&lt;&gt;"")+(P2:P1000&lt;&gt;"")+(S2:S1000&lt;&gt;"")=0,,IF(ISNUMBER(D2:D1000),D2:D1000,0)+IF(ISNUMBER(E2:E1000),E2:E1000,0)+IF(ISNUMBER(F2:F1000),F2:F1000,0)+IF(ISNUMBER(G2:G1000),G2:G1000,0)+IF(ISNUMBER(M2:M1000),M2:M1000,0)+IF(ISNUMBER(N2:N1000),N2:N1000,0)+IF(ISNUMBER(O2:O1000),O2:O1000,0)+IF(ISNUMBER(P2:P1000),P2:P1000,0)+IF(ISNUMBER(S2:S1000),S2:S1000,0))</f>
@@ -940,7 +946,7 @@
       <c r="V2" s="20"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="18">
@@ -1000,7 +1006,7 @@
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>46</v>
       </c>
       <c r="B4" s="18">
@@ -1058,7 +1064,7 @@
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B5" s="18">
@@ -1114,7 +1120,7 @@
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B6" s="18">
@@ -1170,7 +1176,7 @@
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="18">
@@ -1228,7 +1234,7 @@
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="8" t="s">
         <v>50</v>
       </c>
       <c r="B8" s="18">
@@ -1286,7 +1292,7 @@
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B9" s="18">
@@ -1344,7 +1350,7 @@
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B10" s="18">
@@ -1402,7 +1408,7 @@
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B11" s="18">
@@ -1460,7 +1466,7 @@
       </c>
     </row>
     <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>54</v>
       </c>
       <c r="B12" s="18">
@@ -1518,7 +1524,7 @@
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="18">
@@ -1576,7 +1582,7 @@
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B14" s="18">
@@ -1634,7 +1640,7 @@
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B15" s="18">
@@ -1692,7 +1698,7 @@
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
         <v>58</v>
       </c>
       <c r="B16" s="18">
@@ -1750,7 +1756,7 @@
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B17" s="18">
@@ -1808,7 +1814,7 @@
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="8" t="s">
         <v>60</v>
       </c>
       <c r="B18" s="18">
@@ -1866,7 +1872,7 @@
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="8" t="s">
         <v>61</v>
       </c>
       <c r="B19" s="18">
@@ -1924,7 +1930,7 @@
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="8" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="18">
@@ -1980,7 +1986,7 @@
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="8" t="s">
         <v>62</v>
       </c>
       <c r="B21" s="18">
@@ -2038,7 +2044,7 @@
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="8" t="s">
         <v>63</v>
       </c>
       <c r="B22" s="18">
@@ -2094,7 +2100,7 @@
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="8" t="s">
         <v>64</v>
       </c>
       <c r="B23" s="18">
@@ -2150,7 +2156,7 @@
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B24" s="18">
@@ -2208,7 +2214,7 @@
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="8" t="s">
         <v>66</v>
       </c>
       <c r="B25" s="18">
@@ -2266,7 +2272,7 @@
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="8" t="s">
         <v>67</v>
       </c>
       <c r="B26" s="18">
@@ -2324,7 +2330,7 @@
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="8" t="s">
         <v>68</v>
       </c>
       <c r="B27" s="18">
@@ -2384,7 +2390,7 @@
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="8" t="s">
         <v>69</v>
       </c>
       <c r="B28" s="18">
@@ -2442,7 +2448,7 @@
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="8" t="s">
         <v>70</v>
       </c>
       <c r="B29" s="18">
@@ -2500,7 +2506,7 @@
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="8" t="s">
         <v>70</v>
       </c>
       <c r="B30" s="18">
@@ -2556,7 +2562,7 @@
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="8" t="s">
         <v>70</v>
       </c>
       <c r="B31" s="18">
@@ -2612,7 +2618,7 @@
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="8" t="s">
         <v>71</v>
       </c>
       <c r="B32" s="18">
@@ -2674,7 +2680,7 @@
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="8" t="s">
         <v>72</v>
       </c>
       <c r="B33" s="18">
@@ -2736,7 +2742,7 @@
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="8" t="s">
         <v>73</v>
       </c>
       <c r="B34" s="18">
@@ -2796,7 +2802,7 @@
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="8" t="s">
         <v>74</v>
       </c>
       <c r="B35" s="18">
@@ -2858,7 +2864,7 @@
       </c>
     </row>
     <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="8" t="s">
         <v>75</v>
       </c>
       <c r="B36" s="18">
@@ -2920,7 +2926,7 @@
       </c>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="8" t="s">
         <v>76</v>
       </c>
       <c r="B37" s="18">
@@ -2982,7 +2988,7 @@
       </c>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="8" t="s">
         <v>77</v>
       </c>
       <c r="B38" s="18">
@@ -3044,7 +3050,7 @@
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="8" t="s">
         <v>78</v>
       </c>
       <c r="B39" s="18">
@@ -3104,7 +3110,7 @@
       </c>
     </row>
     <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="8" t="s">
         <v>79</v>
       </c>
       <c r="B40" s="18">
@@ -3160,7 +3166,7 @@
       </c>
     </row>
     <row r="41" ht="19.5" customHeight="1">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="8" t="s">
         <v>80</v>
       </c>
       <c r="B41" s="18">
@@ -3220,7 +3226,7 @@
       </c>
     </row>
     <row r="42" ht="19.5" customHeight="1">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="8" t="s">
         <v>81</v>
       </c>
       <c r="B42" s="18">
@@ -3276,7 +3282,7 @@
       </c>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="8" t="s">
         <v>82</v>
       </c>
       <c r="B43" s="18">
@@ -3336,7 +3342,7 @@
       </c>
     </row>
     <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="8" t="s">
         <v>83</v>
       </c>
       <c r="B44" s="18">
@@ -3396,7 +3402,7 @@
       </c>
     </row>
     <row r="45" ht="19.5" customHeight="1">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="8" t="s">
         <v>84</v>
       </c>
       <c r="B45" s="18">
@@ -3456,7 +3462,7 @@
       </c>
     </row>
     <row r="46" ht="19.5" customHeight="1">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="8" t="s">
         <v>85</v>
       </c>
       <c r="B46" s="18">
@@ -3516,7 +3522,7 @@
       </c>
     </row>
     <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="8" t="s">
         <v>86</v>
       </c>
       <c r="B47" s="18">
@@ -3572,7 +3578,7 @@
       </c>
     </row>
     <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="8" t="s">
         <v>87</v>
       </c>
       <c r="B48" s="18">
@@ -3632,7 +3638,7 @@
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="8" t="s">
         <v>88</v>
       </c>
       <c r="B49" s="18">
@@ -4217,7 +4223,9 @@
       <c r="S58" s="21">
         <v>130000.0</v>
       </c>
-      <c r="T58" s="19"/>
+      <c r="T58" s="24" t="s">
+        <v>96</v>
+      </c>
       <c r="U58" s="18">
         <v>55541.78000000003</v>
       </c>
@@ -4226,31 +4234,67 @@
       </c>
     </row>
     <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="10"/>
-      <c r="B59" s="18"/>
+      <c r="A59" s="23">
+        <v>46266.0</v>
+      </c>
+      <c r="B59" s="18">
+        <v>1532314.9300000002</v>
+      </c>
       <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
+      <c r="D59" s="21">
+        <v>4323.0</v>
+      </c>
+      <c r="E59" s="21">
+        <v>2136.0</v>
+      </c>
+      <c r="F59" s="21">
+        <v>19124.0</v>
+      </c>
+      <c r="G59" s="21">
+        <v>1018246.15</v>
+      </c>
+      <c r="H59" s="21">
+        <v>573944.0</v>
+      </c>
       <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
-      <c r="M59" s="18"/>
-      <c r="N59" s="18"/>
-      <c r="O59" s="18"/>
-      <c r="P59" s="18"/>
+      <c r="J59" s="21">
+        <v>41919.0</v>
+      </c>
+      <c r="K59" s="21">
+        <v>187615.0</v>
+      </c>
+      <c r="L59" s="18">
+        <v>444302.15</v>
+      </c>
+      <c r="M59" s="21">
+        <v>1.78</v>
+      </c>
+      <c r="N59" s="21">
+        <v>1394.0</v>
+      </c>
+      <c r="O59" s="21">
+        <v>35000.0</v>
+      </c>
+      <c r="P59" s="21">
+        <v>322090.0</v>
+      </c>
       <c r="Q59" s="18"/>
       <c r="R59" s="18"/>
-      <c r="S59" s="18"/>
-      <c r="T59" s="19"/>
-      <c r="U59" s="18"/>
-      <c r="V59" s="20"/>
+      <c r="S59" s="21">
+        <v>130000.0</v>
+      </c>
+      <c r="T59" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="U59" s="18">
+        <v>-31039.299999999814</v>
+      </c>
+      <c r="V59" s="20">
+        <v>-0.0198542975125988</v>
+      </c>
     </row>
     <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="10"/>
+      <c r="A60" s="8"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
@@ -4274,7 +4318,7 @@
       <c r="V60" s="20"/>
     </row>
     <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="10"/>
+      <c r="A61" s="8"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
       <c r="D61" s="18"/>
@@ -4298,7 +4342,7 @@
       <c r="V61" s="20"/>
     </row>
     <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="10"/>
+      <c r="A62" s="8"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
       <c r="D62" s="18"/>
@@ -4322,7 +4366,7 @@
       <c r="V62" s="20"/>
     </row>
     <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="10"/>
+      <c r="A63" s="8"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
       <c r="D63" s="18"/>
@@ -4346,7 +4390,7 @@
       <c r="V63" s="20"/>
     </row>
     <row r="64" ht="19.5" customHeight="1">
-      <c r="A64" s="10"/>
+      <c r="A64" s="8"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
       <c r="D64" s="18"/>
@@ -4370,7 +4414,7 @@
       <c r="V64" s="20"/>
     </row>
     <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="10"/>
+      <c r="A65" s="8"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
       <c r="D65" s="18"/>
@@ -4394,7 +4438,7 @@
       <c r="V65" s="20"/>
     </row>
     <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="10"/>
+      <c r="A66" s="8"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
       <c r="D66" s="18"/>
@@ -4418,7 +4462,7 @@
       <c r="V66" s="20"/>
     </row>
     <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="10"/>
+      <c r="A67" s="8"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
       <c r="D67" s="18"/>
@@ -4442,7 +4486,7 @@
       <c r="V67" s="20"/>
     </row>
     <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="10"/>
+      <c r="A68" s="8"/>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
       <c r="D68" s="18"/>
@@ -4466,7 +4510,7 @@
       <c r="V68" s="20"/>
     </row>
     <row r="69" ht="19.5" customHeight="1">
-      <c r="A69" s="10"/>
+      <c r="A69" s="8"/>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
       <c r="D69" s="18"/>
@@ -4490,7 +4534,7 @@
       <c r="V69" s="20"/>
     </row>
     <row r="70" ht="19.5" customHeight="1">
-      <c r="A70" s="10"/>
+      <c r="A70" s="8"/>
       <c r="B70" s="18"/>
       <c r="C70" s="18"/>
       <c r="D70" s="18"/>
@@ -4514,7 +4558,7 @@
       <c r="V70" s="20"/>
     </row>
     <row r="71" ht="19.5" customHeight="1">
-      <c r="A71" s="10"/>
+      <c r="A71" s="8"/>
       <c r="B71" s="18"/>
       <c r="C71" s="18"/>
       <c r="D71" s="18"/>
@@ -4538,7 +4582,7 @@
       <c r="V71" s="20"/>
     </row>
     <row r="72" ht="19.5" customHeight="1">
-      <c r="A72" s="10"/>
+      <c r="A72" s="8"/>
       <c r="B72" s="18"/>
       <c r="C72" s="18"/>
       <c r="D72" s="18"/>
@@ -4562,7 +4606,7 @@
       <c r="V72" s="20"/>
     </row>
     <row r="73" ht="19.5" customHeight="1">
-      <c r="A73" s="10"/>
+      <c r="A73" s="8"/>
       <c r="B73" s="18"/>
       <c r="C73" s="18"/>
       <c r="D73" s="18"/>
@@ -4586,7 +4630,7 @@
       <c r="V73" s="20"/>
     </row>
     <row r="74" ht="19.5" customHeight="1">
-      <c r="A74" s="10"/>
+      <c r="A74" s="8"/>
       <c r="B74" s="18"/>
       <c r="C74" s="18"/>
       <c r="D74" s="18"/>
@@ -4610,7 +4654,7 @@
       <c r="V74" s="20"/>
     </row>
     <row r="75" ht="19.5" customHeight="1">
-      <c r="A75" s="10"/>
+      <c r="A75" s="8"/>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
       <c r="D75" s="18"/>
@@ -4634,7 +4678,7 @@
       <c r="V75" s="20"/>
     </row>
     <row r="76" ht="19.5" customHeight="1">
-      <c r="A76" s="10"/>
+      <c r="A76" s="8"/>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
       <c r="D76" s="18"/>
@@ -4658,7 +4702,7 @@
       <c r="V76" s="20"/>
     </row>
     <row r="77" ht="19.5" customHeight="1">
-      <c r="A77" s="10"/>
+      <c r="A77" s="8"/>
       <c r="B77" s="18"/>
       <c r="C77" s="18"/>
       <c r="D77" s="18"/>
@@ -4682,7 +4726,7 @@
       <c r="V77" s="20"/>
     </row>
     <row r="78" ht="19.5" customHeight="1">
-      <c r="A78" s="10"/>
+      <c r="A78" s="8"/>
       <c r="B78" s="18"/>
       <c r="C78" s="18"/>
       <c r="D78" s="18"/>
@@ -4706,7 +4750,7 @@
       <c r="V78" s="20"/>
     </row>
     <row r="79" ht="19.5" customHeight="1">
-      <c r="A79" s="10"/>
+      <c r="A79" s="8"/>
       <c r="B79" s="18"/>
       <c r="C79" s="18"/>
       <c r="D79" s="18"/>
@@ -4730,7 +4774,7 @@
       <c r="V79" s="20"/>
     </row>
     <row r="80" ht="19.5" customHeight="1">
-      <c r="A80" s="10"/>
+      <c r="A80" s="8"/>
       <c r="B80" s="18"/>
       <c r="C80" s="18"/>
       <c r="D80" s="18"/>
@@ -4754,7 +4798,7 @@
       <c r="V80" s="20"/>
     </row>
     <row r="81" ht="19.5" customHeight="1">
-      <c r="A81" s="10"/>
+      <c r="A81" s="8"/>
       <c r="B81" s="18"/>
       <c r="C81" s="18"/>
       <c r="D81" s="18"/>
@@ -4778,7 +4822,7 @@
       <c r="V81" s="20"/>
     </row>
     <row r="82" ht="19.5" customHeight="1">
-      <c r="A82" s="10"/>
+      <c r="A82" s="8"/>
       <c r="B82" s="18"/>
       <c r="C82" s="18"/>
       <c r="D82" s="18"/>
@@ -4802,7 +4846,7 @@
       <c r="V82" s="20"/>
     </row>
     <row r="83" ht="19.5" customHeight="1">
-      <c r="A83" s="10"/>
+      <c r="A83" s="8"/>
       <c r="B83" s="18"/>
       <c r="C83" s="18"/>
       <c r="D83" s="18"/>
@@ -4826,7 +4870,7 @@
       <c r="V83" s="20"/>
     </row>
     <row r="84" ht="19.5" customHeight="1">
-      <c r="A84" s="10"/>
+      <c r="A84" s="8"/>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
       <c r="D84" s="18"/>
@@ -4850,7 +4894,7 @@
       <c r="V84" s="20"/>
     </row>
     <row r="85" ht="19.5" customHeight="1">
-      <c r="A85" s="10"/>
+      <c r="A85" s="8"/>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
       <c r="D85" s="18"/>
@@ -4874,7 +4918,7 @@
       <c r="V85" s="20"/>
     </row>
     <row r="86" ht="19.5" customHeight="1">
-      <c r="A86" s="10"/>
+      <c r="A86" s="8"/>
       <c r="B86" s="18"/>
       <c r="C86" s="18"/>
       <c r="D86" s="18"/>
@@ -4898,7 +4942,7 @@
       <c r="V86" s="20"/>
     </row>
     <row r="87" ht="19.5" customHeight="1">
-      <c r="A87" s="10"/>
+      <c r="A87" s="8"/>
       <c r="B87" s="18"/>
       <c r="C87" s="18"/>
       <c r="D87" s="18"/>
@@ -4922,7 +4966,7 @@
       <c r="V87" s="20"/>
     </row>
     <row r="88" ht="19.5" customHeight="1">
-      <c r="A88" s="10"/>
+      <c r="A88" s="8"/>
       <c r="B88" s="18"/>
       <c r="C88" s="18"/>
       <c r="D88" s="18"/>
@@ -4946,7 +4990,7 @@
       <c r="V88" s="20"/>
     </row>
     <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="10"/>
+      <c r="A89" s="8"/>
       <c r="B89" s="18"/>
       <c r="C89" s="18"/>
       <c r="D89" s="18"/>
@@ -4970,7 +5014,7 @@
       <c r="V89" s="20"/>
     </row>
     <row r="90" ht="19.5" customHeight="1">
-      <c r="A90" s="10"/>
+      <c r="A90" s="8"/>
       <c r="B90" s="18"/>
       <c r="C90" s="18"/>
       <c r="D90" s="18"/>
@@ -4994,7 +5038,7 @@
       <c r="V90" s="20"/>
     </row>
     <row r="91" ht="19.5" customHeight="1">
-      <c r="A91" s="10"/>
+      <c r="A91" s="8"/>
       <c r="B91" s="18"/>
       <c r="C91" s="18"/>
       <c r="D91" s="18"/>
@@ -5018,7 +5062,7 @@
       <c r="V91" s="20"/>
     </row>
     <row r="92" ht="19.5" customHeight="1">
-      <c r="A92" s="10"/>
+      <c r="A92" s="8"/>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
       <c r="D92" s="18"/>
@@ -5042,7 +5086,7 @@
       <c r="V92" s="20"/>
     </row>
     <row r="93" ht="19.5" customHeight="1">
-      <c r="A93" s="10"/>
+      <c r="A93" s="8"/>
       <c r="B93" s="18"/>
       <c r="C93" s="18"/>
       <c r="D93" s="18"/>
@@ -5066,7 +5110,7 @@
       <c r="V93" s="20"/>
     </row>
     <row r="94" ht="19.5" customHeight="1">
-      <c r="A94" s="10"/>
+      <c r="A94" s="8"/>
       <c r="B94" s="18"/>
       <c r="C94" s="18"/>
       <c r="D94" s="18"/>
@@ -5090,7 +5134,7 @@
       <c r="V94" s="20"/>
     </row>
     <row r="95" ht="19.5" customHeight="1">
-      <c r="A95" s="10"/>
+      <c r="A95" s="8"/>
       <c r="B95" s="18"/>
       <c r="C95" s="18"/>
       <c r="D95" s="18"/>
@@ -5114,7 +5158,7 @@
       <c r="V95" s="20"/>
     </row>
     <row r="96" ht="19.5" customHeight="1">
-      <c r="A96" s="10"/>
+      <c r="A96" s="8"/>
       <c r="B96" s="18"/>
       <c r="C96" s="18"/>
       <c r="D96" s="18"/>
@@ -5138,7 +5182,7 @@
       <c r="V96" s="20"/>
     </row>
     <row r="97" ht="19.5" customHeight="1">
-      <c r="A97" s="10"/>
+      <c r="A97" s="8"/>
       <c r="B97" s="18"/>
       <c r="C97" s="18"/>
       <c r="D97" s="18"/>
@@ -5162,7 +5206,7 @@
       <c r="V97" s="20"/>
     </row>
     <row r="98" ht="19.5" customHeight="1">
-      <c r="A98" s="10"/>
+      <c r="A98" s="8"/>
       <c r="B98" s="18"/>
       <c r="C98" s="18"/>
       <c r="D98" s="18"/>
@@ -5186,7 +5230,7 @@
       <c r="V98" s="20"/>
     </row>
     <row r="99" ht="19.5" customHeight="1">
-      <c r="A99" s="10"/>
+      <c r="A99" s="8"/>
       <c r="B99" s="18"/>
       <c r="C99" s="18"/>
       <c r="D99" s="18"/>
@@ -5210,7 +5254,7 @@
       <c r="V99" s="20"/>
     </row>
     <row r="100" ht="19.5" customHeight="1">
-      <c r="A100" s="10"/>
+      <c r="A100" s="8"/>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
       <c r="D100" s="18"/>
@@ -5234,7 +5278,7 @@
       <c r="V100" s="20"/>
     </row>
     <row r="101" ht="19.5" customHeight="1">
-      <c r="A101" s="10"/>
+      <c r="A101" s="8"/>
       <c r="B101" s="18"/>
       <c r="C101" s="18"/>
       <c r="D101" s="18"/>
@@ -5258,7 +5302,7 @@
       <c r="V101" s="20"/>
     </row>
     <row r="102" ht="19.5" customHeight="1">
-      <c r="A102" s="10"/>
+      <c r="A102" s="8"/>
       <c r="B102" s="18"/>
       <c r="C102" s="18"/>
       <c r="D102" s="18"/>
@@ -5282,7 +5326,7 @@
       <c r="V102" s="20"/>
     </row>
     <row r="103" ht="19.5" customHeight="1">
-      <c r="A103" s="10"/>
+      <c r="A103" s="8"/>
       <c r="B103" s="18"/>
       <c r="C103" s="18"/>
       <c r="D103" s="18"/>
@@ -5306,7 +5350,7 @@
       <c r="V103" s="20"/>
     </row>
     <row r="104" ht="19.5" customHeight="1">
-      <c r="A104" s="10"/>
+      <c r="A104" s="8"/>
       <c r="B104" s="18"/>
       <c r="C104" s="18"/>
       <c r="D104" s="18"/>
@@ -5330,7 +5374,7 @@
       <c r="V104" s="20"/>
     </row>
     <row r="105" ht="19.5" customHeight="1">
-      <c r="A105" s="10"/>
+      <c r="A105" s="8"/>
       <c r="B105" s="18"/>
       <c r="C105" s="18"/>
       <c r="D105" s="18"/>
@@ -5354,7 +5398,7 @@
       <c r="V105" s="20"/>
     </row>
     <row r="106" ht="19.5" customHeight="1">
-      <c r="A106" s="10"/>
+      <c r="A106" s="8"/>
       <c r="B106" s="18"/>
       <c r="C106" s="18"/>
       <c r="D106" s="18"/>
@@ -5378,7 +5422,7 @@
       <c r="V106" s="20"/>
     </row>
     <row r="107" ht="19.5" customHeight="1">
-      <c r="A107" s="10"/>
+      <c r="A107" s="8"/>
       <c r="B107" s="18"/>
       <c r="C107" s="18"/>
       <c r="D107" s="18"/>
@@ -5402,7 +5446,7 @@
       <c r="V107" s="20"/>
     </row>
     <row r="108" ht="19.5" customHeight="1">
-      <c r="A108" s="10"/>
+      <c r="A108" s="8"/>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
       <c r="D108" s="18"/>
@@ -5426,7 +5470,7 @@
       <c r="V108" s="20"/>
     </row>
     <row r="109" ht="19.5" customHeight="1">
-      <c r="A109" s="10"/>
+      <c r="A109" s="8"/>
       <c r="B109" s="18"/>
       <c r="C109" s="18"/>
       <c r="D109" s="18"/>
@@ -5450,7 +5494,7 @@
       <c r="V109" s="20"/>
     </row>
     <row r="110" ht="19.5" customHeight="1">
-      <c r="A110" s="10"/>
+      <c r="A110" s="8"/>
       <c r="B110" s="18"/>
       <c r="C110" s="18"/>
       <c r="D110" s="18"/>
@@ -5474,7 +5518,7 @@
       <c r="V110" s="20"/>
     </row>
     <row r="111" ht="19.5" customHeight="1">
-      <c r="A111" s="10"/>
+      <c r="A111" s="8"/>
       <c r="B111" s="18"/>
       <c r="C111" s="18"/>
       <c r="D111" s="18"/>
@@ -5498,7 +5542,7 @@
       <c r="V111" s="20"/>
     </row>
     <row r="112" ht="19.5" customHeight="1">
-      <c r="A112" s="10"/>
+      <c r="A112" s="8"/>
       <c r="B112" s="18"/>
       <c r="C112" s="18"/>
       <c r="D112" s="18"/>
@@ -5522,7 +5566,7 @@
       <c r="V112" s="20"/>
     </row>
     <row r="113" ht="19.5" customHeight="1">
-      <c r="A113" s="10"/>
+      <c r="A113" s="8"/>
       <c r="B113" s="18"/>
       <c r="C113" s="18"/>
       <c r="D113" s="18"/>
@@ -5546,7 +5590,7 @@
       <c r="V113" s="20"/>
     </row>
     <row r="114" ht="19.5" customHeight="1">
-      <c r="A114" s="10"/>
+      <c r="A114" s="8"/>
       <c r="B114" s="18"/>
       <c r="C114" s="18"/>
       <c r="D114" s="18"/>
@@ -5570,7 +5614,7 @@
       <c r="V114" s="20"/>
     </row>
     <row r="115" ht="19.5" customHeight="1">
-      <c r="A115" s="10"/>
+      <c r="A115" s="8"/>
       <c r="B115" s="18"/>
       <c r="C115" s="18"/>
       <c r="D115" s="18"/>
@@ -5594,7 +5638,7 @@
       <c r="V115" s="20"/>
     </row>
     <row r="116" ht="19.5" customHeight="1">
-      <c r="A116" s="10"/>
+      <c r="A116" s="8"/>
       <c r="B116" s="18"/>
       <c r="C116" s="18"/>
       <c r="D116" s="18"/>
@@ -5618,7 +5662,7 @@
       <c r="V116" s="20"/>
     </row>
     <row r="117" ht="19.5" customHeight="1">
-      <c r="A117" s="10"/>
+      <c r="A117" s="8"/>
       <c r="B117" s="18"/>
       <c r="C117" s="18"/>
       <c r="D117" s="18"/>
@@ -5642,7 +5686,7 @@
       <c r="V117" s="20"/>
     </row>
     <row r="118" ht="19.5" customHeight="1">
-      <c r="A118" s="10"/>
+      <c r="A118" s="8"/>
       <c r="B118" s="18"/>
       <c r="C118" s="18"/>
       <c r="D118" s="18"/>
@@ -5666,7 +5710,7 @@
       <c r="V118" s="20"/>
     </row>
     <row r="119" ht="19.5" customHeight="1">
-      <c r="A119" s="10"/>
+      <c r="A119" s="8"/>
       <c r="B119" s="18"/>
       <c r="C119" s="18"/>
       <c r="D119" s="18"/>
@@ -5690,7 +5734,7 @@
       <c r="V119" s="20"/>
     </row>
     <row r="120" ht="19.5" customHeight="1">
-      <c r="A120" s="10"/>
+      <c r="A120" s="8"/>
       <c r="B120" s="18"/>
       <c r="C120" s="18"/>
       <c r="D120" s="18"/>
@@ -5714,7 +5758,7 @@
       <c r="V120" s="20"/>
     </row>
     <row r="121" ht="19.5" customHeight="1">
-      <c r="A121" s="10"/>
+      <c r="A121" s="8"/>
       <c r="B121" s="18"/>
       <c r="C121" s="18"/>
       <c r="D121" s="18"/>
@@ -5738,7 +5782,7 @@
       <c r="V121" s="20"/>
     </row>
     <row r="122" ht="19.5" customHeight="1">
-      <c r="A122" s="10"/>
+      <c r="A122" s="8"/>
       <c r="B122" s="18"/>
       <c r="C122" s="18"/>
       <c r="D122" s="18"/>
@@ -5762,7 +5806,7 @@
       <c r="V122" s="20"/>
     </row>
     <row r="123" ht="19.5" customHeight="1">
-      <c r="A123" s="10"/>
+      <c r="A123" s="8"/>
       <c r="B123" s="18"/>
       <c r="C123" s="18"/>
       <c r="D123" s="18"/>
@@ -5786,7 +5830,7 @@
       <c r="V123" s="20"/>
     </row>
     <row r="124" ht="19.5" customHeight="1">
-      <c r="A124" s="10"/>
+      <c r="A124" s="8"/>
       <c r="B124" s="18"/>
       <c r="C124" s="18"/>
       <c r="D124" s="18"/>
@@ -5810,7 +5854,7 @@
       <c r="V124" s="20"/>
     </row>
     <row r="125" ht="19.5" customHeight="1">
-      <c r="A125" s="10"/>
+      <c r="A125" s="8"/>
       <c r="B125" s="18"/>
       <c r="C125" s="18"/>
       <c r="D125" s="18"/>
@@ -5834,7 +5878,7 @@
       <c r="V125" s="20"/>
     </row>
     <row r="126" ht="19.5" customHeight="1">
-      <c r="A126" s="10"/>
+      <c r="A126" s="8"/>
       <c r="B126" s="18"/>
       <c r="C126" s="18"/>
       <c r="D126" s="18"/>
@@ -5858,7 +5902,7 @@
       <c r="V126" s="20"/>
     </row>
     <row r="127" ht="19.5" customHeight="1">
-      <c r="A127" s="10"/>
+      <c r="A127" s="8"/>
       <c r="B127" s="18"/>
       <c r="C127" s="18"/>
       <c r="D127" s="18"/>
@@ -5882,7 +5926,7 @@
       <c r="V127" s="20"/>
     </row>
     <row r="128" ht="19.5" customHeight="1">
-      <c r="A128" s="10"/>
+      <c r="A128" s="8"/>
       <c r="B128" s="18"/>
       <c r="C128" s="18"/>
       <c r="D128" s="18"/>
@@ -5906,7 +5950,7 @@
       <c r="V128" s="20"/>
     </row>
     <row r="129" ht="19.5" customHeight="1">
-      <c r="A129" s="10"/>
+      <c r="A129" s="8"/>
       <c r="B129" s="18"/>
       <c r="C129" s="18"/>
       <c r="D129" s="18"/>
@@ -5930,7 +5974,7 @@
       <c r="V129" s="20"/>
     </row>
     <row r="130" ht="19.5" customHeight="1">
-      <c r="A130" s="10"/>
+      <c r="A130" s="8"/>
       <c r="B130" s="18"/>
       <c r="C130" s="18"/>
       <c r="D130" s="18"/>
@@ -5954,7 +5998,7 @@
       <c r="V130" s="20"/>
     </row>
     <row r="131" ht="19.5" customHeight="1">
-      <c r="A131" s="10"/>
+      <c r="A131" s="8"/>
       <c r="B131" s="18"/>
       <c r="C131" s="18"/>
       <c r="D131" s="18"/>
@@ -5978,7 +6022,7 @@
       <c r="V131" s="20"/>
     </row>
     <row r="132" ht="19.5" customHeight="1">
-      <c r="A132" s="10"/>
+      <c r="A132" s="8"/>
       <c r="B132" s="18"/>
       <c r="C132" s="18"/>
       <c r="D132" s="18"/>
@@ -6002,7 +6046,7 @@
       <c r="V132" s="20"/>
     </row>
     <row r="133" ht="19.5" customHeight="1">
-      <c r="A133" s="10"/>
+      <c r="A133" s="8"/>
       <c r="B133" s="18"/>
       <c r="C133" s="18"/>
       <c r="D133" s="18"/>
@@ -6026,7 +6070,7 @@
       <c r="V133" s="20"/>
     </row>
     <row r="134" ht="19.5" customHeight="1">
-      <c r="A134" s="10"/>
+      <c r="A134" s="8"/>
       <c r="B134" s="18"/>
       <c r="C134" s="18"/>
       <c r="D134" s="18"/>
@@ -6050,7 +6094,7 @@
       <c r="V134" s="20"/>
     </row>
     <row r="135" ht="19.5" customHeight="1">
-      <c r="A135" s="10"/>
+      <c r="A135" s="8"/>
       <c r="B135" s="18"/>
       <c r="C135" s="18"/>
       <c r="D135" s="18"/>
@@ -6074,7 +6118,7 @@
       <c r="V135" s="20"/>
     </row>
     <row r="136" ht="19.5" customHeight="1">
-      <c r="A136" s="10"/>
+      <c r="A136" s="8"/>
       <c r="B136" s="18"/>
       <c r="C136" s="18"/>
       <c r="D136" s="18"/>
@@ -6098,7 +6142,7 @@
       <c r="V136" s="20"/>
     </row>
     <row r="137" ht="19.5" customHeight="1">
-      <c r="A137" s="10"/>
+      <c r="A137" s="8"/>
       <c r="B137" s="18"/>
       <c r="C137" s="18"/>
       <c r="D137" s="18"/>
@@ -6122,7 +6166,7 @@
       <c r="V137" s="20"/>
     </row>
     <row r="138" ht="19.5" customHeight="1">
-      <c r="A138" s="10"/>
+      <c r="A138" s="8"/>
       <c r="B138" s="18"/>
       <c r="C138" s="18"/>
       <c r="D138" s="18"/>
@@ -6146,7 +6190,7 @@
       <c r="V138" s="20"/>
     </row>
     <row r="139" ht="19.5" customHeight="1">
-      <c r="A139" s="10"/>
+      <c r="A139" s="8"/>
       <c r="B139" s="18"/>
       <c r="C139" s="18"/>
       <c r="D139" s="18"/>
@@ -6170,7 +6214,7 @@
       <c r="V139" s="20"/>
     </row>
     <row r="140" ht="19.5" customHeight="1">
-      <c r="A140" s="10"/>
+      <c r="A140" s="8"/>
       <c r="B140" s="18"/>
       <c r="C140" s="18"/>
       <c r="D140" s="18"/>
@@ -6194,7 +6238,7 @@
       <c r="V140" s="20"/>
     </row>
     <row r="141" ht="19.5" customHeight="1">
-      <c r="A141" s="10"/>
+      <c r="A141" s="8"/>
       <c r="B141" s="18"/>
       <c r="C141" s="18"/>
       <c r="D141" s="18"/>
@@ -6218,7 +6262,7 @@
       <c r="V141" s="20"/>
     </row>
     <row r="142" ht="19.5" customHeight="1">
-      <c r="A142" s="10"/>
+      <c r="A142" s="8"/>
       <c r="B142" s="18"/>
       <c r="C142" s="18"/>
       <c r="D142" s="18"/>
@@ -6242,7 +6286,7 @@
       <c r="V142" s="20"/>
     </row>
     <row r="143" ht="19.5" customHeight="1">
-      <c r="A143" s="10"/>
+      <c r="A143" s="8"/>
       <c r="B143" s="18"/>
       <c r="C143" s="18"/>
       <c r="D143" s="18"/>
@@ -6266,7 +6310,7 @@
       <c r="V143" s="20"/>
     </row>
     <row r="144" ht="19.5" customHeight="1">
-      <c r="A144" s="10"/>
+      <c r="A144" s="8"/>
       <c r="B144" s="18"/>
       <c r="C144" s="18"/>
       <c r="D144" s="18"/>
@@ -6290,7 +6334,7 @@
       <c r="V144" s="20"/>
     </row>
     <row r="145" ht="19.5" customHeight="1">
-      <c r="A145" s="10"/>
+      <c r="A145" s="8"/>
       <c r="B145" s="18"/>
       <c r="C145" s="18"/>
       <c r="D145" s="18"/>
@@ -6314,7 +6358,7 @@
       <c r="V145" s="20"/>
     </row>
     <row r="146" ht="19.5" customHeight="1">
-      <c r="A146" s="10"/>
+      <c r="A146" s="8"/>
       <c r="B146" s="18"/>
       <c r="C146" s="18"/>
       <c r="D146" s="18"/>
@@ -6338,7 +6382,7 @@
       <c r="V146" s="20"/>
     </row>
     <row r="147" ht="19.5" customHeight="1">
-      <c r="A147" s="10"/>
+      <c r="A147" s="8"/>
       <c r="B147" s="18"/>
       <c r="C147" s="18"/>
       <c r="D147" s="18"/>
@@ -6362,7 +6406,7 @@
       <c r="V147" s="20"/>
     </row>
     <row r="148" ht="19.5" customHeight="1">
-      <c r="A148" s="10"/>
+      <c r="A148" s="8"/>
       <c r="B148" s="18"/>
       <c r="C148" s="18"/>
       <c r="D148" s="18"/>
@@ -6386,7 +6430,7 @@
       <c r="V148" s="20"/>
     </row>
     <row r="149" ht="19.5" customHeight="1">
-      <c r="A149" s="10"/>
+      <c r="A149" s="8"/>
       <c r="B149" s="18"/>
       <c r="C149" s="18"/>
       <c r="D149" s="18"/>
@@ -6410,7 +6454,7 @@
       <c r="V149" s="20"/>
     </row>
     <row r="150" ht="19.5" customHeight="1">
-      <c r="A150" s="10"/>
+      <c r="A150" s="8"/>
       <c r="B150" s="18"/>
       <c r="C150" s="18"/>
       <c r="D150" s="18"/>
@@ -6434,7 +6478,7 @@
       <c r="V150" s="20"/>
     </row>
     <row r="151" ht="19.5" customHeight="1">
-      <c r="A151" s="10"/>
+      <c r="A151" s="8"/>
       <c r="B151" s="18"/>
       <c r="C151" s="18"/>
       <c r="D151" s="18"/>
@@ -6458,7 +6502,7 @@
       <c r="V151" s="20"/>
     </row>
     <row r="152" ht="19.5" customHeight="1">
-      <c r="A152" s="10"/>
+      <c r="A152" s="8"/>
       <c r="B152" s="18"/>
       <c r="C152" s="18"/>
       <c r="D152" s="18"/>
@@ -6482,7 +6526,7 @@
       <c r="V152" s="20"/>
     </row>
     <row r="153" ht="19.5" customHeight="1">
-      <c r="A153" s="10"/>
+      <c r="A153" s="8"/>
       <c r="B153" s="18"/>
       <c r="C153" s="18"/>
       <c r="D153" s="18"/>
@@ -6506,7 +6550,7 @@
       <c r="V153" s="20"/>
     </row>
     <row r="154" ht="19.5" customHeight="1">
-      <c r="A154" s="10"/>
+      <c r="A154" s="8"/>
       <c r="B154" s="18"/>
       <c r="C154" s="18"/>
       <c r="D154" s="18"/>
@@ -6530,7 +6574,7 @@
       <c r="V154" s="20"/>
     </row>
     <row r="155" ht="19.5" customHeight="1">
-      <c r="A155" s="10"/>
+      <c r="A155" s="8"/>
       <c r="B155" s="18"/>
       <c r="C155" s="18"/>
       <c r="D155" s="18"/>
@@ -6554,7 +6598,7 @@
       <c r="V155" s="20"/>
     </row>
     <row r="156" ht="19.5" customHeight="1">
-      <c r="A156" s="10"/>
+      <c r="A156" s="8"/>
       <c r="B156" s="18"/>
       <c r="C156" s="18"/>
       <c r="D156" s="18"/>
@@ -6578,7 +6622,7 @@
       <c r="V156" s="20"/>
     </row>
     <row r="157" ht="19.5" customHeight="1">
-      <c r="A157" s="10"/>
+      <c r="A157" s="8"/>
       <c r="B157" s="18"/>
       <c r="C157" s="18"/>
       <c r="D157" s="18"/>
@@ -6602,7 +6646,7 @@
       <c r="V157" s="20"/>
     </row>
     <row r="158" ht="19.5" customHeight="1">
-      <c r="A158" s="10"/>
+      <c r="A158" s="8"/>
       <c r="B158" s="18"/>
       <c r="C158" s="18"/>
       <c r="D158" s="18"/>
@@ -6626,7 +6670,7 @@
       <c r="V158" s="20"/>
     </row>
     <row r="159" ht="19.5" customHeight="1">
-      <c r="A159" s="10"/>
+      <c r="A159" s="8"/>
       <c r="B159" s="18"/>
       <c r="C159" s="18"/>
       <c r="D159" s="18"/>
@@ -6650,7 +6694,7 @@
       <c r="V159" s="20"/>
     </row>
     <row r="160" ht="19.5" customHeight="1">
-      <c r="A160" s="10"/>
+      <c r="A160" s="8"/>
       <c r="B160" s="18"/>
       <c r="C160" s="18"/>
       <c r="D160" s="18"/>
@@ -6674,7 +6718,7 @@
       <c r="V160" s="20"/>
     </row>
     <row r="161" ht="19.5" customHeight="1">
-      <c r="A161" s="10"/>
+      <c r="A161" s="8"/>
       <c r="B161" s="18"/>
       <c r="C161" s="18"/>
       <c r="D161" s="18"/>
@@ -6698,7 +6742,7 @@
       <c r="V161" s="20"/>
     </row>
     <row r="162" ht="19.5" customHeight="1">
-      <c r="A162" s="10"/>
+      <c r="A162" s="8"/>
       <c r="B162" s="18"/>
       <c r="C162" s="18"/>
       <c r="D162" s="18"/>
@@ -6722,7 +6766,7 @@
       <c r="V162" s="20"/>
     </row>
     <row r="163" ht="19.5" customHeight="1">
-      <c r="A163" s="10"/>
+      <c r="A163" s="8"/>
       <c r="B163" s="18"/>
       <c r="C163" s="18"/>
       <c r="D163" s="18"/>
@@ -6746,7 +6790,7 @@
       <c r="V163" s="20"/>
     </row>
     <row r="164" ht="19.5" customHeight="1">
-      <c r="A164" s="10"/>
+      <c r="A164" s="8"/>
       <c r="B164" s="18"/>
       <c r="C164" s="18"/>
       <c r="D164" s="18"/>
@@ -6770,7 +6814,7 @@
       <c r="V164" s="20"/>
     </row>
     <row r="165" ht="19.5" customHeight="1">
-      <c r="A165" s="10"/>
+      <c r="A165" s="8"/>
       <c r="B165" s="18"/>
       <c r="C165" s="18"/>
       <c r="D165" s="18"/>
@@ -6794,7 +6838,7 @@
       <c r="V165" s="20"/>
     </row>
     <row r="166" ht="19.5" customHeight="1">
-      <c r="A166" s="10"/>
+      <c r="A166" s="8"/>
       <c r="B166" s="18"/>
       <c r="C166" s="18"/>
       <c r="D166" s="18"/>
@@ -6818,7 +6862,7 @@
       <c r="V166" s="20"/>
     </row>
     <row r="167" ht="19.5" customHeight="1">
-      <c r="A167" s="10"/>
+      <c r="A167" s="8"/>
       <c r="B167" s="18"/>
       <c r="C167" s="18"/>
       <c r="D167" s="18"/>
@@ -6842,7 +6886,7 @@
       <c r="V167" s="20"/>
     </row>
     <row r="168" ht="19.5" customHeight="1">
-      <c r="A168" s="10"/>
+      <c r="A168" s="8"/>
       <c r="B168" s="18"/>
       <c r="C168" s="18"/>
       <c r="D168" s="18"/>
@@ -6866,7 +6910,7 @@
       <c r="V168" s="20"/>
     </row>
     <row r="169" ht="19.5" customHeight="1">
-      <c r="A169" s="10"/>
+      <c r="A169" s="8"/>
       <c r="B169" s="18"/>
       <c r="C169" s="18"/>
       <c r="D169" s="18"/>
@@ -6890,7 +6934,7 @@
       <c r="V169" s="20"/>
     </row>
     <row r="170" ht="19.5" customHeight="1">
-      <c r="A170" s="10"/>
+      <c r="A170" s="8"/>
       <c r="B170" s="18"/>
       <c r="C170" s="18"/>
       <c r="D170" s="18"/>
@@ -6914,7 +6958,7 @@
       <c r="V170" s="20"/>
     </row>
     <row r="171" ht="19.5" customHeight="1">
-      <c r="A171" s="10"/>
+      <c r="A171" s="8"/>
       <c r="B171" s="18"/>
       <c r="C171" s="18"/>
       <c r="D171" s="18"/>
@@ -6938,7 +6982,7 @@
       <c r="V171" s="20"/>
     </row>
     <row r="172" ht="19.5" customHeight="1">
-      <c r="A172" s="10"/>
+      <c r="A172" s="8"/>
       <c r="B172" s="18"/>
       <c r="C172" s="18"/>
       <c r="D172" s="18"/>
@@ -6962,7 +7006,7 @@
       <c r="V172" s="20"/>
     </row>
     <row r="173" ht="19.5" customHeight="1">
-      <c r="A173" s="10"/>
+      <c r="A173" s="8"/>
       <c r="B173" s="18"/>
       <c r="C173" s="18"/>
       <c r="D173" s="18"/>
@@ -6986,7 +7030,7 @@
       <c r="V173" s="20"/>
     </row>
     <row r="174" ht="19.5" customHeight="1">
-      <c r="A174" s="10"/>
+      <c r="A174" s="8"/>
       <c r="B174" s="18"/>
       <c r="C174" s="18"/>
       <c r="D174" s="18"/>
@@ -7010,7 +7054,7 @@
       <c r="V174" s="20"/>
     </row>
     <row r="175" ht="19.5" customHeight="1">
-      <c r="A175" s="10"/>
+      <c r="A175" s="8"/>
       <c r="B175" s="18"/>
       <c r="C175" s="18"/>
       <c r="D175" s="18"/>
@@ -7034,7 +7078,7 @@
       <c r="V175" s="20"/>
     </row>
     <row r="176" ht="19.5" customHeight="1">
-      <c r="A176" s="10"/>
+      <c r="A176" s="8"/>
       <c r="B176" s="18"/>
       <c r="C176" s="18"/>
       <c r="D176" s="18"/>
@@ -7058,7 +7102,7 @@
       <c r="V176" s="20"/>
     </row>
     <row r="177" ht="19.5" customHeight="1">
-      <c r="A177" s="10"/>
+      <c r="A177" s="8"/>
       <c r="B177" s="18"/>
       <c r="C177" s="18"/>
       <c r="D177" s="18"/>
@@ -7082,7 +7126,7 @@
       <c r="V177" s="20"/>
     </row>
     <row r="178" ht="19.5" customHeight="1">
-      <c r="A178" s="10"/>
+      <c r="A178" s="8"/>
       <c r="B178" s="18"/>
       <c r="C178" s="18"/>
       <c r="D178" s="18"/>
@@ -7106,7 +7150,7 @@
       <c r="V178" s="20"/>
     </row>
     <row r="179" ht="19.5" customHeight="1">
-      <c r="A179" s="10"/>
+      <c r="A179" s="8"/>
       <c r="B179" s="18"/>
       <c r="C179" s="18"/>
       <c r="D179" s="18"/>
@@ -7130,7 +7174,7 @@
       <c r="V179" s="20"/>
     </row>
     <row r="180" ht="19.5" customHeight="1">
-      <c r="A180" s="10"/>
+      <c r="A180" s="8"/>
       <c r="B180" s="18"/>
       <c r="C180" s="18"/>
       <c r="D180" s="18"/>
@@ -7154,7 +7198,7 @@
       <c r="V180" s="20"/>
     </row>
     <row r="181" ht="19.5" customHeight="1">
-      <c r="A181" s="10"/>
+      <c r="A181" s="8"/>
       <c r="B181" s="18"/>
       <c r="C181" s="18"/>
       <c r="D181" s="18"/>
@@ -7178,7 +7222,7 @@
       <c r="V181" s="20"/>
     </row>
     <row r="182" ht="19.5" customHeight="1">
-      <c r="A182" s="10"/>
+      <c r="A182" s="8"/>
       <c r="B182" s="18"/>
       <c r="C182" s="18"/>
       <c r="D182" s="18"/>
@@ -7202,7 +7246,7 @@
       <c r="V182" s="20"/>
     </row>
     <row r="183" ht="19.5" customHeight="1">
-      <c r="A183" s="10"/>
+      <c r="A183" s="8"/>
       <c r="B183" s="18"/>
       <c r="C183" s="18"/>
       <c r="D183" s="18"/>
@@ -7226,7 +7270,7 @@
       <c r="V183" s="20"/>
     </row>
     <row r="184" ht="19.5" customHeight="1">
-      <c r="A184" s="10"/>
+      <c r="A184" s="8"/>
       <c r="B184" s="18"/>
       <c r="C184" s="18"/>
       <c r="D184" s="18"/>
@@ -7250,7 +7294,7 @@
       <c r="V184" s="20"/>
     </row>
     <row r="185" ht="19.5" customHeight="1">
-      <c r="A185" s="10"/>
+      <c r="A185" s="8"/>
       <c r="B185" s="18"/>
       <c r="C185" s="18"/>
       <c r="D185" s="18"/>
@@ -7274,7 +7318,7 @@
       <c r="V185" s="20"/>
     </row>
     <row r="186" ht="19.5" customHeight="1">
-      <c r="A186" s="10"/>
+      <c r="A186" s="8"/>
       <c r="B186" s="18"/>
       <c r="C186" s="18"/>
       <c r="D186" s="18"/>
@@ -7298,7 +7342,7 @@
       <c r="V186" s="20"/>
     </row>
     <row r="187" ht="19.5" customHeight="1">
-      <c r="A187" s="10"/>
+      <c r="A187" s="8"/>
       <c r="B187" s="18"/>
       <c r="C187" s="18"/>
       <c r="D187" s="18"/>
@@ -7322,7 +7366,7 @@
       <c r="V187" s="20"/>
     </row>
     <row r="188" ht="19.5" customHeight="1">
-      <c r="A188" s="10"/>
+      <c r="A188" s="8"/>
       <c r="B188" s="18"/>
       <c r="C188" s="18"/>
       <c r="D188" s="18"/>
@@ -7346,7 +7390,7 @@
       <c r="V188" s="20"/>
     </row>
     <row r="189" ht="19.5" customHeight="1">
-      <c r="A189" s="10"/>
+      <c r="A189" s="8"/>
       <c r="B189" s="18"/>
       <c r="C189" s="18"/>
       <c r="D189" s="18"/>
@@ -7370,7 +7414,7 @@
       <c r="V189" s="20"/>
     </row>
     <row r="190" ht="19.5" customHeight="1">
-      <c r="A190" s="10"/>
+      <c r="A190" s="8"/>
       <c r="B190" s="18"/>
       <c r="C190" s="18"/>
       <c r="D190" s="18"/>
@@ -7394,7 +7438,7 @@
       <c r="V190" s="20"/>
     </row>
     <row r="191" ht="19.5" customHeight="1">
-      <c r="A191" s="10"/>
+      <c r="A191" s="8"/>
       <c r="B191" s="18"/>
       <c r="C191" s="18"/>
       <c r="D191" s="18"/>
@@ -7418,7 +7462,7 @@
       <c r="V191" s="20"/>
     </row>
     <row r="192" ht="19.5" customHeight="1">
-      <c r="A192" s="10"/>
+      <c r="A192" s="8"/>
       <c r="B192" s="18"/>
       <c r="C192" s="18"/>
       <c r="D192" s="18"/>
@@ -7442,7 +7486,7 @@
       <c r="V192" s="20"/>
     </row>
     <row r="193" ht="19.5" customHeight="1">
-      <c r="A193" s="10"/>
+      <c r="A193" s="8"/>
       <c r="B193" s="18"/>
       <c r="C193" s="18"/>
       <c r="D193" s="18"/>
@@ -7466,7 +7510,7 @@
       <c r="V193" s="20"/>
     </row>
     <row r="194" ht="19.5" customHeight="1">
-      <c r="A194" s="10"/>
+      <c r="A194" s="8"/>
       <c r="B194" s="18"/>
       <c r="C194" s="18"/>
       <c r="D194" s="18"/>
@@ -7490,7 +7534,7 @@
       <c r="V194" s="20"/>
     </row>
     <row r="195" ht="19.5" customHeight="1">
-      <c r="A195" s="10"/>
+      <c r="A195" s="8"/>
       <c r="B195" s="18"/>
       <c r="C195" s="18"/>
       <c r="D195" s="18"/>
@@ -7514,7 +7558,7 @@
       <c r="V195" s="20"/>
     </row>
     <row r="196" ht="19.5" customHeight="1">
-      <c r="A196" s="10"/>
+      <c r="A196" s="8"/>
       <c r="B196" s="18"/>
       <c r="C196" s="18"/>
       <c r="D196" s="18"/>
@@ -7538,7 +7582,7 @@
       <c r="V196" s="20"/>
     </row>
     <row r="197" ht="19.5" customHeight="1">
-      <c r="A197" s="10"/>
+      <c r="A197" s="8"/>
       <c r="B197" s="18"/>
       <c r="C197" s="18"/>
       <c r="D197" s="18"/>
@@ -7562,7 +7606,7 @@
       <c r="V197" s="20"/>
     </row>
     <row r="198" ht="19.5" customHeight="1">
-      <c r="A198" s="10"/>
+      <c r="A198" s="8"/>
       <c r="B198" s="18"/>
       <c r="C198" s="18"/>
       <c r="D198" s="18"/>
@@ -7586,7 +7630,7 @@
       <c r="V198" s="20"/>
     </row>
     <row r="199" ht="19.5" customHeight="1">
-      <c r="A199" s="10"/>
+      <c r="A199" s="8"/>
       <c r="B199" s="18"/>
       <c r="C199" s="18"/>
       <c r="D199" s="18"/>
@@ -7610,7 +7654,7 @@
       <c r="V199" s="20"/>
     </row>
     <row r="200" ht="19.5" customHeight="1">
-      <c r="A200" s="10"/>
+      <c r="A200" s="8"/>
       <c r="B200" s="18"/>
       <c r="C200" s="18"/>
       <c r="D200" s="18"/>
@@ -7634,7 +7678,7 @@
       <c r="V200" s="20"/>
     </row>
     <row r="201" ht="19.5" customHeight="1">
-      <c r="A201" s="10"/>
+      <c r="A201" s="8"/>
       <c r="B201" s="18"/>
       <c r="C201" s="18"/>
       <c r="D201" s="18"/>
@@ -7658,7 +7702,7 @@
       <c r="V201" s="20"/>
     </row>
     <row r="202" ht="19.5" customHeight="1">
-      <c r="A202" s="10"/>
+      <c r="A202" s="8"/>
       <c r="B202" s="18"/>
       <c r="C202" s="18"/>
       <c r="D202" s="18"/>
@@ -7682,7 +7726,7 @@
       <c r="V202" s="20"/>
     </row>
     <row r="203" ht="19.5" customHeight="1">
-      <c r="A203" s="10"/>
+      <c r="A203" s="8"/>
       <c r="B203" s="18"/>
       <c r="C203" s="18"/>
       <c r="D203" s="18"/>
@@ -7706,7 +7750,7 @@
       <c r="V203" s="20"/>
     </row>
     <row r="204" ht="19.5" customHeight="1">
-      <c r="A204" s="10"/>
+      <c r="A204" s="8"/>
       <c r="B204" s="18"/>
       <c r="C204" s="18"/>
       <c r="D204" s="18"/>
@@ -7730,7 +7774,7 @@
       <c r="V204" s="20"/>
     </row>
     <row r="205" ht="19.5" customHeight="1">
-      <c r="A205" s="10"/>
+      <c r="A205" s="8"/>
       <c r="B205" s="18"/>
       <c r="C205" s="18"/>
       <c r="D205" s="18"/>
@@ -7754,7 +7798,7 @@
       <c r="V205" s="20"/>
     </row>
     <row r="206" ht="19.5" customHeight="1">
-      <c r="A206" s="10"/>
+      <c r="A206" s="8"/>
       <c r="B206" s="18"/>
       <c r="C206" s="18"/>
       <c r="D206" s="18"/>
@@ -7778,7 +7822,7 @@
       <c r="V206" s="20"/>
     </row>
     <row r="207" ht="19.5" customHeight="1">
-      <c r="A207" s="10"/>
+      <c r="A207" s="8"/>
       <c r="B207" s="18"/>
       <c r="C207" s="18"/>
       <c r="D207" s="18"/>
@@ -7802,7 +7846,7 @@
       <c r="V207" s="20"/>
     </row>
     <row r="208" ht="19.5" customHeight="1">
-      <c r="A208" s="10"/>
+      <c r="A208" s="8"/>
       <c r="B208" s="18"/>
       <c r="C208" s="18"/>
       <c r="D208" s="18"/>
@@ -7826,7 +7870,7 @@
       <c r="V208" s="20"/>
     </row>
     <row r="209" ht="19.5" customHeight="1">
-      <c r="A209" s="10"/>
+      <c r="A209" s="8"/>
       <c r="B209" s="18"/>
       <c r="C209" s="18"/>
       <c r="D209" s="18"/>
@@ -7850,7 +7894,7 @@
       <c r="V209" s="20"/>
     </row>
     <row r="210" ht="19.5" customHeight="1">
-      <c r="A210" s="10"/>
+      <c r="A210" s="8"/>
       <c r="B210" s="18"/>
       <c r="C210" s="18"/>
       <c r="D210" s="18"/>
@@ -7874,7 +7918,7 @@
       <c r="V210" s="20"/>
     </row>
     <row r="211" ht="19.5" customHeight="1">
-      <c r="A211" s="10"/>
+      <c r="A211" s="8"/>
       <c r="B211" s="18"/>
       <c r="C211" s="18"/>
       <c r="D211" s="18"/>
@@ -7898,7 +7942,7 @@
       <c r="V211" s="20"/>
     </row>
     <row r="212" ht="19.5" customHeight="1">
-      <c r="A212" s="10"/>
+      <c r="A212" s="8"/>
       <c r="B212" s="18"/>
       <c r="C212" s="18"/>
       <c r="D212" s="18"/>
@@ -7922,7 +7966,7 @@
       <c r="V212" s="20"/>
     </row>
     <row r="213" ht="19.5" customHeight="1">
-      <c r="A213" s="10"/>
+      <c r="A213" s="8"/>
       <c r="B213" s="18"/>
       <c r="C213" s="18"/>
       <c r="D213" s="18"/>
@@ -7946,7 +7990,7 @@
       <c r="V213" s="20"/>
     </row>
     <row r="214" ht="19.5" customHeight="1">
-      <c r="A214" s="10"/>
+      <c r="A214" s="8"/>
       <c r="B214" s="18"/>
       <c r="C214" s="18"/>
       <c r="D214" s="18"/>
@@ -7970,7 +8014,7 @@
       <c r="V214" s="20"/>
     </row>
     <row r="215" ht="19.5" customHeight="1">
-      <c r="A215" s="10"/>
+      <c r="A215" s="8"/>
       <c r="B215" s="18"/>
       <c r="C215" s="18"/>
       <c r="D215" s="18"/>
@@ -7994,7 +8038,7 @@
       <c r="V215" s="20"/>
     </row>
     <row r="216" ht="19.5" customHeight="1">
-      <c r="A216" s="10"/>
+      <c r="A216" s="8"/>
       <c r="B216" s="18"/>
       <c r="C216" s="18"/>
       <c r="D216" s="18"/>
@@ -8018,7 +8062,7 @@
       <c r="V216" s="20"/>
     </row>
     <row r="217" ht="19.5" customHeight="1">
-      <c r="A217" s="10"/>
+      <c r="A217" s="8"/>
       <c r="B217" s="18"/>
       <c r="C217" s="18"/>
       <c r="D217" s="18"/>
@@ -8042,7 +8086,7 @@
       <c r="V217" s="20"/>
     </row>
     <row r="218" ht="19.5" customHeight="1">
-      <c r="A218" s="10"/>
+      <c r="A218" s="8"/>
       <c r="B218" s="18"/>
       <c r="C218" s="18"/>
       <c r="D218" s="18"/>
@@ -8066,7 +8110,7 @@
       <c r="V218" s="20"/>
     </row>
     <row r="219" ht="19.5" customHeight="1">
-      <c r="A219" s="10"/>
+      <c r="A219" s="8"/>
       <c r="B219" s="18"/>
       <c r="C219" s="18"/>
       <c r="D219" s="18"/>
@@ -8090,7 +8134,7 @@
       <c r="V219" s="20"/>
     </row>
     <row r="220" ht="19.5" customHeight="1">
-      <c r="A220" s="10"/>
+      <c r="A220" s="8"/>
       <c r="B220" s="18"/>
       <c r="C220" s="18"/>
       <c r="D220" s="18"/>
@@ -8114,7 +8158,7 @@
       <c r="V220" s="20"/>
     </row>
     <row r="221" ht="19.5" customHeight="1">
-      <c r="A221" s="10"/>
+      <c r="A221" s="8"/>
       <c r="B221" s="18"/>
       <c r="C221" s="18"/>
       <c r="D221" s="18"/>
@@ -8138,7 +8182,7 @@
       <c r="V221" s="20"/>
     </row>
     <row r="222" ht="19.5" customHeight="1">
-      <c r="A222" s="10"/>
+      <c r="A222" s="8"/>
       <c r="B222" s="18"/>
       <c r="C222" s="18"/>
       <c r="D222" s="18"/>
@@ -8162,7 +8206,7 @@
       <c r="V222" s="20"/>
     </row>
     <row r="223" ht="19.5" customHeight="1">
-      <c r="A223" s="10"/>
+      <c r="A223" s="8"/>
       <c r="B223" s="18"/>
       <c r="C223" s="18"/>
       <c r="D223" s="18"/>
@@ -8186,7 +8230,7 @@
       <c r="V223" s="20"/>
     </row>
     <row r="224" ht="19.5" customHeight="1">
-      <c r="A224" s="10"/>
+      <c r="A224" s="8"/>
       <c r="B224" s="18"/>
       <c r="C224" s="18"/>
       <c r="D224" s="18"/>
@@ -8210,7 +8254,7 @@
       <c r="V224" s="20"/>
     </row>
     <row r="225" ht="19.5" customHeight="1">
-      <c r="A225" s="10"/>
+      <c r="A225" s="8"/>
       <c r="B225" s="18"/>
       <c r="C225" s="18"/>
       <c r="D225" s="18"/>
@@ -8234,7 +8278,7 @@
       <c r="V225" s="20"/>
     </row>
     <row r="226" ht="19.5" customHeight="1">
-      <c r="A226" s="10"/>
+      <c r="A226" s="8"/>
       <c r="B226" s="18"/>
       <c r="C226" s="18"/>
       <c r="D226" s="18"/>
@@ -8258,7 +8302,7 @@
       <c r="V226" s="20"/>
     </row>
     <row r="227" ht="19.5" customHeight="1">
-      <c r="A227" s="10"/>
+      <c r="A227" s="8"/>
       <c r="B227" s="18"/>
       <c r="C227" s="18"/>
       <c r="D227" s="18"/>
@@ -8282,7 +8326,7 @@
       <c r="V227" s="20"/>
     </row>
     <row r="228" ht="19.5" customHeight="1">
-      <c r="A228" s="10"/>
+      <c r="A228" s="8"/>
       <c r="B228" s="18"/>
       <c r="C228" s="18"/>
       <c r="D228" s="18"/>
@@ -8306,7 +8350,7 @@
       <c r="V228" s="20"/>
     </row>
     <row r="229" ht="19.5" customHeight="1">
-      <c r="A229" s="10"/>
+      <c r="A229" s="8"/>
       <c r="B229" s="18"/>
       <c r="C229" s="18"/>
       <c r="D229" s="18"/>
@@ -8330,7 +8374,7 @@
       <c r="V229" s="20"/>
     </row>
     <row r="230" ht="19.5" customHeight="1">
-      <c r="A230" s="10"/>
+      <c r="A230" s="8"/>
       <c r="B230" s="18"/>
       <c r="C230" s="18"/>
       <c r="D230" s="18"/>
@@ -8354,7 +8398,7 @@
       <c r="V230" s="20"/>
     </row>
     <row r="231" ht="19.5" customHeight="1">
-      <c r="A231" s="10"/>
+      <c r="A231" s="8"/>
       <c r="B231" s="18"/>
       <c r="C231" s="18"/>
       <c r="D231" s="18"/>
@@ -8378,7 +8422,7 @@
       <c r="V231" s="20"/>
     </row>
     <row r="232" ht="19.5" customHeight="1">
-      <c r="A232" s="10"/>
+      <c r="A232" s="8"/>
       <c r="B232" s="18"/>
       <c r="C232" s="18"/>
       <c r="D232" s="18"/>
@@ -8402,7 +8446,7 @@
       <c r="V232" s="20"/>
     </row>
     <row r="233" ht="19.5" customHeight="1">
-      <c r="A233" s="10"/>
+      <c r="A233" s="8"/>
       <c r="B233" s="18"/>
       <c r="C233" s="18"/>
       <c r="D233" s="18"/>
@@ -8426,7 +8470,7 @@
       <c r="V233" s="20"/>
     </row>
     <row r="234" ht="19.5" customHeight="1">
-      <c r="A234" s="10"/>
+      <c r="A234" s="8"/>
       <c r="B234" s="18"/>
       <c r="C234" s="18"/>
       <c r="D234" s="18"/>
@@ -8450,7 +8494,7 @@
       <c r="V234" s="20"/>
     </row>
     <row r="235" ht="19.5" customHeight="1">
-      <c r="A235" s="10"/>
+      <c r="A235" s="8"/>
       <c r="B235" s="18"/>
       <c r="C235" s="18"/>
       <c r="D235" s="18"/>
@@ -8474,7 +8518,7 @@
       <c r="V235" s="20"/>
     </row>
     <row r="236" ht="19.5" customHeight="1">
-      <c r="A236" s="10"/>
+      <c r="A236" s="8"/>
       <c r="B236" s="18"/>
       <c r="C236" s="18"/>
       <c r="D236" s="18"/>
@@ -8498,7 +8542,7 @@
       <c r="V236" s="20"/>
     </row>
     <row r="237" ht="19.5" customHeight="1">
-      <c r="A237" s="10"/>
+      <c r="A237" s="8"/>
       <c r="B237" s="18"/>
       <c r="C237" s="18"/>
       <c r="D237" s="18"/>
@@ -8522,7 +8566,7 @@
       <c r="V237" s="20"/>
     </row>
     <row r="238" ht="19.5" customHeight="1">
-      <c r="A238" s="10"/>
+      <c r="A238" s="8"/>
       <c r="B238" s="18"/>
       <c r="C238" s="18"/>
       <c r="D238" s="18"/>
@@ -8546,7 +8590,7 @@
       <c r="V238" s="20"/>
     </row>
     <row r="239" ht="19.5" customHeight="1">
-      <c r="A239" s="10"/>
+      <c r="A239" s="8"/>
       <c r="B239" s="18"/>
       <c r="C239" s="18"/>
       <c r="D239" s="18"/>
@@ -8570,7 +8614,7 @@
       <c r="V239" s="20"/>
     </row>
     <row r="240" ht="19.5" customHeight="1">
-      <c r="A240" s="10"/>
+      <c r="A240" s="8"/>
       <c r="B240" s="18"/>
       <c r="C240" s="18"/>
       <c r="D240" s="18"/>
@@ -8594,7 +8638,7 @@
       <c r="V240" s="20"/>
     </row>
     <row r="241" ht="19.5" customHeight="1">
-      <c r="A241" s="10"/>
+      <c r="A241" s="8"/>
       <c r="B241" s="18"/>
       <c r="C241" s="18"/>
       <c r="D241" s="18"/>
@@ -8618,7 +8662,7 @@
       <c r="V241" s="20"/>
     </row>
     <row r="242" ht="19.5" customHeight="1">
-      <c r="A242" s="10"/>
+      <c r="A242" s="8"/>
       <c r="B242" s="18"/>
       <c r="C242" s="18"/>
       <c r="D242" s="18"/>
@@ -8642,7 +8686,7 @@
       <c r="V242" s="20"/>
     </row>
     <row r="243" ht="19.5" customHeight="1">
-      <c r="A243" s="10"/>
+      <c r="A243" s="8"/>
       <c r="B243" s="18"/>
       <c r="C243" s="18"/>
       <c r="D243" s="18"/>
@@ -8666,7 +8710,7 @@
       <c r="V243" s="20"/>
     </row>
     <row r="244" ht="19.5" customHeight="1">
-      <c r="A244" s="10"/>
+      <c r="A244" s="8"/>
       <c r="B244" s="18"/>
       <c r="C244" s="18"/>
       <c r="D244" s="18"/>
@@ -8690,7 +8734,7 @@
       <c r="V244" s="20"/>
     </row>
     <row r="245" ht="19.5" customHeight="1">
-      <c r="A245" s="10"/>
+      <c r="A245" s="8"/>
       <c r="B245" s="18"/>
       <c r="C245" s="18"/>
       <c r="D245" s="18"/>
@@ -8714,7 +8758,7 @@
       <c r="V245" s="20"/>
     </row>
     <row r="246" ht="19.5" customHeight="1">
-      <c r="A246" s="10"/>
+      <c r="A246" s="8"/>
       <c r="B246" s="18"/>
       <c r="C246" s="18"/>
       <c r="D246" s="18"/>
@@ -8738,7 +8782,7 @@
       <c r="V246" s="20"/>
     </row>
     <row r="247" ht="19.5" customHeight="1">
-      <c r="A247" s="10"/>
+      <c r="A247" s="8"/>
       <c r="B247" s="18"/>
       <c r="C247" s="18"/>
       <c r="D247" s="18"/>
@@ -8762,7 +8806,7 @@
       <c r="V247" s="20"/>
     </row>
     <row r="248" ht="19.5" customHeight="1">
-      <c r="A248" s="10"/>
+      <c r="A248" s="8"/>
       <c r="B248" s="18"/>
       <c r="C248" s="18"/>
       <c r="D248" s="18"/>
@@ -8786,7 +8830,7 @@
       <c r="V248" s="20"/>
     </row>
     <row r="249" ht="19.5" customHeight="1">
-      <c r="A249" s="10"/>
+      <c r="A249" s="8"/>
       <c r="B249" s="18"/>
       <c r="C249" s="18"/>
       <c r="D249" s="18"/>
@@ -8810,7 +8854,7 @@
       <c r="V249" s="20"/>
     </row>
     <row r="250" ht="19.5" customHeight="1">
-      <c r="A250" s="10"/>
+      <c r="A250" s="8"/>
       <c r="B250" s="18"/>
       <c r="C250" s="18"/>
       <c r="D250" s="18"/>
@@ -8834,7 +8878,7 @@
       <c r="V250" s="20"/>
     </row>
     <row r="251" ht="19.5" customHeight="1">
-      <c r="A251" s="10"/>
+      <c r="A251" s="8"/>
       <c r="B251" s="18"/>
       <c r="C251" s="18"/>
       <c r="D251" s="18"/>
@@ -8858,7 +8902,7 @@
       <c r="V251" s="20"/>
     </row>
     <row r="252" ht="19.5" customHeight="1">
-      <c r="A252" s="10"/>
+      <c r="A252" s="8"/>
       <c r="B252" s="18"/>
       <c r="C252" s="18"/>
       <c r="D252" s="18"/>
@@ -8882,7 +8926,7 @@
       <c r="V252" s="20"/>
     </row>
     <row r="253" ht="19.5" customHeight="1">
-      <c r="A253" s="10"/>
+      <c r="A253" s="8"/>
       <c r="B253" s="18"/>
       <c r="C253" s="18"/>
       <c r="D253" s="18"/>
@@ -8906,7 +8950,7 @@
       <c r="V253" s="20"/>
     </row>
     <row r="254" ht="19.5" customHeight="1">
-      <c r="A254" s="10"/>
+      <c r="A254" s="8"/>
       <c r="B254" s="18"/>
       <c r="C254" s="18"/>
       <c r="D254" s="18"/>
@@ -8930,7 +8974,7 @@
       <c r="V254" s="20"/>
     </row>
     <row r="255" ht="19.5" customHeight="1">
-      <c r="A255" s="10"/>
+      <c r="A255" s="8"/>
       <c r="B255" s="18"/>
       <c r="C255" s="18"/>
       <c r="D255" s="18"/>
@@ -8954,7 +8998,7 @@
       <c r="V255" s="20"/>
     </row>
     <row r="256" ht="19.5" customHeight="1">
-      <c r="A256" s="10"/>
+      <c r="A256" s="8"/>
       <c r="B256" s="18"/>
       <c r="C256" s="18"/>
       <c r="D256" s="18"/>
@@ -8978,7 +9022,7 @@
       <c r="V256" s="20"/>
     </row>
     <row r="257" ht="19.5" customHeight="1">
-      <c r="A257" s="10"/>
+      <c r="A257" s="8"/>
       <c r="B257" s="18"/>
       <c r="C257" s="18"/>
       <c r="D257" s="18"/>
@@ -9002,7 +9046,7 @@
       <c r="V257" s="20"/>
     </row>
     <row r="258" ht="19.5" customHeight="1">
-      <c r="A258" s="10"/>
+      <c r="A258" s="8"/>
       <c r="B258" s="18"/>
       <c r="C258" s="18"/>
       <c r="D258" s="18"/>
@@ -9026,7 +9070,7 @@
       <c r="V258" s="20"/>
     </row>
     <row r="259" ht="19.5" customHeight="1">
-      <c r="A259" s="10"/>
+      <c r="A259" s="8"/>
       <c r="B259" s="18"/>
       <c r="C259" s="18"/>
       <c r="D259" s="18"/>
@@ -9050,7 +9094,7 @@
       <c r="V259" s="20"/>
     </row>
     <row r="260" ht="19.5" customHeight="1">
-      <c r="A260" s="10"/>
+      <c r="A260" s="8"/>
       <c r="B260" s="18"/>
       <c r="C260" s="18"/>
       <c r="D260" s="18"/>
@@ -9074,7 +9118,7 @@
       <c r="V260" s="20"/>
     </row>
     <row r="261" ht="19.5" customHeight="1">
-      <c r="A261" s="10"/>
+      <c r="A261" s="8"/>
       <c r="B261" s="18"/>
       <c r="C261" s="18"/>
       <c r="D261" s="18"/>
@@ -9098,7 +9142,7 @@
       <c r="V261" s="20"/>
     </row>
     <row r="262" ht="19.5" customHeight="1">
-      <c r="A262" s="10"/>
+      <c r="A262" s="8"/>
       <c r="B262" s="18"/>
       <c r="C262" s="18"/>
       <c r="D262" s="18"/>
@@ -9122,7 +9166,7 @@
       <c r="V262" s="20"/>
     </row>
     <row r="263" ht="19.5" customHeight="1">
-      <c r="A263" s="10"/>
+      <c r="A263" s="8"/>
       <c r="B263" s="18"/>
       <c r="C263" s="18"/>
       <c r="D263" s="18"/>
@@ -9146,7 +9190,7 @@
       <c r="V263" s="20"/>
     </row>
     <row r="264" ht="19.5" customHeight="1">
-      <c r="A264" s="10"/>
+      <c r="A264" s="8"/>
       <c r="B264" s="18"/>
       <c r="C264" s="18"/>
       <c r="D264" s="18"/>
@@ -9170,7 +9214,7 @@
       <c r="V264" s="20"/>
     </row>
     <row r="265" ht="19.5" customHeight="1">
-      <c r="A265" s="10"/>
+      <c r="A265" s="8"/>
       <c r="B265" s="18"/>
       <c r="C265" s="18"/>
       <c r="D265" s="18"/>
@@ -9194,7 +9238,7 @@
       <c r="V265" s="20"/>
     </row>
     <row r="266" ht="19.5" customHeight="1">
-      <c r="A266" s="10"/>
+      <c r="A266" s="8"/>
       <c r="B266" s="18"/>
       <c r="C266" s="18"/>
       <c r="D266" s="18"/>
@@ -9218,7 +9262,7 @@
       <c r="V266" s="20"/>
     </row>
     <row r="267" ht="19.5" customHeight="1">
-      <c r="A267" s="10"/>
+      <c r="A267" s="8"/>
       <c r="B267" s="18"/>
       <c r="C267" s="18"/>
       <c r="D267" s="18"/>
@@ -9242,7 +9286,7 @@
       <c r="V267" s="20"/>
     </row>
     <row r="268" ht="19.5" customHeight="1">
-      <c r="A268" s="10"/>
+      <c r="A268" s="8"/>
       <c r="B268" s="18"/>
       <c r="C268" s="18"/>
       <c r="D268" s="18"/>
@@ -9266,7 +9310,7 @@
       <c r="V268" s="20"/>
     </row>
     <row r="269" ht="19.5" customHeight="1">
-      <c r="A269" s="10"/>
+      <c r="A269" s="8"/>
       <c r="B269" s="18"/>
       <c r="C269" s="18"/>
       <c r="D269" s="18"/>
@@ -9290,7 +9334,7 @@
       <c r="V269" s="20"/>
     </row>
     <row r="270" ht="19.5" customHeight="1">
-      <c r="A270" s="10"/>
+      <c r="A270" s="8"/>
       <c r="B270" s="18"/>
       <c r="C270" s="18"/>
       <c r="D270" s="18"/>
@@ -9314,7 +9358,7 @@
       <c r="V270" s="20"/>
     </row>
     <row r="271" ht="19.5" customHeight="1">
-      <c r="A271" s="10"/>
+      <c r="A271" s="8"/>
       <c r="B271" s="18"/>
       <c r="C271" s="18"/>
       <c r="D271" s="18"/>
@@ -9338,7 +9382,7 @@
       <c r="V271" s="20"/>
     </row>
     <row r="272" ht="19.5" customHeight="1">
-      <c r="A272" s="10"/>
+      <c r="A272" s="8"/>
       <c r="B272" s="18"/>
       <c r="C272" s="18"/>
       <c r="D272" s="18"/>
@@ -9362,7 +9406,7 @@
       <c r="V272" s="20"/>
     </row>
     <row r="273" ht="19.5" customHeight="1">
-      <c r="A273" s="10"/>
+      <c r="A273" s="8"/>
       <c r="B273" s="18"/>
       <c r="C273" s="18"/>
       <c r="D273" s="18"/>
@@ -9386,7 +9430,7 @@
       <c r="V273" s="20"/>
     </row>
     <row r="274" ht="19.5" customHeight="1">
-      <c r="A274" s="10"/>
+      <c r="A274" s="8"/>
       <c r="B274" s="18"/>
       <c r="C274" s="18"/>
       <c r="D274" s="18"/>
@@ -9410,7 +9454,7 @@
       <c r="V274" s="20"/>
     </row>
     <row r="275" ht="19.5" customHeight="1">
-      <c r="A275" s="10"/>
+      <c r="A275" s="8"/>
       <c r="B275" s="18"/>
       <c r="C275" s="18"/>
       <c r="D275" s="18"/>
@@ -9434,7 +9478,7 @@
       <c r="V275" s="20"/>
     </row>
     <row r="276" ht="19.5" customHeight="1">
-      <c r="A276" s="10"/>
+      <c r="A276" s="8"/>
       <c r="B276" s="18"/>
       <c r="C276" s="18"/>
       <c r="D276" s="18"/>
@@ -9458,7 +9502,7 @@
       <c r="V276" s="20"/>
     </row>
     <row r="277" ht="19.5" customHeight="1">
-      <c r="A277" s="10"/>
+      <c r="A277" s="8"/>
       <c r="B277" s="18"/>
       <c r="C277" s="18"/>
       <c r="D277" s="18"/>
@@ -9482,7 +9526,7 @@
       <c r="V277" s="20"/>
     </row>
     <row r="278" ht="19.5" customHeight="1">
-      <c r="A278" s="10"/>
+      <c r="A278" s="8"/>
       <c r="B278" s="18"/>
       <c r="C278" s="18"/>
       <c r="D278" s="18"/>
@@ -9506,7 +9550,7 @@
       <c r="V278" s="20"/>
     </row>
     <row r="279" ht="19.5" customHeight="1">
-      <c r="A279" s="10"/>
+      <c r="A279" s="8"/>
       <c r="B279" s="18"/>
       <c r="C279" s="18"/>
       <c r="D279" s="18"/>
@@ -9530,7 +9574,7 @@
       <c r="V279" s="20"/>
     </row>
     <row r="280" ht="19.5" customHeight="1">
-      <c r="A280" s="10"/>
+      <c r="A280" s="8"/>
       <c r="B280" s="18"/>
       <c r="C280" s="18"/>
       <c r="D280" s="18"/>
@@ -9554,7 +9598,7 @@
       <c r="V280" s="20"/>
     </row>
     <row r="281" ht="19.5" customHeight="1">
-      <c r="A281" s="10"/>
+      <c r="A281" s="8"/>
       <c r="B281" s="18"/>
       <c r="C281" s="18"/>
       <c r="D281" s="18"/>
@@ -9578,7 +9622,7 @@
       <c r="V281" s="20"/>
     </row>
     <row r="282" ht="19.5" customHeight="1">
-      <c r="A282" s="10"/>
+      <c r="A282" s="8"/>
       <c r="B282" s="18"/>
       <c r="C282" s="18"/>
       <c r="D282" s="18"/>
@@ -9602,7 +9646,7 @@
       <c r="V282" s="20"/>
     </row>
     <row r="283" ht="19.5" customHeight="1">
-      <c r="A283" s="10"/>
+      <c r="A283" s="8"/>
       <c r="B283" s="18"/>
       <c r="C283" s="18"/>
       <c r="D283" s="18"/>
@@ -9626,7 +9670,7 @@
       <c r="V283" s="20"/>
     </row>
     <row r="284" ht="19.5" customHeight="1">
-      <c r="A284" s="10"/>
+      <c r="A284" s="8"/>
       <c r="B284" s="18"/>
       <c r="C284" s="18"/>
       <c r="D284" s="18"/>
@@ -9650,7 +9694,7 @@
       <c r="V284" s="20"/>
     </row>
     <row r="285" ht="19.5" customHeight="1">
-      <c r="A285" s="10"/>
+      <c r="A285" s="8"/>
       <c r="B285" s="18"/>
       <c r="C285" s="18"/>
       <c r="D285" s="18"/>
@@ -9674,7 +9718,7 @@
       <c r="V285" s="20"/>
     </row>
     <row r="286" ht="19.5" customHeight="1">
-      <c r="A286" s="10"/>
+      <c r="A286" s="8"/>
       <c r="B286" s="18"/>
       <c r="C286" s="18"/>
       <c r="D286" s="18"/>
@@ -9698,7 +9742,7 @@
       <c r="V286" s="20"/>
     </row>
     <row r="287" ht="19.5" customHeight="1">
-      <c r="A287" s="10"/>
+      <c r="A287" s="8"/>
       <c r="B287" s="18"/>
       <c r="C287" s="18"/>
       <c r="D287" s="18"/>
@@ -9722,7 +9766,7 @@
       <c r="V287" s="20"/>
     </row>
     <row r="288" ht="19.5" customHeight="1">
-      <c r="A288" s="10"/>
+      <c r="A288" s="8"/>
       <c r="B288" s="18"/>
       <c r="C288" s="18"/>
       <c r="D288" s="18"/>
@@ -9746,7 +9790,7 @@
       <c r="V288" s="20"/>
     </row>
     <row r="289" ht="19.5" customHeight="1">
-      <c r="A289" s="10"/>
+      <c r="A289" s="8"/>
       <c r="B289" s="18"/>
       <c r="C289" s="18"/>
       <c r="D289" s="18"/>
@@ -9770,7 +9814,7 @@
       <c r="V289" s="20"/>
     </row>
     <row r="290" ht="19.5" customHeight="1">
-      <c r="A290" s="10"/>
+      <c r="A290" s="8"/>
       <c r="B290" s="18"/>
       <c r="C290" s="18"/>
       <c r="D290" s="18"/>
@@ -9794,7 +9838,7 @@
       <c r="V290" s="20"/>
     </row>
     <row r="291" ht="19.5" customHeight="1">
-      <c r="A291" s="10"/>
+      <c r="A291" s="8"/>
       <c r="B291" s="18"/>
       <c r="C291" s="18"/>
       <c r="D291" s="18"/>
@@ -9818,7 +9862,7 @@
       <c r="V291" s="20"/>
     </row>
     <row r="292" ht="19.5" customHeight="1">
-      <c r="A292" s="10"/>
+      <c r="A292" s="8"/>
       <c r="B292" s="18"/>
       <c r="C292" s="18"/>
       <c r="D292" s="18"/>
@@ -9842,7 +9886,7 @@
       <c r="V292" s="20"/>
     </row>
     <row r="293" ht="19.5" customHeight="1">
-      <c r="A293" s="10"/>
+      <c r="A293" s="8"/>
       <c r="B293" s="18"/>
       <c r="C293" s="18"/>
       <c r="D293" s="18"/>
@@ -9866,7 +9910,7 @@
       <c r="V293" s="20"/>
     </row>
     <row r="294" ht="19.5" customHeight="1">
-      <c r="A294" s="10"/>
+      <c r="A294" s="8"/>
       <c r="B294" s="18"/>
       <c r="C294" s="18"/>
       <c r="D294" s="18"/>
@@ -9890,7 +9934,7 @@
       <c r="V294" s="20"/>
     </row>
     <row r="295" ht="19.5" customHeight="1">
-      <c r="A295" s="10"/>
+      <c r="A295" s="8"/>
       <c r="B295" s="18"/>
       <c r="C295" s="18"/>
       <c r="D295" s="18"/>
@@ -9914,7 +9958,7 @@
       <c r="V295" s="20"/>
     </row>
     <row r="296" ht="19.5" customHeight="1">
-      <c r="A296" s="10"/>
+      <c r="A296" s="8"/>
       <c r="B296" s="18"/>
       <c r="C296" s="18"/>
       <c r="D296" s="18"/>
@@ -9938,7 +9982,7 @@
       <c r="V296" s="20"/>
     </row>
     <row r="297" ht="19.5" customHeight="1">
-      <c r="A297" s="10"/>
+      <c r="A297" s="8"/>
       <c r="B297" s="18"/>
       <c r="C297" s="18"/>
       <c r="D297" s="18"/>
@@ -9962,7 +10006,7 @@
       <c r="V297" s="20"/>
     </row>
     <row r="298" ht="19.5" customHeight="1">
-      <c r="A298" s="10"/>
+      <c r="A298" s="8"/>
       <c r="B298" s="18"/>
       <c r="C298" s="18"/>
       <c r="D298" s="18"/>
@@ -9986,7 +10030,7 @@
       <c r="V298" s="20"/>
     </row>
     <row r="299" ht="19.5" customHeight="1">
-      <c r="A299" s="10"/>
+      <c r="A299" s="8"/>
       <c r="B299" s="18"/>
       <c r="C299" s="18"/>
       <c r="D299" s="18"/>
@@ -10010,7 +10054,7 @@
       <c r="V299" s="20"/>
     </row>
     <row r="300" ht="19.5" customHeight="1">
-      <c r="A300" s="10"/>
+      <c r="A300" s="8"/>
       <c r="B300" s="18"/>
       <c r="C300" s="18"/>
       <c r="D300" s="18"/>
@@ -10034,7 +10078,7 @@
       <c r="V300" s="20"/>
     </row>
     <row r="301" ht="19.5" customHeight="1">
-      <c r="A301" s="10"/>
+      <c r="A301" s="8"/>
       <c r="B301" s="18"/>
       <c r="C301" s="18"/>
       <c r="D301" s="18"/>
@@ -10058,7 +10102,7 @@
       <c r="V301" s="20"/>
     </row>
     <row r="302" ht="19.5" customHeight="1">
-      <c r="A302" s="10"/>
+      <c r="A302" s="8"/>
       <c r="B302" s="18"/>
       <c r="C302" s="18"/>
       <c r="D302" s="18"/>
@@ -10082,7 +10126,7 @@
       <c r="V302" s="20"/>
     </row>
     <row r="303" ht="19.5" customHeight="1">
-      <c r="A303" s="10"/>
+      <c r="A303" s="8"/>
       <c r="B303" s="18"/>
       <c r="C303" s="18"/>
       <c r="D303" s="18"/>
@@ -10106,7 +10150,7 @@
       <c r="V303" s="20"/>
     </row>
     <row r="304" ht="19.5" customHeight="1">
-      <c r="A304" s="10"/>
+      <c r="A304" s="8"/>
       <c r="B304" s="18"/>
       <c r="C304" s="18"/>
       <c r="D304" s="18"/>
@@ -10130,7 +10174,7 @@
       <c r="V304" s="20"/>
     </row>
     <row r="305" ht="19.5" customHeight="1">
-      <c r="A305" s="10"/>
+      <c r="A305" s="8"/>
       <c r="B305" s="18"/>
       <c r="C305" s="18"/>
       <c r="D305" s="18"/>
@@ -10154,7 +10198,7 @@
       <c r="V305" s="20"/>
     </row>
     <row r="306" ht="19.5" customHeight="1">
-      <c r="A306" s="10"/>
+      <c r="A306" s="8"/>
       <c r="B306" s="18"/>
       <c r="C306" s="18"/>
       <c r="D306" s="18"/>
@@ -10178,7 +10222,7 @@
       <c r="V306" s="20"/>
     </row>
     <row r="307" ht="19.5" customHeight="1">
-      <c r="A307" s="10"/>
+      <c r="A307" s="8"/>
       <c r="B307" s="18"/>
       <c r="C307" s="18"/>
       <c r="D307" s="18"/>
@@ -10202,7 +10246,7 @@
       <c r="V307" s="20"/>
     </row>
     <row r="308" ht="19.5" customHeight="1">
-      <c r="A308" s="10"/>
+      <c r="A308" s="8"/>
       <c r="B308" s="18"/>
       <c r="C308" s="18"/>
       <c r="D308" s="18"/>
@@ -10226,7 +10270,7 @@
       <c r="V308" s="20"/>
     </row>
     <row r="309" ht="19.5" customHeight="1">
-      <c r="A309" s="10"/>
+      <c r="A309" s="8"/>
       <c r="B309" s="18"/>
       <c r="C309" s="18"/>
       <c r="D309" s="18"/>
@@ -10250,7 +10294,7 @@
       <c r="V309" s="20"/>
     </row>
     <row r="310" ht="19.5" customHeight="1">
-      <c r="A310" s="10"/>
+      <c r="A310" s="8"/>
       <c r="B310" s="18"/>
       <c r="C310" s="18"/>
       <c r="D310" s="18"/>
@@ -10274,7 +10318,7 @@
       <c r="V310" s="20"/>
     </row>
     <row r="311" ht="19.5" customHeight="1">
-      <c r="A311" s="10"/>
+      <c r="A311" s="8"/>
       <c r="B311" s="18"/>
       <c r="C311" s="18"/>
       <c r="D311" s="18"/>
@@ -10298,7 +10342,7 @@
       <c r="V311" s="20"/>
     </row>
     <row r="312" ht="19.5" customHeight="1">
-      <c r="A312" s="10"/>
+      <c r="A312" s="8"/>
       <c r="B312" s="18"/>
       <c r="C312" s="18"/>
       <c r="D312" s="18"/>
@@ -10322,7 +10366,7 @@
       <c r="V312" s="20"/>
     </row>
     <row r="313" ht="19.5" customHeight="1">
-      <c r="A313" s="10"/>
+      <c r="A313" s="8"/>
       <c r="B313" s="18"/>
       <c r="C313" s="18"/>
       <c r="D313" s="18"/>
@@ -10346,7 +10390,7 @@
       <c r="V313" s="20"/>
     </row>
     <row r="314" ht="19.5" customHeight="1">
-      <c r="A314" s="10"/>
+      <c r="A314" s="8"/>
       <c r="B314" s="18"/>
       <c r="C314" s="18"/>
       <c r="D314" s="18"/>
@@ -10370,7 +10414,7 @@
       <c r="V314" s="20"/>
     </row>
     <row r="315" ht="19.5" customHeight="1">
-      <c r="A315" s="10"/>
+      <c r="A315" s="8"/>
       <c r="B315" s="18"/>
       <c r="C315" s="18"/>
       <c r="D315" s="18"/>
@@ -10394,7 +10438,7 @@
       <c r="V315" s="20"/>
     </row>
     <row r="316" ht="19.5" customHeight="1">
-      <c r="A316" s="10"/>
+      <c r="A316" s="8"/>
       <c r="B316" s="18"/>
       <c r="C316" s="18"/>
       <c r="D316" s="18"/>
@@ -10418,7 +10462,7 @@
       <c r="V316" s="20"/>
     </row>
     <row r="317" ht="19.5" customHeight="1">
-      <c r="A317" s="10"/>
+      <c r="A317" s="8"/>
       <c r="B317" s="18"/>
       <c r="C317" s="18"/>
       <c r="D317" s="18"/>
@@ -10442,7 +10486,7 @@
       <c r="V317" s="20"/>
     </row>
     <row r="318" ht="19.5" customHeight="1">
-      <c r="A318" s="10"/>
+      <c r="A318" s="8"/>
       <c r="B318" s="18"/>
       <c r="C318" s="18"/>
       <c r="D318" s="18"/>
@@ -10466,7 +10510,7 @@
       <c r="V318" s="20"/>
     </row>
     <row r="319" ht="19.5" customHeight="1">
-      <c r="A319" s="10"/>
+      <c r="A319" s="8"/>
       <c r="B319" s="18"/>
       <c r="C319" s="18"/>
       <c r="D319" s="18"/>
@@ -10490,7 +10534,7 @@
       <c r="V319" s="20"/>
     </row>
     <row r="320" ht="19.5" customHeight="1">
-      <c r="A320" s="10"/>
+      <c r="A320" s="8"/>
       <c r="B320" s="18"/>
       <c r="C320" s="18"/>
       <c r="D320" s="18"/>
@@ -10514,7 +10558,7 @@
       <c r="V320" s="20"/>
     </row>
     <row r="321" ht="19.5" customHeight="1">
-      <c r="A321" s="10"/>
+      <c r="A321" s="8"/>
       <c r="B321" s="18"/>
       <c r="C321" s="18"/>
       <c r="D321" s="18"/>
@@ -10538,7 +10582,7 @@
       <c r="V321" s="20"/>
     </row>
     <row r="322" ht="19.5" customHeight="1">
-      <c r="A322" s="10"/>
+      <c r="A322" s="8"/>
       <c r="B322" s="18"/>
       <c r="C322" s="18"/>
       <c r="D322" s="18"/>
@@ -10562,7 +10606,7 @@
       <c r="V322" s="20"/>
     </row>
     <row r="323" ht="19.5" customHeight="1">
-      <c r="A323" s="10"/>
+      <c r="A323" s="8"/>
       <c r="B323" s="18"/>
       <c r="C323" s="18"/>
       <c r="D323" s="18"/>
@@ -10586,7 +10630,7 @@
       <c r="V323" s="20"/>
     </row>
     <row r="324" ht="19.5" customHeight="1">
-      <c r="A324" s="10"/>
+      <c r="A324" s="8"/>
       <c r="B324" s="18"/>
       <c r="C324" s="18"/>
       <c r="D324" s="18"/>
@@ -10610,7 +10654,7 @@
       <c r="V324" s="20"/>
     </row>
     <row r="325" ht="19.5" customHeight="1">
-      <c r="A325" s="10"/>
+      <c r="A325" s="8"/>
       <c r="B325" s="18"/>
       <c r="C325" s="18"/>
       <c r="D325" s="18"/>
@@ -10634,7 +10678,7 @@
       <c r="V325" s="20"/>
     </row>
     <row r="326" ht="19.5" customHeight="1">
-      <c r="A326" s="10"/>
+      <c r="A326" s="8"/>
       <c r="B326" s="18"/>
       <c r="C326" s="18"/>
       <c r="D326" s="18"/>
@@ -10658,7 +10702,7 @@
       <c r="V326" s="20"/>
     </row>
     <row r="327" ht="19.5" customHeight="1">
-      <c r="A327" s="10"/>
+      <c r="A327" s="8"/>
       <c r="B327" s="18"/>
       <c r="C327" s="18"/>
       <c r="D327" s="18"/>
@@ -10682,7 +10726,7 @@
       <c r="V327" s="20"/>
     </row>
     <row r="328" ht="19.5" customHeight="1">
-      <c r="A328" s="10"/>
+      <c r="A328" s="8"/>
       <c r="B328" s="18"/>
       <c r="C328" s="18"/>
       <c r="D328" s="18"/>
@@ -10706,7 +10750,7 @@
       <c r="V328" s="20"/>
     </row>
     <row r="329" ht="19.5" customHeight="1">
-      <c r="A329" s="10"/>
+      <c r="A329" s="8"/>
       <c r="B329" s="18"/>
       <c r="C329" s="18"/>
       <c r="D329" s="18"/>
@@ -10730,7 +10774,7 @@
       <c r="V329" s="20"/>
     </row>
     <row r="330" ht="19.5" customHeight="1">
-      <c r="A330" s="10"/>
+      <c r="A330" s="8"/>
       <c r="B330" s="18"/>
       <c r="C330" s="18"/>
       <c r="D330" s="18"/>
@@ -10754,7 +10798,7 @@
       <c r="V330" s="20"/>
     </row>
     <row r="331" ht="19.5" customHeight="1">
-      <c r="A331" s="10"/>
+      <c r="A331" s="8"/>
       <c r="B331" s="18"/>
       <c r="C331" s="18"/>
       <c r="D331" s="18"/>
@@ -10778,7 +10822,7 @@
       <c r="V331" s="20"/>
     </row>
     <row r="332" ht="19.5" customHeight="1">
-      <c r="A332" s="10"/>
+      <c r="A332" s="8"/>
       <c r="B332" s="18"/>
       <c r="C332" s="18"/>
       <c r="D332" s="18"/>
@@ -10802,7 +10846,7 @@
       <c r="V332" s="20"/>
     </row>
     <row r="333" ht="19.5" customHeight="1">
-      <c r="A333" s="10"/>
+      <c r="A333" s="8"/>
       <c r="B333" s="18"/>
       <c r="C333" s="18"/>
       <c r="D333" s="18"/>
@@ -10826,7 +10870,7 @@
       <c r="V333" s="20"/>
     </row>
     <row r="334" ht="19.5" customHeight="1">
-      <c r="A334" s="10"/>
+      <c r="A334" s="8"/>
       <c r="B334" s="18"/>
       <c r="C334" s="18"/>
       <c r="D334" s="18"/>
@@ -10850,7 +10894,7 @@
       <c r="V334" s="20"/>
     </row>
     <row r="335" ht="19.5" customHeight="1">
-      <c r="A335" s="10"/>
+      <c r="A335" s="8"/>
       <c r="B335" s="18"/>
       <c r="C335" s="18"/>
       <c r="D335" s="18"/>
@@ -10874,7 +10918,7 @@
       <c r="V335" s="20"/>
     </row>
     <row r="336" ht="19.5" customHeight="1">
-      <c r="A336" s="10"/>
+      <c r="A336" s="8"/>
       <c r="B336" s="18"/>
       <c r="C336" s="18"/>
       <c r="D336" s="18"/>
@@ -10898,7 +10942,7 @@
       <c r="V336" s="20"/>
     </row>
     <row r="337" ht="19.5" customHeight="1">
-      <c r="A337" s="10"/>
+      <c r="A337" s="8"/>
       <c r="B337" s="18"/>
       <c r="C337" s="18"/>
       <c r="D337" s="18"/>
@@ -10922,7 +10966,7 @@
       <c r="V337" s="20"/>
     </row>
     <row r="338" ht="19.5" customHeight="1">
-      <c r="A338" s="10"/>
+      <c r="A338" s="8"/>
       <c r="B338" s="18"/>
       <c r="C338" s="18"/>
       <c r="D338" s="18"/>
@@ -10946,7 +10990,7 @@
       <c r="V338" s="20"/>
     </row>
     <row r="339" ht="19.5" customHeight="1">
-      <c r="A339" s="10"/>
+      <c r="A339" s="8"/>
       <c r="B339" s="18"/>
       <c r="C339" s="18"/>
       <c r="D339" s="18"/>
@@ -10970,7 +11014,7 @@
       <c r="V339" s="20"/>
     </row>
     <row r="340" ht="19.5" customHeight="1">
-      <c r="A340" s="10"/>
+      <c r="A340" s="8"/>
       <c r="B340" s="18"/>
       <c r="C340" s="18"/>
       <c r="D340" s="18"/>
@@ -10994,7 +11038,7 @@
       <c r="V340" s="20"/>
     </row>
     <row r="341" ht="19.5" customHeight="1">
-      <c r="A341" s="10"/>
+      <c r="A341" s="8"/>
       <c r="B341" s="18"/>
       <c r="C341" s="18"/>
       <c r="D341" s="18"/>
@@ -11018,7 +11062,7 @@
       <c r="V341" s="20"/>
     </row>
     <row r="342" ht="19.5" customHeight="1">
-      <c r="A342" s="10"/>
+      <c r="A342" s="8"/>
       <c r="B342" s="18"/>
       <c r="C342" s="18"/>
       <c r="D342" s="18"/>
@@ -11042,7 +11086,7 @@
       <c r="V342" s="20"/>
     </row>
     <row r="343" ht="19.5" customHeight="1">
-      <c r="A343" s="10"/>
+      <c r="A343" s="8"/>
       <c r="B343" s="18"/>
       <c r="C343" s="18"/>
       <c r="D343" s="18"/>
@@ -11066,7 +11110,7 @@
       <c r="V343" s="20"/>
     </row>
     <row r="344" ht="19.5" customHeight="1">
-      <c r="A344" s="10"/>
+      <c r="A344" s="8"/>
       <c r="B344" s="18"/>
       <c r="C344" s="18"/>
       <c r="D344" s="18"/>
@@ -11090,7 +11134,7 @@
       <c r="V344" s="20"/>
     </row>
     <row r="345" ht="19.5" customHeight="1">
-      <c r="A345" s="10"/>
+      <c r="A345" s="8"/>
       <c r="B345" s="18"/>
       <c r="C345" s="18"/>
       <c r="D345" s="18"/>
@@ -11114,7 +11158,7 @@
       <c r="V345" s="20"/>
     </row>
     <row r="346" ht="19.5" customHeight="1">
-      <c r="A346" s="10"/>
+      <c r="A346" s="8"/>
       <c r="B346" s="18"/>
       <c r="C346" s="18"/>
       <c r="D346" s="18"/>
@@ -11138,7 +11182,7 @@
       <c r="V346" s="20"/>
     </row>
     <row r="347" ht="19.5" customHeight="1">
-      <c r="A347" s="10"/>
+      <c r="A347" s="8"/>
       <c r="B347" s="18"/>
       <c r="C347" s="18"/>
       <c r="D347" s="18"/>
@@ -11162,7 +11206,7 @@
       <c r="V347" s="20"/>
     </row>
     <row r="348" ht="19.5" customHeight="1">
-      <c r="A348" s="10"/>
+      <c r="A348" s="8"/>
       <c r="B348" s="18"/>
       <c r="C348" s="18"/>
       <c r="D348" s="18"/>
@@ -11186,7 +11230,7 @@
       <c r="V348" s="20"/>
     </row>
     <row r="349" ht="19.5" customHeight="1">
-      <c r="A349" s="10"/>
+      <c r="A349" s="8"/>
       <c r="B349" s="18"/>
       <c r="C349" s="18"/>
       <c r="D349" s="18"/>
@@ -11210,7 +11254,7 @@
       <c r="V349" s="20"/>
     </row>
     <row r="350" ht="19.5" customHeight="1">
-      <c r="A350" s="10"/>
+      <c r="A350" s="8"/>
       <c r="B350" s="18"/>
       <c r="C350" s="18"/>
       <c r="D350" s="18"/>
@@ -11234,7 +11278,7 @@
       <c r="V350" s="20"/>
     </row>
     <row r="351" ht="19.5" customHeight="1">
-      <c r="A351" s="10"/>
+      <c r="A351" s="8"/>
       <c r="B351" s="18"/>
       <c r="C351" s="18"/>
       <c r="D351" s="18"/>
@@ -11258,7 +11302,7 @@
       <c r="V351" s="20"/>
     </row>
     <row r="352" ht="19.5" customHeight="1">
-      <c r="A352" s="10"/>
+      <c r="A352" s="8"/>
       <c r="B352" s="18"/>
       <c r="C352" s="18"/>
       <c r="D352" s="18"/>
@@ -11282,7 +11326,7 @@
       <c r="V352" s="20"/>
     </row>
     <row r="353" ht="19.5" customHeight="1">
-      <c r="A353" s="10"/>
+      <c r="A353" s="8"/>
       <c r="B353" s="18"/>
       <c r="C353" s="18"/>
       <c r="D353" s="18"/>
@@ -11306,7 +11350,7 @@
       <c r="V353" s="20"/>
     </row>
     <row r="354" ht="19.5" customHeight="1">
-      <c r="A354" s="10"/>
+      <c r="A354" s="8"/>
       <c r="B354" s="18"/>
       <c r="C354" s="18"/>
       <c r="D354" s="18"/>
@@ -11330,7 +11374,7 @@
       <c r="V354" s="20"/>
     </row>
     <row r="355" ht="19.5" customHeight="1">
-      <c r="A355" s="10"/>
+      <c r="A355" s="8"/>
       <c r="B355" s="18"/>
       <c r="C355" s="18"/>
       <c r="D355" s="18"/>
@@ -11354,7 +11398,7 @@
       <c r="V355" s="20"/>
     </row>
     <row r="356" ht="19.5" customHeight="1">
-      <c r="A356" s="10"/>
+      <c r="A356" s="8"/>
       <c r="B356" s="18"/>
       <c r="C356" s="18"/>
       <c r="D356" s="18"/>
@@ -11378,7 +11422,7 @@
       <c r="V356" s="20"/>
     </row>
     <row r="357" ht="19.5" customHeight="1">
-      <c r="A357" s="10"/>
+      <c r="A357" s="8"/>
       <c r="B357" s="18"/>
       <c r="C357" s="18"/>
       <c r="D357" s="18"/>
@@ -11402,7 +11446,7 @@
       <c r="V357" s="20"/>
     </row>
     <row r="358" ht="19.5" customHeight="1">
-      <c r="A358" s="10"/>
+      <c r="A358" s="8"/>
       <c r="B358" s="18"/>
       <c r="C358" s="18"/>
       <c r="D358" s="18"/>
@@ -11426,7 +11470,7 @@
       <c r="V358" s="20"/>
     </row>
     <row r="359" ht="19.5" customHeight="1">
-      <c r="A359" s="10"/>
+      <c r="A359" s="8"/>
       <c r="B359" s="18"/>
       <c r="C359" s="18"/>
       <c r="D359" s="18"/>
@@ -11450,7 +11494,7 @@
       <c r="V359" s="20"/>
     </row>
     <row r="360" ht="19.5" customHeight="1">
-      <c r="A360" s="10"/>
+      <c r="A360" s="8"/>
       <c r="B360" s="18"/>
       <c r="C360" s="18"/>
       <c r="D360" s="18"/>
@@ -11474,7 +11518,7 @@
       <c r="V360" s="20"/>
     </row>
     <row r="361" ht="19.5" customHeight="1">
-      <c r="A361" s="10"/>
+      <c r="A361" s="8"/>
       <c r="B361" s="18"/>
       <c r="C361" s="18"/>
       <c r="D361" s="18"/>
@@ -11498,7 +11542,7 @@
       <c r="V361" s="20"/>
     </row>
     <row r="362" ht="19.5" customHeight="1">
-      <c r="A362" s="10"/>
+      <c r="A362" s="8"/>
       <c r="B362" s="18"/>
       <c r="C362" s="18"/>
       <c r="D362" s="18"/>
@@ -11522,7 +11566,7 @@
       <c r="V362" s="20"/>
     </row>
     <row r="363" ht="19.5" customHeight="1">
-      <c r="A363" s="10"/>
+      <c r="A363" s="8"/>
       <c r="B363" s="18"/>
       <c r="C363" s="18"/>
       <c r="D363" s="18"/>
@@ -11546,7 +11590,7 @@
       <c r="V363" s="20"/>
     </row>
     <row r="364" ht="19.5" customHeight="1">
-      <c r="A364" s="10"/>
+      <c r="A364" s="8"/>
       <c r="B364" s="18"/>
       <c r="C364" s="18"/>
       <c r="D364" s="18"/>
@@ -11570,7 +11614,7 @@
       <c r="V364" s="20"/>
     </row>
     <row r="365" ht="19.5" customHeight="1">
-      <c r="A365" s="10"/>
+      <c r="A365" s="8"/>
       <c r="B365" s="18"/>
       <c r="C365" s="18"/>
       <c r="D365" s="18"/>
@@ -11594,7 +11638,7 @@
       <c r="V365" s="20"/>
     </row>
     <row r="366" ht="19.5" customHeight="1">
-      <c r="A366" s="10"/>
+      <c r="A366" s="8"/>
       <c r="B366" s="18"/>
       <c r="C366" s="18"/>
       <c r="D366" s="18"/>
@@ -11618,7 +11662,7 @@
       <c r="V366" s="20"/>
     </row>
     <row r="367" ht="19.5" customHeight="1">
-      <c r="A367" s="10"/>
+      <c r="A367" s="8"/>
       <c r="B367" s="18"/>
       <c r="C367" s="18"/>
       <c r="D367" s="18"/>
@@ -11642,7 +11686,7 @@
       <c r="V367" s="20"/>
     </row>
     <row r="368" ht="19.5" customHeight="1">
-      <c r="A368" s="10"/>
+      <c r="A368" s="8"/>
       <c r="B368" s="18"/>
       <c r="C368" s="18"/>
       <c r="D368" s="18"/>
@@ -11666,7 +11710,7 @@
       <c r="V368" s="20"/>
     </row>
     <row r="369" ht="19.5" customHeight="1">
-      <c r="A369" s="10"/>
+      <c r="A369" s="8"/>
       <c r="B369" s="18"/>
       <c r="C369" s="18"/>
       <c r="D369" s="18"/>
@@ -11690,7 +11734,7 @@
       <c r="V369" s="20"/>
     </row>
     <row r="370" ht="19.5" customHeight="1">
-      <c r="A370" s="10"/>
+      <c r="A370" s="8"/>
       <c r="B370" s="18"/>
       <c r="C370" s="18"/>
       <c r="D370" s="18"/>
@@ -11714,7 +11758,7 @@
       <c r="V370" s="20"/>
     </row>
     <row r="371" ht="19.5" customHeight="1">
-      <c r="A371" s="10"/>
+      <c r="A371" s="8"/>
       <c r="B371" s="18"/>
       <c r="C371" s="18"/>
       <c r="D371" s="18"/>
@@ -11738,7 +11782,7 @@
       <c r="V371" s="20"/>
     </row>
     <row r="372" ht="19.5" customHeight="1">
-      <c r="A372" s="10"/>
+      <c r="A372" s="8"/>
       <c r="B372" s="18"/>
       <c r="C372" s="18"/>
       <c r="D372" s="18"/>
@@ -11762,7 +11806,7 @@
       <c r="V372" s="20"/>
     </row>
     <row r="373" ht="19.5" customHeight="1">
-      <c r="A373" s="10"/>
+      <c r="A373" s="8"/>
       <c r="B373" s="18"/>
       <c r="C373" s="18"/>
       <c r="D373" s="18"/>
@@ -11786,7 +11830,7 @@
       <c r="V373" s="20"/>
     </row>
     <row r="374" ht="19.5" customHeight="1">
-      <c r="A374" s="10"/>
+      <c r="A374" s="8"/>
       <c r="B374" s="18"/>
       <c r="C374" s="18"/>
       <c r="D374" s="18"/>
@@ -11810,7 +11854,7 @@
       <c r="V374" s="20"/>
     </row>
     <row r="375" ht="19.5" customHeight="1">
-      <c r="A375" s="10"/>
+      <c r="A375" s="8"/>
       <c r="B375" s="18"/>
       <c r="C375" s="18"/>
       <c r="D375" s="18"/>
@@ -11834,7 +11878,7 @@
       <c r="V375" s="20"/>
     </row>
     <row r="376" ht="19.5" customHeight="1">
-      <c r="A376" s="10"/>
+      <c r="A376" s="8"/>
       <c r="B376" s="18"/>
       <c r="C376" s="18"/>
       <c r="D376" s="18"/>
@@ -11858,7 +11902,7 @@
       <c r="V376" s="20"/>
     </row>
     <row r="377" ht="19.5" customHeight="1">
-      <c r="A377" s="10"/>
+      <c r="A377" s="8"/>
       <c r="B377" s="18"/>
       <c r="C377" s="18"/>
       <c r="D377" s="18"/>
@@ -11882,7 +11926,7 @@
       <c r="V377" s="20"/>
     </row>
     <row r="378" ht="19.5" customHeight="1">
-      <c r="A378" s="10"/>
+      <c r="A378" s="8"/>
       <c r="B378" s="18"/>
       <c r="C378" s="18"/>
       <c r="D378" s="18"/>
@@ -11906,7 +11950,7 @@
       <c r="V378" s="20"/>
     </row>
     <row r="379" ht="19.5" customHeight="1">
-      <c r="A379" s="10"/>
+      <c r="A379" s="8"/>
       <c r="B379" s="18"/>
       <c r="C379" s="18"/>
       <c r="D379" s="18"/>
@@ -11930,7 +11974,7 @@
       <c r="V379" s="20"/>
     </row>
     <row r="380" ht="19.5" customHeight="1">
-      <c r="A380" s="10"/>
+      <c r="A380" s="8"/>
       <c r="B380" s="18"/>
       <c r="C380" s="18"/>
       <c r="D380" s="18"/>
@@ -11954,7 +11998,7 @@
       <c r="V380" s="20"/>
     </row>
     <row r="381" ht="19.5" customHeight="1">
-      <c r="A381" s="10"/>
+      <c r="A381" s="8"/>
       <c r="B381" s="18"/>
       <c r="C381" s="18"/>
       <c r="D381" s="18"/>
@@ -11978,7 +12022,7 @@
       <c r="V381" s="20"/>
     </row>
     <row r="382" ht="19.5" customHeight="1">
-      <c r="A382" s="10"/>
+      <c r="A382" s="8"/>
       <c r="B382" s="18"/>
       <c r="C382" s="18"/>
       <c r="D382" s="18"/>
@@ -12002,7 +12046,7 @@
       <c r="V382" s="20"/>
     </row>
     <row r="383" ht="19.5" customHeight="1">
-      <c r="A383" s="10"/>
+      <c r="A383" s="8"/>
       <c r="B383" s="18"/>
       <c r="C383" s="18"/>
       <c r="D383" s="18"/>
@@ -12026,7 +12070,7 @@
       <c r="V383" s="20"/>
     </row>
     <row r="384" ht="19.5" customHeight="1">
-      <c r="A384" s="10"/>
+      <c r="A384" s="8"/>
       <c r="B384" s="18"/>
       <c r="C384" s="18"/>
       <c r="D384" s="18"/>
@@ -12050,7 +12094,7 @@
       <c r="V384" s="20"/>
     </row>
     <row r="385" ht="19.5" customHeight="1">
-      <c r="A385" s="10"/>
+      <c r="A385" s="8"/>
       <c r="B385" s="18"/>
       <c r="C385" s="18"/>
       <c r="D385" s="18"/>
@@ -12074,7 +12118,7 @@
       <c r="V385" s="20"/>
     </row>
     <row r="386" ht="19.5" customHeight="1">
-      <c r="A386" s="10"/>
+      <c r="A386" s="8"/>
       <c r="B386" s="18"/>
       <c r="C386" s="18"/>
       <c r="D386" s="18"/>
@@ -12098,7 +12142,7 @@
       <c r="V386" s="20"/>
     </row>
     <row r="387" ht="19.5" customHeight="1">
-      <c r="A387" s="10"/>
+      <c r="A387" s="8"/>
       <c r="B387" s="18"/>
       <c r="C387" s="18"/>
       <c r="D387" s="18"/>
@@ -12122,7 +12166,7 @@
       <c r="V387" s="20"/>
     </row>
     <row r="388" ht="19.5" customHeight="1">
-      <c r="A388" s="10"/>
+      <c r="A388" s="8"/>
       <c r="B388" s="18"/>
       <c r="C388" s="18"/>
       <c r="D388" s="18"/>
@@ -12146,7 +12190,7 @@
       <c r="V388" s="20"/>
     </row>
     <row r="389" ht="19.5" customHeight="1">
-      <c r="A389" s="10"/>
+      <c r="A389" s="8"/>
       <c r="B389" s="18"/>
       <c r="C389" s="18"/>
       <c r="D389" s="18"/>
@@ -12170,7 +12214,7 @@
       <c r="V389" s="20"/>
     </row>
     <row r="390" ht="19.5" customHeight="1">
-      <c r="A390" s="10"/>
+      <c r="A390" s="8"/>
       <c r="B390" s="18"/>
       <c r="C390" s="18"/>
       <c r="D390" s="18"/>
@@ -12194,7 +12238,7 @@
       <c r="V390" s="20"/>
     </row>
     <row r="391" ht="19.5" customHeight="1">
-      <c r="A391" s="10"/>
+      <c r="A391" s="8"/>
       <c r="B391" s="18"/>
       <c r="C391" s="18"/>
       <c r="D391" s="18"/>
@@ -12218,7 +12262,7 @@
       <c r="V391" s="20"/>
     </row>
     <row r="392" ht="19.5" customHeight="1">
-      <c r="A392" s="10"/>
+      <c r="A392" s="8"/>
       <c r="B392" s="18"/>
       <c r="C392" s="18"/>
       <c r="D392" s="18"/>
@@ -12242,7 +12286,7 @@
       <c r="V392" s="20"/>
     </row>
     <row r="393" ht="19.5" customHeight="1">
-      <c r="A393" s="10"/>
+      <c r="A393" s="8"/>
       <c r="B393" s="18"/>
       <c r="C393" s="18"/>
       <c r="D393" s="18"/>
@@ -12266,7 +12310,7 @@
       <c r="V393" s="20"/>
     </row>
     <row r="394" ht="19.5" customHeight="1">
-      <c r="A394" s="10"/>
+      <c r="A394" s="8"/>
       <c r="B394" s="18"/>
       <c r="C394" s="18"/>
       <c r="D394" s="18"/>
@@ -12290,7 +12334,7 @@
       <c r="V394" s="20"/>
     </row>
     <row r="395" ht="19.5" customHeight="1">
-      <c r="A395" s="10"/>
+      <c r="A395" s="8"/>
       <c r="B395" s="18"/>
       <c r="C395" s="18"/>
       <c r="D395" s="18"/>
@@ -12314,7 +12358,7 @@
       <c r="V395" s="20"/>
     </row>
     <row r="396" ht="19.5" customHeight="1">
-      <c r="A396" s="10"/>
+      <c r="A396" s="8"/>
       <c r="B396" s="18"/>
       <c r="C396" s="18"/>
       <c r="D396" s="18"/>
@@ -12338,7 +12382,7 @@
       <c r="V396" s="20"/>
     </row>
     <row r="397" ht="19.5" customHeight="1">
-      <c r="A397" s="10"/>
+      <c r="A397" s="8"/>
       <c r="B397" s="18"/>
       <c r="C397" s="18"/>
       <c r="D397" s="18"/>
@@ -12362,7 +12406,7 @@
       <c r="V397" s="20"/>
     </row>
     <row r="398" ht="19.5" customHeight="1">
-      <c r="A398" s="10"/>
+      <c r="A398" s="8"/>
       <c r="B398" s="18"/>
       <c r="C398" s="18"/>
       <c r="D398" s="18"/>
@@ -12386,7 +12430,7 @@
       <c r="V398" s="20"/>
     </row>
     <row r="399" ht="19.5" customHeight="1">
-      <c r="A399" s="10"/>
+      <c r="A399" s="8"/>
       <c r="B399" s="18"/>
       <c r="C399" s="18"/>
       <c r="D399" s="18"/>
@@ -12410,7 +12454,7 @@
       <c r="V399" s="20"/>
     </row>
     <row r="400" ht="19.5" customHeight="1">
-      <c r="A400" s="10"/>
+      <c r="A400" s="8"/>
       <c r="B400" s="18"/>
       <c r="C400" s="18"/>
       <c r="D400" s="18"/>
@@ -12434,7 +12478,7 @@
       <c r="V400" s="20"/>
     </row>
     <row r="401" ht="19.5" customHeight="1">
-      <c r="A401" s="10"/>
+      <c r="A401" s="8"/>
       <c r="B401" s="18"/>
       <c r="C401" s="18"/>
       <c r="D401" s="18"/>
@@ -12458,7 +12502,7 @@
       <c r="V401" s="20"/>
     </row>
     <row r="402" ht="19.5" customHeight="1">
-      <c r="A402" s="10"/>
+      <c r="A402" s="8"/>
       <c r="B402" s="18"/>
       <c r="C402" s="18"/>
       <c r="D402" s="18"/>
@@ -12482,7 +12526,7 @@
       <c r="V402" s="20"/>
     </row>
     <row r="403" ht="19.5" customHeight="1">
-      <c r="A403" s="10"/>
+      <c r="A403" s="8"/>
       <c r="B403" s="18"/>
       <c r="C403" s="18"/>
       <c r="D403" s="18"/>
@@ -12506,7 +12550,7 @@
       <c r="V403" s="20"/>
     </row>
     <row r="404" ht="19.5" customHeight="1">
-      <c r="A404" s="10"/>
+      <c r="A404" s="8"/>
       <c r="B404" s="18"/>
       <c r="C404" s="18"/>
       <c r="D404" s="18"/>
@@ -12530,7 +12574,7 @@
       <c r="V404" s="20"/>
     </row>
     <row r="405" ht="19.5" customHeight="1">
-      <c r="A405" s="10"/>
+      <c r="A405" s="8"/>
       <c r="B405" s="18"/>
       <c r="C405" s="18"/>
       <c r="D405" s="18"/>
@@ -12554,7 +12598,7 @@
       <c r="V405" s="20"/>
     </row>
     <row r="406" ht="19.5" customHeight="1">
-      <c r="A406" s="10"/>
+      <c r="A406" s="8"/>
       <c r="B406" s="18"/>
       <c r="C406" s="18"/>
       <c r="D406" s="18"/>
@@ -12578,7 +12622,7 @@
       <c r="V406" s="20"/>
     </row>
     <row r="407" ht="19.5" customHeight="1">
-      <c r="A407" s="10"/>
+      <c r="A407" s="8"/>
       <c r="B407" s="18"/>
       <c r="C407" s="18"/>
       <c r="D407" s="18"/>
@@ -12602,7 +12646,7 @@
       <c r="V407" s="20"/>
     </row>
     <row r="408" ht="19.5" customHeight="1">
-      <c r="A408" s="10"/>
+      <c r="A408" s="8"/>
       <c r="B408" s="18"/>
       <c r="C408" s="18"/>
       <c r="D408" s="18"/>
@@ -12626,7 +12670,7 @@
       <c r="V408" s="20"/>
     </row>
     <row r="409" ht="19.5" customHeight="1">
-      <c r="A409" s="10"/>
+      <c r="A409" s="8"/>
       <c r="B409" s="18"/>
       <c r="C409" s="18"/>
       <c r="D409" s="18"/>
@@ -12650,7 +12694,7 @@
       <c r="V409" s="20"/>
     </row>
     <row r="410" ht="19.5" customHeight="1">
-      <c r="A410" s="10"/>
+      <c r="A410" s="8"/>
       <c r="B410" s="18"/>
       <c r="C410" s="18"/>
       <c r="D410" s="18"/>
@@ -12674,7 +12718,7 @@
       <c r="V410" s="20"/>
     </row>
     <row r="411" ht="19.5" customHeight="1">
-      <c r="A411" s="10"/>
+      <c r="A411" s="8"/>
       <c r="B411" s="18"/>
       <c r="C411" s="18"/>
       <c r="D411" s="18"/>
@@ -12698,7 +12742,7 @@
       <c r="V411" s="20"/>
     </row>
     <row r="412" ht="19.5" customHeight="1">
-      <c r="A412" s="10"/>
+      <c r="A412" s="8"/>
       <c r="B412" s="18"/>
       <c r="C412" s="18"/>
       <c r="D412" s="18"/>
@@ -12722,7 +12766,7 @@
       <c r="V412" s="20"/>
     </row>
     <row r="413" ht="19.5" customHeight="1">
-      <c r="A413" s="10"/>
+      <c r="A413" s="8"/>
       <c r="B413" s="18"/>
       <c r="C413" s="18"/>
       <c r="D413" s="18"/>
@@ -12746,7 +12790,7 @@
       <c r="V413" s="20"/>
     </row>
     <row r="414" ht="19.5" customHeight="1">
-      <c r="A414" s="10"/>
+      <c r="A414" s="8"/>
       <c r="B414" s="18"/>
       <c r="C414" s="18"/>
       <c r="D414" s="18"/>
@@ -12770,7 +12814,7 @@
       <c r="V414" s="20"/>
     </row>
     <row r="415" ht="19.5" customHeight="1">
-      <c r="A415" s="10"/>
+      <c r="A415" s="8"/>
       <c r="B415" s="18"/>
       <c r="C415" s="18"/>
       <c r="D415" s="18"/>
@@ -12794,7 +12838,7 @@
       <c r="V415" s="20"/>
     </row>
     <row r="416" ht="19.5" customHeight="1">
-      <c r="A416" s="10"/>
+      <c r="A416" s="8"/>
       <c r="B416" s="18"/>
       <c r="C416" s="18"/>
       <c r="D416" s="18"/>
@@ -12818,7 +12862,7 @@
       <c r="V416" s="20"/>
     </row>
     <row r="417" ht="19.5" customHeight="1">
-      <c r="A417" s="10"/>
+      <c r="A417" s="8"/>
       <c r="B417" s="18"/>
       <c r="C417" s="18"/>
       <c r="D417" s="18"/>
@@ -12842,7 +12886,7 @@
       <c r="V417" s="20"/>
     </row>
     <row r="418" ht="19.5" customHeight="1">
-      <c r="A418" s="10"/>
+      <c r="A418" s="8"/>
       <c r="B418" s="18"/>
       <c r="C418" s="18"/>
       <c r="D418" s="18"/>
@@ -12866,7 +12910,7 @@
       <c r="V418" s="20"/>
     </row>
     <row r="419" ht="19.5" customHeight="1">
-      <c r="A419" s="10"/>
+      <c r="A419" s="8"/>
       <c r="B419" s="18"/>
       <c r="C419" s="18"/>
       <c r="D419" s="18"/>
@@ -12890,7 +12934,7 @@
       <c r="V419" s="20"/>
     </row>
     <row r="420" ht="19.5" customHeight="1">
-      <c r="A420" s="10"/>
+      <c r="A420" s="8"/>
       <c r="B420" s="18"/>
       <c r="C420" s="18"/>
       <c r="D420" s="18"/>
@@ -12914,7 +12958,7 @@
       <c r="V420" s="20"/>
     </row>
     <row r="421" ht="19.5" customHeight="1">
-      <c r="A421" s="10"/>
+      <c r="A421" s="8"/>
       <c r="B421" s="18"/>
       <c r="C421" s="18"/>
       <c r="D421" s="18"/>
@@ -12938,7 +12982,7 @@
       <c r="V421" s="20"/>
     </row>
     <row r="422" ht="19.5" customHeight="1">
-      <c r="A422" s="10"/>
+      <c r="A422" s="8"/>
       <c r="B422" s="18"/>
       <c r="C422" s="18"/>
       <c r="D422" s="18"/>
@@ -12962,7 +13006,7 @@
       <c r="V422" s="20"/>
     </row>
     <row r="423" ht="19.5" customHeight="1">
-      <c r="A423" s="10"/>
+      <c r="A423" s="8"/>
       <c r="B423" s="18"/>
       <c r="C423" s="18"/>
       <c r="D423" s="18"/>
@@ -12986,7 +13030,7 @@
       <c r="V423" s="20"/>
     </row>
     <row r="424" ht="19.5" customHeight="1">
-      <c r="A424" s="10"/>
+      <c r="A424" s="8"/>
       <c r="B424" s="18"/>
       <c r="C424" s="18"/>
       <c r="D424" s="18"/>
@@ -13010,7 +13054,7 @@
       <c r="V424" s="20"/>
     </row>
     <row r="425" ht="19.5" customHeight="1">
-      <c r="A425" s="10"/>
+      <c r="A425" s="8"/>
       <c r="B425" s="18"/>
       <c r="C425" s="18"/>
       <c r="D425" s="18"/>
@@ -13034,7 +13078,7 @@
       <c r="V425" s="20"/>
     </row>
     <row r="426" ht="19.5" customHeight="1">
-      <c r="A426" s="10"/>
+      <c r="A426" s="8"/>
       <c r="B426" s="18"/>
       <c r="C426" s="18"/>
       <c r="D426" s="18"/>
@@ -13058,7 +13102,7 @@
       <c r="V426" s="20"/>
     </row>
     <row r="427" ht="19.5" customHeight="1">
-      <c r="A427" s="10"/>
+      <c r="A427" s="8"/>
       <c r="B427" s="18"/>
       <c r="C427" s="18"/>
       <c r="D427" s="18"/>
@@ -13082,7 +13126,7 @@
       <c r="V427" s="20"/>
     </row>
     <row r="428" ht="19.5" customHeight="1">
-      <c r="A428" s="10"/>
+      <c r="A428" s="8"/>
       <c r="B428" s="18"/>
       <c r="C428" s="18"/>
       <c r="D428" s="18"/>
@@ -13106,7 +13150,7 @@
       <c r="V428" s="20"/>
     </row>
     <row r="429" ht="19.5" customHeight="1">
-      <c r="A429" s="10"/>
+      <c r="A429" s="8"/>
       <c r="B429" s="18"/>
       <c r="C429" s="18"/>
       <c r="D429" s="18"/>
@@ -13130,7 +13174,7 @@
       <c r="V429" s="20"/>
     </row>
     <row r="430" ht="19.5" customHeight="1">
-      <c r="A430" s="10"/>
+      <c r="A430" s="8"/>
       <c r="B430" s="18"/>
       <c r="C430" s="18"/>
       <c r="D430" s="18"/>
@@ -13154,7 +13198,7 @@
       <c r="V430" s="20"/>
     </row>
     <row r="431" ht="19.5" customHeight="1">
-      <c r="A431" s="10"/>
+      <c r="A431" s="8"/>
       <c r="B431" s="18"/>
       <c r="C431" s="18"/>
       <c r="D431" s="18"/>
@@ -13178,7 +13222,7 @@
       <c r="V431" s="20"/>
     </row>
     <row r="432" ht="19.5" customHeight="1">
-      <c r="A432" s="10"/>
+      <c r="A432" s="8"/>
       <c r="B432" s="18"/>
       <c r="C432" s="18"/>
       <c r="D432" s="18"/>
@@ -13202,7 +13246,7 @@
       <c r="V432" s="20"/>
     </row>
     <row r="433" ht="19.5" customHeight="1">
-      <c r="A433" s="10"/>
+      <c r="A433" s="8"/>
       <c r="B433" s="18"/>
       <c r="C433" s="18"/>
       <c r="D433" s="18"/>
@@ -13226,7 +13270,7 @@
       <c r="V433" s="20"/>
     </row>
     <row r="434" ht="19.5" customHeight="1">
-      <c r="A434" s="10"/>
+      <c r="A434" s="8"/>
       <c r="B434" s="18"/>
       <c r="C434" s="18"/>
       <c r="D434" s="18"/>
@@ -13250,7 +13294,7 @@
       <c r="V434" s="20"/>
     </row>
     <row r="435" ht="19.5" customHeight="1">
-      <c r="A435" s="10"/>
+      <c r="A435" s="8"/>
       <c r="B435" s="18"/>
       <c r="C435" s="18"/>
       <c r="D435" s="18"/>
@@ -13274,7 +13318,7 @@
       <c r="V435" s="20"/>
     </row>
     <row r="436" ht="19.5" customHeight="1">
-      <c r="A436" s="10"/>
+      <c r="A436" s="8"/>
       <c r="B436" s="18"/>
       <c r="C436" s="18"/>
       <c r="D436" s="18"/>
@@ -13298,7 +13342,7 @@
       <c r="V436" s="20"/>
     </row>
     <row r="437" ht="19.5" customHeight="1">
-      <c r="A437" s="10"/>
+      <c r="A437" s="8"/>
       <c r="B437" s="18"/>
       <c r="C437" s="18"/>
       <c r="D437" s="18"/>
@@ -13322,7 +13366,7 @@
       <c r="V437" s="20"/>
     </row>
     <row r="438" ht="19.5" customHeight="1">
-      <c r="A438" s="10"/>
+      <c r="A438" s="8"/>
       <c r="B438" s="18"/>
       <c r="C438" s="18"/>
       <c r="D438" s="18"/>
@@ -13346,7 +13390,7 @@
       <c r="V438" s="20"/>
     </row>
     <row r="439" ht="19.5" customHeight="1">
-      <c r="A439" s="10"/>
+      <c r="A439" s="8"/>
       <c r="B439" s="18"/>
       <c r="C439" s="18"/>
       <c r="D439" s="18"/>
@@ -13370,7 +13414,7 @@
       <c r="V439" s="20"/>
     </row>
     <row r="440" ht="19.5" customHeight="1">
-      <c r="A440" s="10"/>
+      <c r="A440" s="8"/>
       <c r="B440" s="18"/>
       <c r="C440" s="18"/>
       <c r="D440" s="18"/>
@@ -13394,7 +13438,7 @@
       <c r="V440" s="20"/>
     </row>
     <row r="441" ht="19.5" customHeight="1">
-      <c r="A441" s="10"/>
+      <c r="A441" s="8"/>
       <c r="B441" s="18"/>
       <c r="C441" s="18"/>
       <c r="D441" s="18"/>
@@ -13418,7 +13462,7 @@
       <c r="V441" s="20"/>
     </row>
     <row r="442" ht="19.5" customHeight="1">
-      <c r="A442" s="10"/>
+      <c r="A442" s="8"/>
       <c r="B442" s="18"/>
       <c r="C442" s="18"/>
       <c r="D442" s="18"/>
@@ -13442,7 +13486,7 @@
       <c r="V442" s="20"/>
     </row>
     <row r="443" ht="19.5" customHeight="1">
-      <c r="A443" s="10"/>
+      <c r="A443" s="8"/>
       <c r="B443" s="18"/>
       <c r="C443" s="18"/>
       <c r="D443" s="18"/>
@@ -13466,7 +13510,7 @@
       <c r="V443" s="20"/>
     </row>
     <row r="444" ht="19.5" customHeight="1">
-      <c r="A444" s="10"/>
+      <c r="A444" s="8"/>
       <c r="B444" s="18"/>
       <c r="C444" s="18"/>
       <c r="D444" s="18"/>
@@ -13490,7 +13534,7 @@
       <c r="V444" s="20"/>
     </row>
     <row r="445" ht="19.5" customHeight="1">
-      <c r="A445" s="10"/>
+      <c r="A445" s="8"/>
       <c r="B445" s="18"/>
       <c r="C445" s="18"/>
       <c r="D445" s="18"/>
@@ -13514,7 +13558,7 @@
       <c r="V445" s="20"/>
     </row>
     <row r="446" ht="19.5" customHeight="1">
-      <c r="A446" s="10"/>
+      <c r="A446" s="8"/>
       <c r="B446" s="18"/>
       <c r="C446" s="18"/>
       <c r="D446" s="18"/>
@@ -13538,7 +13582,7 @@
       <c r="V446" s="20"/>
     </row>
     <row r="447" ht="19.5" customHeight="1">
-      <c r="A447" s="10"/>
+      <c r="A447" s="8"/>
       <c r="B447" s="18"/>
       <c r="C447" s="18"/>
       <c r="D447" s="18"/>
@@ -13562,7 +13606,7 @@
       <c r="V447" s="20"/>
     </row>
     <row r="448" ht="19.5" customHeight="1">
-      <c r="A448" s="10"/>
+      <c r="A448" s="8"/>
       <c r="B448" s="18"/>
       <c r="C448" s="18"/>
       <c r="D448" s="18"/>
@@ -13586,7 +13630,7 @@
       <c r="V448" s="20"/>
     </row>
     <row r="449" ht="19.5" customHeight="1">
-      <c r="A449" s="10"/>
+      <c r="A449" s="8"/>
       <c r="B449" s="18"/>
       <c r="C449" s="18"/>
       <c r="D449" s="18"/>
@@ -13610,7 +13654,7 @@
       <c r="V449" s="20"/>
     </row>
     <row r="450" ht="19.5" customHeight="1">
-      <c r="A450" s="10"/>
+      <c r="A450" s="8"/>
       <c r="B450" s="18"/>
       <c r="C450" s="18"/>
       <c r="D450" s="18"/>
@@ -13634,7 +13678,7 @@
       <c r="V450" s="20"/>
     </row>
     <row r="451" ht="19.5" customHeight="1">
-      <c r="A451" s="10"/>
+      <c r="A451" s="8"/>
       <c r="B451" s="18"/>
       <c r="C451" s="18"/>
       <c r="D451" s="18"/>
@@ -13658,7 +13702,7 @@
       <c r="V451" s="20"/>
     </row>
     <row r="452" ht="19.5" customHeight="1">
-      <c r="A452" s="10"/>
+      <c r="A452" s="8"/>
       <c r="B452" s="18"/>
       <c r="C452" s="18"/>
       <c r="D452" s="18"/>
@@ -13682,7 +13726,7 @@
       <c r="V452" s="20"/>
     </row>
     <row r="453" ht="19.5" customHeight="1">
-      <c r="A453" s="10"/>
+      <c r="A453" s="8"/>
       <c r="B453" s="18"/>
       <c r="C453" s="18"/>
       <c r="D453" s="18"/>
@@ -13706,7 +13750,7 @@
       <c r="V453" s="20"/>
     </row>
     <row r="454" ht="19.5" customHeight="1">
-      <c r="A454" s="10"/>
+      <c r="A454" s="8"/>
       <c r="B454" s="18"/>
       <c r="C454" s="18"/>
       <c r="D454" s="18"/>
@@ -13730,7 +13774,7 @@
       <c r="V454" s="20"/>
     </row>
     <row r="455" ht="19.5" customHeight="1">
-      <c r="A455" s="10"/>
+      <c r="A455" s="8"/>
       <c r="B455" s="18"/>
       <c r="C455" s="18"/>
       <c r="D455" s="18"/>
@@ -13754,7 +13798,7 @@
       <c r="V455" s="20"/>
     </row>
     <row r="456" ht="19.5" customHeight="1">
-      <c r="A456" s="10"/>
+      <c r="A456" s="8"/>
       <c r="B456" s="18"/>
       <c r="C456" s="18"/>
       <c r="D456" s="18"/>
@@ -13778,7 +13822,7 @@
       <c r="V456" s="20"/>
     </row>
     <row r="457" ht="19.5" customHeight="1">
-      <c r="A457" s="10"/>
+      <c r="A457" s="8"/>
       <c r="B457" s="18"/>
       <c r="C457" s="18"/>
       <c r="D457" s="18"/>
@@ -13802,7 +13846,7 @@
       <c r="V457" s="20"/>
     </row>
     <row r="458" ht="19.5" customHeight="1">
-      <c r="A458" s="10"/>
+      <c r="A458" s="8"/>
       <c r="B458" s="18"/>
       <c r="C458" s="18"/>
       <c r="D458" s="18"/>
@@ -13826,7 +13870,7 @@
       <c r="V458" s="20"/>
     </row>
     <row r="459" ht="19.5" customHeight="1">
-      <c r="A459" s="10"/>
+      <c r="A459" s="8"/>
       <c r="B459" s="18"/>
       <c r="C459" s="18"/>
       <c r="D459" s="18"/>
@@ -13850,7 +13894,7 @@
       <c r="V459" s="20"/>
     </row>
     <row r="460" ht="19.5" customHeight="1">
-      <c r="A460" s="10"/>
+      <c r="A460" s="8"/>
       <c r="B460" s="18"/>
       <c r="C460" s="18"/>
       <c r="D460" s="18"/>
@@ -13874,7 +13918,7 @@
       <c r="V460" s="20"/>
     </row>
     <row r="461" ht="19.5" customHeight="1">
-      <c r="A461" s="10"/>
+      <c r="A461" s="8"/>
       <c r="B461" s="18"/>
       <c r="C461" s="18"/>
       <c r="D461" s="18"/>
@@ -13898,7 +13942,7 @@
       <c r="V461" s="20"/>
     </row>
     <row r="462" ht="19.5" customHeight="1">
-      <c r="A462" s="10"/>
+      <c r="A462" s="8"/>
       <c r="B462" s="18"/>
       <c r="C462" s="18"/>
       <c r="D462" s="18"/>
@@ -13922,7 +13966,7 @@
       <c r="V462" s="20"/>
     </row>
     <row r="463" ht="19.5" customHeight="1">
-      <c r="A463" s="10"/>
+      <c r="A463" s="8"/>
       <c r="B463" s="18"/>
       <c r="C463" s="18"/>
       <c r="D463" s="18"/>
@@ -13946,7 +13990,7 @@
       <c r="V463" s="20"/>
     </row>
     <row r="464" ht="19.5" customHeight="1">
-      <c r="A464" s="10"/>
+      <c r="A464" s="8"/>
       <c r="B464" s="18"/>
       <c r="C464" s="18"/>
       <c r="D464" s="18"/>
@@ -13970,7 +14014,7 @@
       <c r="V464" s="20"/>
     </row>
     <row r="465" ht="19.5" customHeight="1">
-      <c r="A465" s="10"/>
+      <c r="A465" s="8"/>
       <c r="B465" s="18"/>
       <c r="C465" s="18"/>
       <c r="D465" s="18"/>
@@ -13994,7 +14038,7 @@
       <c r="V465" s="20"/>
     </row>
     <row r="466" ht="19.5" customHeight="1">
-      <c r="A466" s="10"/>
+      <c r="A466" s="8"/>
       <c r="B466" s="18"/>
       <c r="C466" s="18"/>
       <c r="D466" s="18"/>
@@ -14018,7 +14062,7 @@
       <c r="V466" s="20"/>
     </row>
     <row r="467" ht="19.5" customHeight="1">
-      <c r="A467" s="10"/>
+      <c r="A467" s="8"/>
       <c r="B467" s="18"/>
       <c r="C467" s="18"/>
       <c r="D467" s="18"/>
@@ -14042,7 +14086,7 @@
       <c r="V467" s="20"/>
     </row>
     <row r="468" ht="19.5" customHeight="1">
-      <c r="A468" s="10"/>
+      <c r="A468" s="8"/>
       <c r="B468" s="18"/>
       <c r="C468" s="18"/>
       <c r="D468" s="18"/>
@@ -14066,7 +14110,7 @@
       <c r="V468" s="20"/>
     </row>
     <row r="469" ht="19.5" customHeight="1">
-      <c r="A469" s="10"/>
+      <c r="A469" s="8"/>
       <c r="B469" s="18"/>
       <c r="C469" s="18"/>
       <c r="D469" s="18"/>
@@ -14090,7 +14134,7 @@
       <c r="V469" s="20"/>
     </row>
     <row r="470" ht="19.5" customHeight="1">
-      <c r="A470" s="10"/>
+      <c r="A470" s="8"/>
       <c r="B470" s="18"/>
       <c r="C470" s="18"/>
       <c r="D470" s="18"/>
@@ -14114,7 +14158,7 @@
       <c r="V470" s="20"/>
     </row>
     <row r="471" ht="19.5" customHeight="1">
-      <c r="A471" s="10"/>
+      <c r="A471" s="8"/>
       <c r="B471" s="18"/>
       <c r="C471" s="18"/>
       <c r="D471" s="18"/>
@@ -14138,7 +14182,7 @@
       <c r="V471" s="20"/>
     </row>
     <row r="472" ht="19.5" customHeight="1">
-      <c r="A472" s="10"/>
+      <c r="A472" s="8"/>
       <c r="B472" s="18"/>
       <c r="C472" s="18"/>
       <c r="D472" s="18"/>
@@ -14162,7 +14206,7 @@
       <c r="V472" s="20"/>
     </row>
     <row r="473" ht="19.5" customHeight="1">
-      <c r="A473" s="10"/>
+      <c r="A473" s="8"/>
       <c r="B473" s="18"/>
       <c r="C473" s="18"/>
       <c r="D473" s="18"/>
@@ -14186,7 +14230,7 @@
       <c r="V473" s="20"/>
     </row>
     <row r="474" ht="19.5" customHeight="1">
-      <c r="A474" s="10"/>
+      <c r="A474" s="8"/>
       <c r="B474" s="18"/>
       <c r="C474" s="18"/>
       <c r="D474" s="18"/>
@@ -14210,7 +14254,7 @@
       <c r="V474" s="20"/>
     </row>
     <row r="475" ht="19.5" customHeight="1">
-      <c r="A475" s="10"/>
+      <c r="A475" s="8"/>
       <c r="B475" s="18"/>
       <c r="C475" s="18"/>
       <c r="D475" s="18"/>
@@ -14234,7 +14278,7 @@
       <c r="V475" s="20"/>
     </row>
     <row r="476" ht="19.5" customHeight="1">
-      <c r="A476" s="10"/>
+      <c r="A476" s="8"/>
       <c r="B476" s="18"/>
       <c r="C476" s="18"/>
       <c r="D476" s="18"/>
@@ -14258,7 +14302,7 @@
       <c r="V476" s="20"/>
     </row>
     <row r="477" ht="19.5" customHeight="1">
-      <c r="A477" s="10"/>
+      <c r="A477" s="8"/>
       <c r="B477" s="18"/>
       <c r="C477" s="18"/>
       <c r="D477" s="18"/>
@@ -14282,7 +14326,7 @@
       <c r="V477" s="20"/>
     </row>
     <row r="478" ht="19.5" customHeight="1">
-      <c r="A478" s="10"/>
+      <c r="A478" s="8"/>
       <c r="B478" s="18"/>
       <c r="C478" s="18"/>
       <c r="D478" s="18"/>
@@ -14306,7 +14350,7 @@
       <c r="V478" s="20"/>
     </row>
     <row r="479" ht="19.5" customHeight="1">
-      <c r="A479" s="10"/>
+      <c r="A479" s="8"/>
       <c r="B479" s="18"/>
       <c r="C479" s="18"/>
       <c r="D479" s="18"/>
@@ -14330,7 +14374,7 @@
       <c r="V479" s="20"/>
     </row>
     <row r="480" ht="19.5" customHeight="1">
-      <c r="A480" s="10"/>
+      <c r="A480" s="8"/>
       <c r="B480" s="18"/>
       <c r="C480" s="18"/>
       <c r="D480" s="18"/>
@@ -14354,7 +14398,7 @@
       <c r="V480" s="20"/>
     </row>
     <row r="481" ht="19.5" customHeight="1">
-      <c r="A481" s="10"/>
+      <c r="A481" s="8"/>
       <c r="B481" s="18"/>
       <c r="C481" s="18"/>
       <c r="D481" s="18"/>
@@ -14378,7 +14422,7 @@
       <c r="V481" s="20"/>
     </row>
     <row r="482" ht="19.5" customHeight="1">
-      <c r="A482" s="10"/>
+      <c r="A482" s="8"/>
       <c r="B482" s="18"/>
       <c r="C482" s="18"/>
       <c r="D482" s="18"/>
@@ -14402,7 +14446,7 @@
       <c r="V482" s="20"/>
     </row>
     <row r="483" ht="19.5" customHeight="1">
-      <c r="A483" s="10"/>
+      <c r="A483" s="8"/>
       <c r="B483" s="18"/>
       <c r="C483" s="18"/>
       <c r="D483" s="18"/>
@@ -14426,7 +14470,7 @@
       <c r="V483" s="20"/>
     </row>
     <row r="484" ht="19.5" customHeight="1">
-      <c r="A484" s="10"/>
+      <c r="A484" s="8"/>
       <c r="B484" s="18"/>
       <c r="C484" s="18"/>
       <c r="D484" s="18"/>
@@ -14450,7 +14494,7 @@
       <c r="V484" s="20"/>
     </row>
     <row r="485" ht="19.5" customHeight="1">
-      <c r="A485" s="10"/>
+      <c r="A485" s="8"/>
       <c r="B485" s="18"/>
       <c r="C485" s="18"/>
       <c r="D485" s="18"/>
@@ -14474,7 +14518,7 @@
       <c r="V485" s="20"/>
     </row>
     <row r="486" ht="19.5" customHeight="1">
-      <c r="A486" s="10"/>
+      <c r="A486" s="8"/>
       <c r="B486" s="18"/>
       <c r="C486" s="18"/>
       <c r="D486" s="18"/>
@@ -14498,7 +14542,7 @@
       <c r="V486" s="20"/>
     </row>
     <row r="487" ht="19.5" customHeight="1">
-      <c r="A487" s="10"/>
+      <c r="A487" s="8"/>
       <c r="B487" s="18"/>
       <c r="C487" s="18"/>
       <c r="D487" s="18"/>
@@ -14522,7 +14566,7 @@
       <c r="V487" s="20"/>
     </row>
     <row r="488" ht="19.5" customHeight="1">
-      <c r="A488" s="10"/>
+      <c r="A488" s="8"/>
       <c r="B488" s="18"/>
       <c r="C488" s="18"/>
       <c r="D488" s="18"/>
@@ -14546,7 +14590,7 @@
       <c r="V488" s="20"/>
     </row>
     <row r="489" ht="19.5" customHeight="1">
-      <c r="A489" s="10"/>
+      <c r="A489" s="8"/>
       <c r="B489" s="18"/>
       <c r="C489" s="18"/>
       <c r="D489" s="18"/>
@@ -14570,7 +14614,7 @@
       <c r="V489" s="20"/>
     </row>
     <row r="490" ht="19.5" customHeight="1">
-      <c r="A490" s="10"/>
+      <c r="A490" s="8"/>
       <c r="B490" s="18"/>
       <c r="C490" s="18"/>
       <c r="D490" s="18"/>
@@ -14594,7 +14638,7 @@
       <c r="V490" s="20"/>
     </row>
     <row r="491" ht="19.5" customHeight="1">
-      <c r="A491" s="10"/>
+      <c r="A491" s="8"/>
       <c r="B491" s="18"/>
       <c r="C491" s="18"/>
       <c r="D491" s="18"/>
@@ -14618,7 +14662,7 @@
       <c r="V491" s="20"/>
     </row>
     <row r="492" ht="19.5" customHeight="1">
-      <c r="A492" s="10"/>
+      <c r="A492" s="8"/>
       <c r="B492" s="18"/>
       <c r="C492" s="18"/>
       <c r="D492" s="18"/>
@@ -14642,7 +14686,7 @@
       <c r="V492" s="20"/>
     </row>
     <row r="493" ht="19.5" customHeight="1">
-      <c r="A493" s="10"/>
+      <c r="A493" s="8"/>
       <c r="B493" s="18"/>
       <c r="C493" s="18"/>
       <c r="D493" s="18"/>
@@ -14666,7 +14710,7 @@
       <c r="V493" s="20"/>
     </row>
     <row r="494" ht="19.5" customHeight="1">
-      <c r="A494" s="10"/>
+      <c r="A494" s="8"/>
       <c r="B494" s="18"/>
       <c r="C494" s="18"/>
       <c r="D494" s="18"/>
@@ -14690,7 +14734,7 @@
       <c r="V494" s="20"/>
     </row>
     <row r="495" ht="19.5" customHeight="1">
-      <c r="A495" s="10"/>
+      <c r="A495" s="8"/>
       <c r="B495" s="18"/>
       <c r="C495" s="18"/>
       <c r="D495" s="18"/>
@@ -14714,7 +14758,7 @@
       <c r="V495" s="20"/>
     </row>
     <row r="496" ht="19.5" customHeight="1">
-      <c r="A496" s="10"/>
+      <c r="A496" s="8"/>
       <c r="B496" s="18"/>
       <c r="C496" s="18"/>
       <c r="D496" s="18"/>
@@ -14738,7 +14782,7 @@
       <c r="V496" s="20"/>
     </row>
     <row r="497" ht="19.5" customHeight="1">
-      <c r="A497" s="10"/>
+      <c r="A497" s="8"/>
       <c r="B497" s="18"/>
       <c r="C497" s="18"/>
       <c r="D497" s="18"/>
@@ -14762,7 +14806,7 @@
       <c r="V497" s="20"/>
     </row>
     <row r="498" ht="19.5" customHeight="1">
-      <c r="A498" s="10"/>
+      <c r="A498" s="8"/>
       <c r="B498" s="18"/>
       <c r="C498" s="18"/>
       <c r="D498" s="18"/>
@@ -14786,7 +14830,7 @@
       <c r="V498" s="20"/>
     </row>
     <row r="499" ht="19.5" customHeight="1">
-      <c r="A499" s="10"/>
+      <c r="A499" s="8"/>
       <c r="B499" s="18"/>
       <c r="C499" s="18"/>
       <c r="D499" s="18"/>
@@ -14810,7 +14854,7 @@
       <c r="V499" s="20"/>
     </row>
     <row r="500" ht="19.5" customHeight="1">
-      <c r="A500" s="10"/>
+      <c r="A500" s="8"/>
       <c r="B500" s="18"/>
       <c r="C500" s="18"/>
       <c r="D500" s="18"/>
@@ -14834,7 +14878,7 @@
       <c r="V500" s="20"/>
     </row>
     <row r="501" ht="19.5" customHeight="1">
-      <c r="A501" s="10"/>
+      <c r="A501" s="8"/>
       <c r="B501" s="18"/>
       <c r="C501" s="18"/>
       <c r="D501" s="18"/>
@@ -14858,7 +14902,7 @@
       <c r="V501" s="20"/>
     </row>
     <row r="502" ht="19.5" customHeight="1">
-      <c r="A502" s="10"/>
+      <c r="A502" s="8"/>
       <c r="B502" s="18"/>
       <c r="C502" s="18"/>
       <c r="D502" s="18"/>
@@ -14882,7 +14926,7 @@
       <c r="V502" s="20"/>
     </row>
     <row r="503" ht="19.5" customHeight="1">
-      <c r="A503" s="10"/>
+      <c r="A503" s="8"/>
       <c r="B503" s="18"/>
       <c r="C503" s="18"/>
       <c r="D503" s="18"/>
@@ -14906,7 +14950,7 @@
       <c r="V503" s="20"/>
     </row>
     <row r="504" ht="19.5" customHeight="1">
-      <c r="A504" s="10"/>
+      <c r="A504" s="8"/>
       <c r="B504" s="18"/>
       <c r="C504" s="18"/>
       <c r="D504" s="18"/>
@@ -14930,7 +14974,7 @@
       <c r="V504" s="20"/>
     </row>
     <row r="505" ht="19.5" customHeight="1">
-      <c r="A505" s="10"/>
+      <c r="A505" s="8"/>
       <c r="B505" s="18"/>
       <c r="C505" s="18"/>
       <c r="D505" s="18"/>
@@ -14954,7 +14998,7 @@
       <c r="V505" s="20"/>
     </row>
     <row r="506" ht="19.5" customHeight="1">
-      <c r="A506" s="10"/>
+      <c r="A506" s="8"/>
       <c r="B506" s="18"/>
       <c r="C506" s="18"/>
       <c r="D506" s="18"/>
@@ -14978,7 +15022,7 @@
       <c r="V506" s="20"/>
     </row>
     <row r="507" ht="19.5" customHeight="1">
-      <c r="A507" s="10"/>
+      <c r="A507" s="8"/>
       <c r="B507" s="18"/>
       <c r="C507" s="18"/>
       <c r="D507" s="18"/>
@@ -15002,7 +15046,7 @@
       <c r="V507" s="20"/>
     </row>
     <row r="508" ht="19.5" customHeight="1">
-      <c r="A508" s="10"/>
+      <c r="A508" s="8"/>
       <c r="B508" s="18"/>
       <c r="C508" s="18"/>
       <c r="D508" s="18"/>
@@ -15026,7 +15070,7 @@
       <c r="V508" s="20"/>
     </row>
     <row r="509" ht="19.5" customHeight="1">
-      <c r="A509" s="10"/>
+      <c r="A509" s="8"/>
       <c r="B509" s="18"/>
       <c r="C509" s="18"/>
       <c r="D509" s="18"/>
@@ -15050,7 +15094,7 @@
       <c r="V509" s="20"/>
     </row>
     <row r="510" ht="19.5" customHeight="1">
-      <c r="A510" s="10"/>
+      <c r="A510" s="8"/>
       <c r="B510" s="18"/>
       <c r="C510" s="18"/>
       <c r="D510" s="18"/>
@@ -15074,7 +15118,7 @@
       <c r="V510" s="20"/>
     </row>
     <row r="511" ht="19.5" customHeight="1">
-      <c r="A511" s="10"/>
+      <c r="A511" s="8"/>
       <c r="B511" s="18"/>
       <c r="C511" s="18"/>
       <c r="D511" s="18"/>
@@ -15098,7 +15142,7 @@
       <c r="V511" s="20"/>
     </row>
     <row r="512" ht="19.5" customHeight="1">
-      <c r="A512" s="10"/>
+      <c r="A512" s="8"/>
       <c r="B512" s="18"/>
       <c r="C512" s="18"/>
       <c r="D512" s="18"/>
@@ -15122,7 +15166,7 @@
       <c r="V512" s="20"/>
     </row>
     <row r="513" ht="19.5" customHeight="1">
-      <c r="A513" s="10"/>
+      <c r="A513" s="8"/>
       <c r="B513" s="18"/>
       <c r="C513" s="18"/>
       <c r="D513" s="18"/>
@@ -15146,7 +15190,7 @@
       <c r="V513" s="20"/>
     </row>
     <row r="514" ht="19.5" customHeight="1">
-      <c r="A514" s="10"/>
+      <c r="A514" s="8"/>
       <c r="B514" s="18"/>
       <c r="C514" s="18"/>
       <c r="D514" s="18"/>
@@ -15170,7 +15214,7 @@
       <c r="V514" s="20"/>
     </row>
     <row r="515" ht="19.5" customHeight="1">
-      <c r="A515" s="10"/>
+      <c r="A515" s="8"/>
       <c r="B515" s="18"/>
       <c r="C515" s="18"/>
       <c r="D515" s="18"/>
@@ -15194,7 +15238,7 @@
       <c r="V515" s="20"/>
     </row>
     <row r="516" ht="19.5" customHeight="1">
-      <c r="A516" s="10"/>
+      <c r="A516" s="8"/>
       <c r="B516" s="18"/>
       <c r="C516" s="18"/>
       <c r="D516" s="18"/>
@@ -15218,7 +15262,7 @@
       <c r="V516" s="20"/>
     </row>
     <row r="517" ht="19.5" customHeight="1">
-      <c r="A517" s="10"/>
+      <c r="A517" s="8"/>
       <c r="B517" s="18"/>
       <c r="C517" s="18"/>
       <c r="D517" s="18"/>
@@ -15242,7 +15286,7 @@
       <c r="V517" s="20"/>
     </row>
     <row r="518" ht="19.5" customHeight="1">
-      <c r="A518" s="10"/>
+      <c r="A518" s="8"/>
       <c r="B518" s="18"/>
       <c r="C518" s="18"/>
       <c r="D518" s="18"/>
@@ -15266,7 +15310,7 @@
       <c r="V518" s="20"/>
     </row>
     <row r="519" ht="19.5" customHeight="1">
-      <c r="A519" s="10"/>
+      <c r="A519" s="8"/>
       <c r="B519" s="18"/>
       <c r="C519" s="18"/>
       <c r="D519" s="18"/>
@@ -15290,7 +15334,7 @@
       <c r="V519" s="20"/>
     </row>
     <row r="520" ht="19.5" customHeight="1">
-      <c r="A520" s="10"/>
+      <c r="A520" s="8"/>
       <c r="B520" s="18"/>
       <c r="C520" s="18"/>
       <c r="D520" s="18"/>
@@ -15314,7 +15358,7 @@
       <c r="V520" s="20"/>
     </row>
     <row r="521" ht="19.5" customHeight="1">
-      <c r="A521" s="10"/>
+      <c r="A521" s="8"/>
       <c r="B521" s="18"/>
       <c r="C521" s="18"/>
       <c r="D521" s="18"/>
@@ -15338,7 +15382,7 @@
       <c r="V521" s="20"/>
     </row>
     <row r="522" ht="19.5" customHeight="1">
-      <c r="A522" s="10"/>
+      <c r="A522" s="8"/>
       <c r="B522" s="18"/>
       <c r="C522" s="18"/>
       <c r="D522" s="18"/>
@@ -15362,7 +15406,7 @@
       <c r="V522" s="20"/>
     </row>
     <row r="523" ht="19.5" customHeight="1">
-      <c r="A523" s="10"/>
+      <c r="A523" s="8"/>
       <c r="B523" s="18"/>
       <c r="C523" s="18"/>
       <c r="D523" s="18"/>
@@ -15386,7 +15430,7 @@
       <c r="V523" s="20"/>
     </row>
     <row r="524" ht="19.5" customHeight="1">
-      <c r="A524" s="10"/>
+      <c r="A524" s="8"/>
       <c r="B524" s="18"/>
       <c r="C524" s="18"/>
       <c r="D524" s="18"/>
@@ -15410,7 +15454,7 @@
       <c r="V524" s="20"/>
     </row>
     <row r="525" ht="19.5" customHeight="1">
-      <c r="A525" s="10"/>
+      <c r="A525" s="8"/>
       <c r="B525" s="18"/>
       <c r="C525" s="18"/>
       <c r="D525" s="18"/>
@@ -15434,7 +15478,7 @@
       <c r="V525" s="20"/>
     </row>
     <row r="526" ht="19.5" customHeight="1">
-      <c r="A526" s="10"/>
+      <c r="A526" s="8"/>
       <c r="B526" s="18"/>
       <c r="C526" s="18"/>
       <c r="D526" s="18"/>
@@ -15458,7 +15502,7 @@
       <c r="V526" s="20"/>
     </row>
     <row r="527" ht="19.5" customHeight="1">
-      <c r="A527" s="10"/>
+      <c r="A527" s="8"/>
       <c r="B527" s="18"/>
       <c r="C527" s="18"/>
       <c r="D527" s="18"/>
@@ -15482,7 +15526,7 @@
       <c r="V527" s="20"/>
     </row>
     <row r="528" ht="19.5" customHeight="1">
-      <c r="A528" s="10"/>
+      <c r="A528" s="8"/>
       <c r="B528" s="18"/>
       <c r="C528" s="18"/>
       <c r="D528" s="18"/>
@@ -15506,7 +15550,7 @@
       <c r="V528" s="20"/>
     </row>
     <row r="529" ht="19.5" customHeight="1">
-      <c r="A529" s="10"/>
+      <c r="A529" s="8"/>
       <c r="B529" s="18"/>
       <c r="C529" s="18"/>
       <c r="D529" s="18"/>
@@ -15530,7 +15574,7 @@
       <c r="V529" s="20"/>
     </row>
     <row r="530" ht="19.5" customHeight="1">
-      <c r="A530" s="10"/>
+      <c r="A530" s="8"/>
       <c r="B530" s="18"/>
       <c r="C530" s="18"/>
       <c r="D530" s="18"/>
@@ -15554,7 +15598,7 @@
       <c r="V530" s="20"/>
     </row>
     <row r="531" ht="19.5" customHeight="1">
-      <c r="A531" s="10"/>
+      <c r="A531" s="8"/>
       <c r="B531" s="18"/>
       <c r="C531" s="18"/>
       <c r="D531" s="18"/>
@@ -15578,7 +15622,7 @@
       <c r="V531" s="20"/>
     </row>
     <row r="532" ht="19.5" customHeight="1">
-      <c r="A532" s="10"/>
+      <c r="A532" s="8"/>
       <c r="B532" s="18"/>
       <c r="C532" s="18"/>
       <c r="D532" s="18"/>
@@ -15602,7 +15646,7 @@
       <c r="V532" s="20"/>
     </row>
     <row r="533" ht="19.5" customHeight="1">
-      <c r="A533" s="10"/>
+      <c r="A533" s="8"/>
       <c r="B533" s="18"/>
       <c r="C533" s="18"/>
       <c r="D533" s="18"/>
@@ -15626,7 +15670,7 @@
       <c r="V533" s="20"/>
     </row>
     <row r="534" ht="19.5" customHeight="1">
-      <c r="A534" s="10"/>
+      <c r="A534" s="8"/>
       <c r="B534" s="18"/>
       <c r="C534" s="18"/>
       <c r="D534" s="18"/>
@@ -15650,7 +15694,7 @@
       <c r="V534" s="20"/>
     </row>
     <row r="535" ht="19.5" customHeight="1">
-      <c r="A535" s="10"/>
+      <c r="A535" s="8"/>
       <c r="B535" s="18"/>
       <c r="C535" s="18"/>
       <c r="D535" s="18"/>
@@ -15674,7 +15718,7 @@
       <c r="V535" s="20"/>
     </row>
     <row r="536" ht="19.5" customHeight="1">
-      <c r="A536" s="10"/>
+      <c r="A536" s="8"/>
       <c r="B536" s="18"/>
       <c r="C536" s="18"/>
       <c r="D536" s="18"/>
@@ -15698,7 +15742,7 @@
       <c r="V536" s="20"/>
     </row>
     <row r="537" ht="19.5" customHeight="1">
-      <c r="A537" s="10"/>
+      <c r="A537" s="8"/>
       <c r="B537" s="18"/>
       <c r="C537" s="18"/>
       <c r="D537" s="18"/>
@@ -15722,7 +15766,7 @@
       <c r="V537" s="20"/>
     </row>
     <row r="538" ht="19.5" customHeight="1">
-      <c r="A538" s="10"/>
+      <c r="A538" s="8"/>
       <c r="B538" s="18"/>
       <c r="C538" s="18"/>
       <c r="D538" s="18"/>
@@ -15746,7 +15790,7 @@
       <c r="V538" s="20"/>
     </row>
     <row r="539" ht="19.5" customHeight="1">
-      <c r="A539" s="10"/>
+      <c r="A539" s="8"/>
       <c r="B539" s="18"/>
       <c r="C539" s="18"/>
       <c r="D539" s="18"/>
@@ -15770,7 +15814,7 @@
       <c r="V539" s="20"/>
     </row>
     <row r="540" ht="19.5" customHeight="1">
-      <c r="A540" s="10"/>
+      <c r="A540" s="8"/>
       <c r="B540" s="18"/>
       <c r="C540" s="18"/>
       <c r="D540" s="18"/>
@@ -15794,7 +15838,7 @@
       <c r="V540" s="20"/>
     </row>
     <row r="541" ht="19.5" customHeight="1">
-      <c r="A541" s="10"/>
+      <c r="A541" s="8"/>
       <c r="B541" s="18"/>
       <c r="C541" s="18"/>
       <c r="D541" s="18"/>
@@ -15818,7 +15862,7 @@
       <c r="V541" s="20"/>
     </row>
     <row r="542" ht="19.5" customHeight="1">
-      <c r="A542" s="10"/>
+      <c r="A542" s="8"/>
       <c r="B542" s="18"/>
       <c r="C542" s="18"/>
       <c r="D542" s="18"/>
@@ -15842,7 +15886,7 @@
       <c r="V542" s="20"/>
     </row>
     <row r="543" ht="19.5" customHeight="1">
-      <c r="A543" s="10"/>
+      <c r="A543" s="8"/>
       <c r="B543" s="18"/>
       <c r="C543" s="18"/>
       <c r="D543" s="18"/>
@@ -15866,7 +15910,7 @@
       <c r="V543" s="20"/>
     </row>
     <row r="544" ht="19.5" customHeight="1">
-      <c r="A544" s="10"/>
+      <c r="A544" s="8"/>
       <c r="B544" s="18"/>
       <c r="C544" s="18"/>
       <c r="D544" s="18"/>
@@ -15890,7 +15934,7 @@
       <c r="V544" s="20"/>
     </row>
     <row r="545" ht="19.5" customHeight="1">
-      <c r="A545" s="10"/>
+      <c r="A545" s="8"/>
       <c r="B545" s="18"/>
       <c r="C545" s="18"/>
       <c r="D545" s="18"/>
@@ -15914,7 +15958,7 @@
       <c r="V545" s="20"/>
     </row>
     <row r="546" ht="19.5" customHeight="1">
-      <c r="A546" s="10"/>
+      <c r="A546" s="8"/>
       <c r="B546" s="18"/>
       <c r="C546" s="18"/>
       <c r="D546" s="18"/>
@@ -15938,7 +15982,7 @@
       <c r="V546" s="20"/>
     </row>
     <row r="547" ht="19.5" customHeight="1">
-      <c r="A547" s="10"/>
+      <c r="A547" s="8"/>
       <c r="B547" s="18"/>
       <c r="C547" s="18"/>
       <c r="D547" s="18"/>
@@ -15962,7 +16006,7 @@
       <c r="V547" s="20"/>
     </row>
     <row r="548" ht="19.5" customHeight="1">
-      <c r="A548" s="10"/>
+      <c r="A548" s="8"/>
       <c r="B548" s="18"/>
       <c r="C548" s="18"/>
       <c r="D548" s="18"/>
@@ -15986,7 +16030,7 @@
       <c r="V548" s="20"/>
     </row>
     <row r="549" ht="19.5" customHeight="1">
-      <c r="A549" s="10"/>
+      <c r="A549" s="8"/>
       <c r="B549" s="18"/>
       <c r="C549" s="18"/>
       <c r="D549" s="18"/>
@@ -16010,7 +16054,7 @@
       <c r="V549" s="20"/>
     </row>
     <row r="550" ht="19.5" customHeight="1">
-      <c r="A550" s="10"/>
+      <c r="A550" s="8"/>
       <c r="B550" s="18"/>
       <c r="C550" s="18"/>
       <c r="D550" s="18"/>
@@ -16034,7 +16078,7 @@
       <c r="V550" s="20"/>
     </row>
     <row r="551" ht="19.5" customHeight="1">
-      <c r="A551" s="10"/>
+      <c r="A551" s="8"/>
       <c r="B551" s="18"/>
       <c r="C551" s="18"/>
       <c r="D551" s="18"/>
@@ -16058,7 +16102,7 @@
       <c r="V551" s="20"/>
     </row>
     <row r="552" ht="19.5" customHeight="1">
-      <c r="A552" s="10"/>
+      <c r="A552" s="8"/>
       <c r="B552" s="18"/>
       <c r="C552" s="18"/>
       <c r="D552" s="18"/>
@@ -16082,7 +16126,7 @@
       <c r="V552" s="20"/>
     </row>
     <row r="553" ht="19.5" customHeight="1">
-      <c r="A553" s="10"/>
+      <c r="A553" s="8"/>
       <c r="B553" s="18"/>
       <c r="C553" s="18"/>
       <c r="D553" s="18"/>
@@ -16106,7 +16150,7 @@
       <c r="V553" s="20"/>
     </row>
     <row r="554" ht="19.5" customHeight="1">
-      <c r="A554" s="10"/>
+      <c r="A554" s="8"/>
       <c r="B554" s="18"/>
       <c r="C554" s="18"/>
       <c r="D554" s="18"/>
@@ -16130,7 +16174,7 @@
       <c r="V554" s="20"/>
     </row>
     <row r="555" ht="19.5" customHeight="1">
-      <c r="A555" s="10"/>
+      <c r="A555" s="8"/>
       <c r="B555" s="18"/>
       <c r="C555" s="18"/>
       <c r="D555" s="18"/>
@@ -16154,7 +16198,7 @@
       <c r="V555" s="20"/>
     </row>
     <row r="556" ht="19.5" customHeight="1">
-      <c r="A556" s="10"/>
+      <c r="A556" s="8"/>
       <c r="B556" s="18"/>
       <c r="C556" s="18"/>
       <c r="D556" s="18"/>
@@ -16178,7 +16222,7 @@
       <c r="V556" s="20"/>
     </row>
     <row r="557" ht="19.5" customHeight="1">
-      <c r="A557" s="10"/>
+      <c r="A557" s="8"/>
       <c r="B557" s="18"/>
       <c r="C557" s="18"/>
       <c r="D557" s="18"/>
@@ -16202,7 +16246,7 @@
       <c r="V557" s="20"/>
     </row>
     <row r="558" ht="19.5" customHeight="1">
-      <c r="A558" s="10"/>
+      <c r="A558" s="8"/>
       <c r="B558" s="18"/>
       <c r="C558" s="18"/>
       <c r="D558" s="18"/>
@@ -16226,7 +16270,7 @@
       <c r="V558" s="20"/>
     </row>
     <row r="559" ht="19.5" customHeight="1">
-      <c r="A559" s="10"/>
+      <c r="A559" s="8"/>
       <c r="B559" s="18"/>
       <c r="C559" s="18"/>
       <c r="D559" s="18"/>
@@ -16250,7 +16294,7 @@
       <c r="V559" s="20"/>
     </row>
     <row r="560" ht="19.5" customHeight="1">
-      <c r="A560" s="10"/>
+      <c r="A560" s="8"/>
       <c r="B560" s="18"/>
       <c r="C560" s="18"/>
       <c r="D560" s="18"/>
@@ -16274,7 +16318,7 @@
       <c r="V560" s="20"/>
     </row>
     <row r="561" ht="19.5" customHeight="1">
-      <c r="A561" s="10"/>
+      <c r="A561" s="8"/>
       <c r="B561" s="18"/>
       <c r="C561" s="18"/>
       <c r="D561" s="18"/>
@@ -16298,7 +16342,7 @@
       <c r="V561" s="20"/>
     </row>
     <row r="562" ht="19.5" customHeight="1">
-      <c r="A562" s="10"/>
+      <c r="A562" s="8"/>
       <c r="B562" s="18"/>
       <c r="C562" s="18"/>
       <c r="D562" s="18"/>
@@ -16322,7 +16366,7 @@
       <c r="V562" s="20"/>
     </row>
     <row r="563" ht="19.5" customHeight="1">
-      <c r="A563" s="10"/>
+      <c r="A563" s="8"/>
       <c r="B563" s="18"/>
       <c r="C563" s="18"/>
       <c r="D563" s="18"/>
@@ -16346,7 +16390,7 @@
       <c r="V563" s="20"/>
     </row>
     <row r="564" ht="19.5" customHeight="1">
-      <c r="A564" s="10"/>
+      <c r="A564" s="8"/>
       <c r="B564" s="18"/>
       <c r="C564" s="18"/>
       <c r="D564" s="18"/>
@@ -16370,7 +16414,7 @@
       <c r="V564" s="20"/>
     </row>
     <row r="565" ht="19.5" customHeight="1">
-      <c r="A565" s="10"/>
+      <c r="A565" s="8"/>
       <c r="B565" s="18"/>
       <c r="C565" s="18"/>
       <c r="D565" s="18"/>
@@ -16394,7 +16438,7 @@
       <c r="V565" s="20"/>
     </row>
     <row r="566" ht="19.5" customHeight="1">
-      <c r="A566" s="10"/>
+      <c r="A566" s="8"/>
       <c r="B566" s="18"/>
       <c r="C566" s="18"/>
       <c r="D566" s="18"/>
@@ -16418,7 +16462,7 @@
       <c r="V566" s="20"/>
     </row>
     <row r="567" ht="19.5" customHeight="1">
-      <c r="A567" s="10"/>
+      <c r="A567" s="8"/>
       <c r="B567" s="18"/>
       <c r="C567" s="18"/>
       <c r="D567" s="18"/>
@@ -16442,7 +16486,7 @@
       <c r="V567" s="20"/>
     </row>
     <row r="568" ht="19.5" customHeight="1">
-      <c r="A568" s="10"/>
+      <c r="A568" s="8"/>
       <c r="B568" s="18"/>
       <c r="C568" s="18"/>
       <c r="D568" s="18"/>
@@ -16466,7 +16510,7 @@
       <c r="V568" s="20"/>
     </row>
     <row r="569" ht="19.5" customHeight="1">
-      <c r="A569" s="10"/>
+      <c r="A569" s="8"/>
       <c r="B569" s="18"/>
       <c r="C569" s="18"/>
       <c r="D569" s="18"/>
@@ -16490,7 +16534,7 @@
       <c r="V569" s="20"/>
     </row>
     <row r="570" ht="19.5" customHeight="1">
-      <c r="A570" s="10"/>
+      <c r="A570" s="8"/>
       <c r="B570" s="18"/>
       <c r="C570" s="18"/>
       <c r="D570" s="18"/>
@@ -16514,7 +16558,7 @@
       <c r="V570" s="20"/>
     </row>
     <row r="571" ht="19.5" customHeight="1">
-      <c r="A571" s="10"/>
+      <c r="A571" s="8"/>
       <c r="B571" s="18"/>
       <c r="C571" s="18"/>
       <c r="D571" s="18"/>
@@ -16538,7 +16582,7 @@
       <c r="V571" s="20"/>
     </row>
     <row r="572" ht="19.5" customHeight="1">
-      <c r="A572" s="10"/>
+      <c r="A572" s="8"/>
       <c r="B572" s="18"/>
       <c r="C572" s="18"/>
       <c r="D572" s="18"/>
@@ -16562,7 +16606,7 @@
       <c r="V572" s="20"/>
     </row>
     <row r="573" ht="19.5" customHeight="1">
-      <c r="A573" s="10"/>
+      <c r="A573" s="8"/>
       <c r="B573" s="18"/>
       <c r="C573" s="18"/>
       <c r="D573" s="18"/>
@@ -16586,7 +16630,7 @@
       <c r="V573" s="20"/>
     </row>
     <row r="574" ht="19.5" customHeight="1">
-      <c r="A574" s="10"/>
+      <c r="A574" s="8"/>
       <c r="B574" s="18"/>
       <c r="C574" s="18"/>
       <c r="D574" s="18"/>
@@ -16610,7 +16654,7 @@
       <c r="V574" s="20"/>
     </row>
     <row r="575" ht="19.5" customHeight="1">
-      <c r="A575" s="10"/>
+      <c r="A575" s="8"/>
       <c r="B575" s="18"/>
       <c r="C575" s="18"/>
       <c r="D575" s="18"/>
@@ -16634,7 +16678,7 @@
       <c r="V575" s="20"/>
     </row>
     <row r="576" ht="19.5" customHeight="1">
-      <c r="A576" s="10"/>
+      <c r="A576" s="8"/>
       <c r="B576" s="18"/>
       <c r="C576" s="18"/>
       <c r="D576" s="18"/>
@@ -16658,7 +16702,7 @@
       <c r="V576" s="20"/>
     </row>
     <row r="577" ht="19.5" customHeight="1">
-      <c r="A577" s="10"/>
+      <c r="A577" s="8"/>
       <c r="B577" s="18"/>
       <c r="C577" s="18"/>
       <c r="D577" s="18"/>
@@ -16682,7 +16726,7 @@
       <c r="V577" s="20"/>
     </row>
     <row r="578" ht="19.5" customHeight="1">
-      <c r="A578" s="10"/>
+      <c r="A578" s="8"/>
       <c r="B578" s="18"/>
       <c r="C578" s="18"/>
       <c r="D578" s="18"/>
@@ -16706,7 +16750,7 @@
       <c r="V578" s="20"/>
     </row>
     <row r="579" ht="19.5" customHeight="1">
-      <c r="A579" s="10"/>
+      <c r="A579" s="8"/>
       <c r="B579" s="18"/>
       <c r="C579" s="18"/>
       <c r="D579" s="18"/>
@@ -16730,7 +16774,7 @@
       <c r="V579" s="20"/>
     </row>
     <row r="580" ht="19.5" customHeight="1">
-      <c r="A580" s="10"/>
+      <c r="A580" s="8"/>
       <c r="B580" s="18"/>
       <c r="C580" s="18"/>
       <c r="D580" s="18"/>
@@ -16754,7 +16798,7 @@
       <c r="V580" s="20"/>
     </row>
     <row r="581" ht="19.5" customHeight="1">
-      <c r="A581" s="10"/>
+      <c r="A581" s="8"/>
       <c r="B581" s="18"/>
       <c r="C581" s="18"/>
       <c r="D581" s="18"/>
@@ -16778,7 +16822,7 @@
       <c r="V581" s="20"/>
     </row>
     <row r="582" ht="19.5" customHeight="1">
-      <c r="A582" s="10"/>
+      <c r="A582" s="8"/>
       <c r="B582" s="18"/>
       <c r="C582" s="18"/>
       <c r="D582" s="18"/>
@@ -16802,7 +16846,7 @@
       <c r="V582" s="20"/>
     </row>
     <row r="583" ht="19.5" customHeight="1">
-      <c r="A583" s="10"/>
+      <c r="A583" s="8"/>
       <c r="B583" s="18"/>
       <c r="C583" s="18"/>
       <c r="D583" s="18"/>
@@ -16826,7 +16870,7 @@
       <c r="V583" s="20"/>
     </row>
     <row r="584" ht="19.5" customHeight="1">
-      <c r="A584" s="10"/>
+      <c r="A584" s="8"/>
       <c r="B584" s="18"/>
       <c r="C584" s="18"/>
       <c r="D584" s="18"/>
@@ -16850,7 +16894,7 @@
       <c r="V584" s="20"/>
     </row>
     <row r="585" ht="19.5" customHeight="1">
-      <c r="A585" s="10"/>
+      <c r="A585" s="8"/>
       <c r="B585" s="18"/>
       <c r="C585" s="18"/>
       <c r="D585" s="18"/>
@@ -16874,7 +16918,7 @@
       <c r="V585" s="20"/>
     </row>
     <row r="586" ht="19.5" customHeight="1">
-      <c r="A586" s="10"/>
+      <c r="A586" s="8"/>
       <c r="B586" s="18"/>
       <c r="C586" s="18"/>
       <c r="D586" s="18"/>
@@ -16898,7 +16942,7 @@
       <c r="V586" s="20"/>
     </row>
     <row r="587" ht="19.5" customHeight="1">
-      <c r="A587" s="10"/>
+      <c r="A587" s="8"/>
       <c r="B587" s="18"/>
       <c r="C587" s="18"/>
       <c r="D587" s="18"/>
@@ -16922,7 +16966,7 @@
       <c r="V587" s="20"/>
     </row>
     <row r="588" ht="19.5" customHeight="1">
-      <c r="A588" s="10"/>
+      <c r="A588" s="8"/>
       <c r="B588" s="18"/>
       <c r="C588" s="18"/>
       <c r="D588" s="18"/>
@@ -16946,7 +16990,7 @@
       <c r="V588" s="20"/>
     </row>
     <row r="589" ht="19.5" customHeight="1">
-      <c r="A589" s="10"/>
+      <c r="A589" s="8"/>
       <c r="B589" s="18"/>
       <c r="C589" s="18"/>
       <c r="D589" s="18"/>
@@ -16970,7 +17014,7 @@
       <c r="V589" s="20"/>
     </row>
     <row r="590" ht="19.5" customHeight="1">
-      <c r="A590" s="10"/>
+      <c r="A590" s="8"/>
       <c r="B590" s="18"/>
       <c r="C590" s="18"/>
       <c r="D590" s="18"/>
@@ -16994,7 +17038,7 @@
       <c r="V590" s="20"/>
     </row>
     <row r="591" ht="19.5" customHeight="1">
-      <c r="A591" s="10"/>
+      <c r="A591" s="8"/>
       <c r="B591" s="18"/>
       <c r="C591" s="18"/>
       <c r="D591" s="18"/>
@@ -17018,7 +17062,7 @@
       <c r="V591" s="20"/>
     </row>
     <row r="592" ht="19.5" customHeight="1">
-      <c r="A592" s="10"/>
+      <c r="A592" s="8"/>
       <c r="B592" s="18"/>
       <c r="C592" s="18"/>
       <c r="D592" s="18"/>
@@ -17042,7 +17086,7 @@
       <c r="V592" s="20"/>
     </row>
     <row r="593" ht="19.5" customHeight="1">
-      <c r="A593" s="10"/>
+      <c r="A593" s="8"/>
       <c r="B593" s="18"/>
       <c r="C593" s="18"/>
       <c r="D593" s="18"/>
@@ -17066,7 +17110,7 @@
       <c r="V593" s="20"/>
     </row>
     <row r="594" ht="19.5" customHeight="1">
-      <c r="A594" s="10"/>
+      <c r="A594" s="8"/>
       <c r="B594" s="18"/>
       <c r="C594" s="18"/>
       <c r="D594" s="18"/>
@@ -17090,7 +17134,7 @@
       <c r="V594" s="20"/>
     </row>
     <row r="595" ht="19.5" customHeight="1">
-      <c r="A595" s="10"/>
+      <c r="A595" s="8"/>
       <c r="B595" s="18"/>
       <c r="C595" s="18"/>
       <c r="D595" s="18"/>
@@ -17114,7 +17158,7 @@
       <c r="V595" s="20"/>
     </row>
     <row r="596" ht="19.5" customHeight="1">
-      <c r="A596" s="10"/>
+      <c r="A596" s="8"/>
       <c r="B596" s="18"/>
       <c r="C596" s="18"/>
       <c r="D596" s="18"/>
@@ -17138,7 +17182,7 @@
       <c r="V596" s="20"/>
     </row>
     <row r="597" ht="19.5" customHeight="1">
-      <c r="A597" s="10"/>
+      <c r="A597" s="8"/>
       <c r="B597" s="18"/>
       <c r="C597" s="18"/>
       <c r="D597" s="18"/>
@@ -17162,7 +17206,7 @@
       <c r="V597" s="20"/>
     </row>
     <row r="598" ht="19.5" customHeight="1">
-      <c r="A598" s="10"/>
+      <c r="A598" s="8"/>
       <c r="B598" s="18"/>
       <c r="C598" s="18"/>
       <c r="D598" s="18"/>
@@ -17186,7 +17230,7 @@
       <c r="V598" s="20"/>
     </row>
     <row r="599" ht="19.5" customHeight="1">
-      <c r="A599" s="10"/>
+      <c r="A599" s="8"/>
       <c r="B599" s="18"/>
       <c r="C599" s="18"/>
       <c r="D599" s="18"/>
@@ -17210,7 +17254,7 @@
       <c r="V599" s="20"/>
     </row>
     <row r="600" ht="19.5" customHeight="1">
-      <c r="A600" s="10"/>
+      <c r="A600" s="8"/>
       <c r="B600" s="18"/>
       <c r="C600" s="18"/>
       <c r="D600" s="18"/>
@@ -17234,7 +17278,7 @@
       <c r="V600" s="20"/>
     </row>
     <row r="601" ht="19.5" customHeight="1">
-      <c r="A601" s="10"/>
+      <c r="A601" s="8"/>
       <c r="B601" s="18"/>
       <c r="C601" s="18"/>
       <c r="D601" s="18"/>
@@ -17258,7 +17302,7 @@
       <c r="V601" s="20"/>
     </row>
     <row r="602" ht="19.5" customHeight="1">
-      <c r="A602" s="10"/>
+      <c r="A602" s="8"/>
       <c r="B602" s="18"/>
       <c r="C602" s="18"/>
       <c r="D602" s="18"/>
@@ -17282,7 +17326,7 @@
       <c r="V602" s="20"/>
     </row>
     <row r="603" ht="19.5" customHeight="1">
-      <c r="A603" s="10"/>
+      <c r="A603" s="8"/>
       <c r="B603" s="18"/>
       <c r="C603" s="18"/>
       <c r="D603" s="18"/>
@@ -17306,7 +17350,7 @@
       <c r="V603" s="20"/>
     </row>
     <row r="604" ht="19.5" customHeight="1">
-      <c r="A604" s="10"/>
+      <c r="A604" s="8"/>
       <c r="B604" s="18"/>
       <c r="C604" s="18"/>
       <c r="D604" s="18"/>
@@ -17330,7 +17374,7 @@
       <c r="V604" s="20"/>
     </row>
     <row r="605" ht="19.5" customHeight="1">
-      <c r="A605" s="10"/>
+      <c r="A605" s="8"/>
       <c r="B605" s="18"/>
       <c r="C605" s="18"/>
       <c r="D605" s="18"/>
@@ -17354,7 +17398,7 @@
       <c r="V605" s="20"/>
     </row>
     <row r="606" ht="19.5" customHeight="1">
-      <c r="A606" s="10"/>
+      <c r="A606" s="8"/>
       <c r="B606" s="18"/>
       <c r="C606" s="18"/>
       <c r="D606" s="18"/>
@@ -17378,7 +17422,7 @@
       <c r="V606" s="20"/>
     </row>
     <row r="607" ht="19.5" customHeight="1">
-      <c r="A607" s="10"/>
+      <c r="A607" s="8"/>
       <c r="B607" s="18"/>
       <c r="C607" s="18"/>
       <c r="D607" s="18"/>
@@ -17402,7 +17446,7 @@
       <c r="V607" s="20"/>
     </row>
     <row r="608" ht="19.5" customHeight="1">
-      <c r="A608" s="10"/>
+      <c r="A608" s="8"/>
       <c r="B608" s="18"/>
       <c r="C608" s="18"/>
       <c r="D608" s="18"/>
@@ -17426,7 +17470,7 @@
       <c r="V608" s="20"/>
     </row>
     <row r="609" ht="19.5" customHeight="1">
-      <c r="A609" s="10"/>
+      <c r="A609" s="8"/>
       <c r="B609" s="18"/>
       <c r="C609" s="18"/>
       <c r="D609" s="18"/>
@@ -17450,7 +17494,7 @@
       <c r="V609" s="20"/>
     </row>
     <row r="610" ht="19.5" customHeight="1">
-      <c r="A610" s="10"/>
+      <c r="A610" s="8"/>
       <c r="B610" s="18"/>
       <c r="C610" s="18"/>
       <c r="D610" s="18"/>
@@ -17474,7 +17518,7 @@
       <c r="V610" s="20"/>
     </row>
     <row r="611" ht="19.5" customHeight="1">
-      <c r="A611" s="10"/>
+      <c r="A611" s="8"/>
       <c r="B611" s="18"/>
       <c r="C611" s="18"/>
       <c r="D611" s="18"/>
@@ -17498,7 +17542,7 @@
       <c r="V611" s="20"/>
     </row>
     <row r="612" ht="19.5" customHeight="1">
-      <c r="A612" s="10"/>
+      <c r="A612" s="8"/>
       <c r="B612" s="18"/>
       <c r="C612" s="18"/>
       <c r="D612" s="18"/>
@@ -17522,7 +17566,7 @@
       <c r="V612" s="20"/>
     </row>
     <row r="613" ht="19.5" customHeight="1">
-      <c r="A613" s="10"/>
+      <c r="A613" s="8"/>
       <c r="B613" s="18"/>
       <c r="C613" s="18"/>
       <c r="D613" s="18"/>
@@ -17546,7 +17590,7 @@
       <c r="V613" s="20"/>
     </row>
     <row r="614" ht="19.5" customHeight="1">
-      <c r="A614" s="10"/>
+      <c r="A614" s="8"/>
       <c r="B614" s="18"/>
       <c r="C614" s="18"/>
       <c r="D614" s="18"/>
@@ -17570,7 +17614,7 @@
       <c r="V614" s="20"/>
     </row>
     <row r="615" ht="19.5" customHeight="1">
-      <c r="A615" s="10"/>
+      <c r="A615" s="8"/>
       <c r="B615" s="18"/>
       <c r="C615" s="18"/>
       <c r="D615" s="18"/>
@@ -17594,7 +17638,7 @@
       <c r="V615" s="20"/>
     </row>
     <row r="616" ht="19.5" customHeight="1">
-      <c r="A616" s="10"/>
+      <c r="A616" s="8"/>
       <c r="B616" s="18"/>
       <c r="C616" s="18"/>
       <c r="D616" s="18"/>
@@ -17618,7 +17662,7 @@
       <c r="V616" s="20"/>
     </row>
     <row r="617" ht="19.5" customHeight="1">
-      <c r="A617" s="10"/>
+      <c r="A617" s="8"/>
       <c r="B617" s="18"/>
       <c r="C617" s="18"/>
       <c r="D617" s="18"/>
@@ -17642,7 +17686,7 @@
       <c r="V617" s="20"/>
     </row>
     <row r="618" ht="19.5" customHeight="1">
-      <c r="A618" s="10"/>
+      <c r="A618" s="8"/>
       <c r="B618" s="18"/>
       <c r="C618" s="18"/>
       <c r="D618" s="18"/>
@@ -17666,7 +17710,7 @@
       <c r="V618" s="20"/>
     </row>
     <row r="619" ht="19.5" customHeight="1">
-      <c r="A619" s="10"/>
+      <c r="A619" s="8"/>
       <c r="B619" s="18"/>
       <c r="C619" s="18"/>
       <c r="D619" s="18"/>
@@ -17690,7 +17734,7 @@
       <c r="V619" s="20"/>
     </row>
     <row r="620" ht="19.5" customHeight="1">
-      <c r="A620" s="10"/>
+      <c r="A620" s="8"/>
       <c r="B620" s="18"/>
       <c r="C620" s="18"/>
       <c r="D620" s="18"/>
@@ -17714,7 +17758,7 @@
       <c r="V620" s="20"/>
     </row>
     <row r="621" ht="19.5" customHeight="1">
-      <c r="A621" s="10"/>
+      <c r="A621" s="8"/>
       <c r="B621" s="18"/>
       <c r="C621" s="18"/>
       <c r="D621" s="18"/>
@@ -17738,7 +17782,7 @@
       <c r="V621" s="20"/>
     </row>
     <row r="622" ht="19.5" customHeight="1">
-      <c r="A622" s="10"/>
+      <c r="A622" s="8"/>
       <c r="B622" s="18"/>
       <c r="C622" s="18"/>
       <c r="D622" s="18"/>
@@ -17762,7 +17806,7 @@
       <c r="V622" s="20"/>
     </row>
     <row r="623" ht="19.5" customHeight="1">
-      <c r="A623" s="10"/>
+      <c r="A623" s="8"/>
       <c r="B623" s="18"/>
       <c r="C623" s="18"/>
       <c r="D623" s="18"/>
@@ -17786,7 +17830,7 @@
       <c r="V623" s="20"/>
     </row>
     <row r="624" ht="19.5" customHeight="1">
-      <c r="A624" s="10"/>
+      <c r="A624" s="8"/>
       <c r="B624" s="18"/>
       <c r="C624" s="18"/>
       <c r="D624" s="18"/>
@@ -17810,7 +17854,7 @@
       <c r="V624" s="20"/>
     </row>
     <row r="625" ht="19.5" customHeight="1">
-      <c r="A625" s="10"/>
+      <c r="A625" s="8"/>
       <c r="B625" s="18"/>
       <c r="C625" s="18"/>
       <c r="D625" s="18"/>
@@ -17834,7 +17878,7 @@
       <c r="V625" s="20"/>
     </row>
     <row r="626" ht="19.5" customHeight="1">
-      <c r="A626" s="10"/>
+      <c r="A626" s="8"/>
       <c r="B626" s="18"/>
       <c r="C626" s="18"/>
       <c r="D626" s="18"/>
@@ -17858,7 +17902,7 @@
       <c r="V626" s="20"/>
     </row>
     <row r="627" ht="19.5" customHeight="1">
-      <c r="A627" s="10"/>
+      <c r="A627" s="8"/>
       <c r="B627" s="18"/>
       <c r="C627" s="18"/>
       <c r="D627" s="18"/>
@@ -17882,7 +17926,7 @@
       <c r="V627" s="20"/>
     </row>
     <row r="628" ht="19.5" customHeight="1">
-      <c r="A628" s="10"/>
+      <c r="A628" s="8"/>
       <c r="B628" s="18"/>
       <c r="C628" s="18"/>
       <c r="D628" s="18"/>
@@ -17906,7 +17950,7 @@
       <c r="V628" s="20"/>
     </row>
     <row r="629" ht="19.5" customHeight="1">
-      <c r="A629" s="10"/>
+      <c r="A629" s="8"/>
       <c r="B629" s="18"/>
       <c r="C629" s="18"/>
       <c r="D629" s="18"/>
@@ -17930,7 +17974,7 @@
       <c r="V629" s="20"/>
     </row>
     <row r="630" ht="19.5" customHeight="1">
-      <c r="A630" s="10"/>
+      <c r="A630" s="8"/>
       <c r="B630" s="18"/>
       <c r="C630" s="18"/>
       <c r="D630" s="18"/>
@@ -17954,7 +17998,7 @@
       <c r="V630" s="20"/>
     </row>
     <row r="631" ht="19.5" customHeight="1">
-      <c r="A631" s="10"/>
+      <c r="A631" s="8"/>
       <c r="B631" s="18"/>
       <c r="C631" s="18"/>
       <c r="D631" s="18"/>
@@ -17978,7 +18022,7 @@
       <c r="V631" s="20"/>
     </row>
     <row r="632" ht="19.5" customHeight="1">
-      <c r="A632" s="10"/>
+      <c r="A632" s="8"/>
       <c r="B632" s="18"/>
       <c r="C632" s="18"/>
       <c r="D632" s="18"/>
@@ -18002,7 +18046,7 @@
       <c r="V632" s="20"/>
     </row>
     <row r="633" ht="19.5" customHeight="1">
-      <c r="A633" s="10"/>
+      <c r="A633" s="8"/>
       <c r="B633" s="18"/>
       <c r="C633" s="18"/>
       <c r="D633" s="18"/>
@@ -18026,7 +18070,7 @@
       <c r="V633" s="20"/>
     </row>
     <row r="634" ht="19.5" customHeight="1">
-      <c r="A634" s="10"/>
+      <c r="A634" s="8"/>
       <c r="B634" s="18"/>
       <c r="C634" s="18"/>
       <c r="D634" s="18"/>
@@ -18050,7 +18094,7 @@
       <c r="V634" s="20"/>
     </row>
     <row r="635" ht="19.5" customHeight="1">
-      <c r="A635" s="10"/>
+      <c r="A635" s="8"/>
       <c r="B635" s="18"/>
       <c r="C635" s="18"/>
       <c r="D635" s="18"/>
@@ -18074,7 +18118,7 @@
       <c r="V635" s="20"/>
     </row>
     <row r="636" ht="19.5" customHeight="1">
-      <c r="A636" s="10"/>
+      <c r="A636" s="8"/>
       <c r="B636" s="18"/>
       <c r="C636" s="18"/>
       <c r="D636" s="18"/>
@@ -18098,7 +18142,7 @@
       <c r="V636" s="20"/>
     </row>
     <row r="637" ht="19.5" customHeight="1">
-      <c r="A637" s="10"/>
+      <c r="A637" s="8"/>
       <c r="B637" s="18"/>
       <c r="C637" s="18"/>
       <c r="D637" s="18"/>
@@ -18122,7 +18166,7 @@
       <c r="V637" s="20"/>
     </row>
     <row r="638" ht="19.5" customHeight="1">
-      <c r="A638" s="10"/>
+      <c r="A638" s="8"/>
       <c r="B638" s="18"/>
       <c r="C638" s="18"/>
       <c r="D638" s="18"/>
@@ -18146,7 +18190,7 @@
       <c r="V638" s="20"/>
     </row>
     <row r="639" ht="19.5" customHeight="1">
-      <c r="A639" s="10"/>
+      <c r="A639" s="8"/>
       <c r="B639" s="18"/>
       <c r="C639" s="18"/>
       <c r="D639" s="18"/>
@@ -18170,7 +18214,7 @@
       <c r="V639" s="20"/>
     </row>
     <row r="640" ht="19.5" customHeight="1">
-      <c r="A640" s="10"/>
+      <c r="A640" s="8"/>
       <c r="B640" s="18"/>
       <c r="C640" s="18"/>
       <c r="D640" s="18"/>
@@ -18194,7 +18238,7 @@
       <c r="V640" s="20"/>
     </row>
     <row r="641" ht="19.5" customHeight="1">
-      <c r="A641" s="10"/>
+      <c r="A641" s="8"/>
       <c r="B641" s="18"/>
       <c r="C641" s="18"/>
       <c r="D641" s="18"/>
@@ -18218,7 +18262,7 @@
       <c r="V641" s="20"/>
     </row>
     <row r="642" ht="19.5" customHeight="1">
-      <c r="A642" s="10"/>
+      <c r="A642" s="8"/>
       <c r="B642" s="18"/>
       <c r="C642" s="18"/>
       <c r="D642" s="18"/>
@@ -18242,7 +18286,7 @@
       <c r="V642" s="20"/>
     </row>
     <row r="643" ht="19.5" customHeight="1">
-      <c r="A643" s="10"/>
+      <c r="A643" s="8"/>
       <c r="B643" s="18"/>
       <c r="C643" s="18"/>
       <c r="D643" s="18"/>
@@ -18266,7 +18310,7 @@
       <c r="V643" s="20"/>
     </row>
     <row r="644" ht="19.5" customHeight="1">
-      <c r="A644" s="10"/>
+      <c r="A644" s="8"/>
       <c r="B644" s="18"/>
       <c r="C644" s="18"/>
       <c r="D644" s="18"/>
@@ -18290,7 +18334,7 @@
       <c r="V644" s="20"/>
     </row>
     <row r="645" ht="19.5" customHeight="1">
-      <c r="A645" s="10"/>
+      <c r="A645" s="8"/>
       <c r="B645" s="18"/>
       <c r="C645" s="18"/>
       <c r="D645" s="18"/>
@@ -18314,7 +18358,7 @@
       <c r="V645" s="20"/>
     </row>
     <row r="646" ht="19.5" customHeight="1">
-      <c r="A646" s="10"/>
+      <c r="A646" s="8"/>
       <c r="B646" s="18"/>
       <c r="C646" s="18"/>
       <c r="D646" s="18"/>
@@ -18338,7 +18382,7 @@
       <c r="V646" s="20"/>
     </row>
     <row r="647" ht="19.5" customHeight="1">
-      <c r="A647" s="10"/>
+      <c r="A647" s="8"/>
       <c r="B647" s="18"/>
       <c r="C647" s="18"/>
       <c r="D647" s="18"/>
@@ -18362,7 +18406,7 @@
       <c r="V647" s="20"/>
     </row>
     <row r="648" ht="19.5" customHeight="1">
-      <c r="A648" s="10"/>
+      <c r="A648" s="8"/>
       <c r="B648" s="18"/>
       <c r="C648" s="18"/>
       <c r="D648" s="18"/>
@@ -18386,7 +18430,7 @@
       <c r="V648" s="20"/>
     </row>
     <row r="649" ht="19.5" customHeight="1">
-      <c r="A649" s="10"/>
+      <c r="A649" s="8"/>
       <c r="B649" s="18"/>
       <c r="C649" s="18"/>
       <c r="D649" s="18"/>
@@ -18410,7 +18454,7 @@
       <c r="V649" s="20"/>
     </row>
     <row r="650" ht="19.5" customHeight="1">
-      <c r="A650" s="10"/>
+      <c r="A650" s="8"/>
       <c r="B650" s="18"/>
       <c r="C650" s="18"/>
       <c r="D650" s="18"/>
@@ -18434,7 +18478,7 @@
       <c r="V650" s="20"/>
     </row>
     <row r="651" ht="19.5" customHeight="1">
-      <c r="A651" s="10"/>
+      <c r="A651" s="8"/>
       <c r="B651" s="18"/>
       <c r="C651" s="18"/>
       <c r="D651" s="18"/>
@@ -18458,7 +18502,7 @@
       <c r="V651" s="20"/>
     </row>
     <row r="652" ht="19.5" customHeight="1">
-      <c r="A652" s="10"/>
+      <c r="A652" s="8"/>
       <c r="B652" s="18"/>
       <c r="C652" s="18"/>
       <c r="D652" s="18"/>
@@ -18482,7 +18526,7 @@
       <c r="V652" s="20"/>
     </row>
     <row r="653" ht="19.5" customHeight="1">
-      <c r="A653" s="10"/>
+      <c r="A653" s="8"/>
       <c r="B653" s="18"/>
       <c r="C653" s="18"/>
       <c r="D653" s="18"/>
@@ -18506,7 +18550,7 @@
       <c r="V653" s="20"/>
     </row>
     <row r="654" ht="19.5" customHeight="1">
-      <c r="A654" s="10"/>
+      <c r="A654" s="8"/>
       <c r="B654" s="18"/>
       <c r="C654" s="18"/>
       <c r="D654" s="18"/>
@@ -18530,7 +18574,7 @@
       <c r="V654" s="20"/>
     </row>
     <row r="655" ht="19.5" customHeight="1">
-      <c r="A655" s="10"/>
+      <c r="A655" s="8"/>
       <c r="B655" s="18"/>
       <c r="C655" s="18"/>
       <c r="D655" s="18"/>
@@ -18554,7 +18598,7 @@
       <c r="V655" s="20"/>
     </row>
     <row r="656" ht="19.5" customHeight="1">
-      <c r="A656" s="10"/>
+      <c r="A656" s="8"/>
       <c r="B656" s="18"/>
       <c r="C656" s="18"/>
       <c r="D656" s="18"/>
@@ -18578,7 +18622,7 @@
       <c r="V656" s="20"/>
     </row>
     <row r="657" ht="19.5" customHeight="1">
-      <c r="A657" s="10"/>
+      <c r="A657" s="8"/>
       <c r="B657" s="18"/>
       <c r="C657" s="18"/>
       <c r="D657" s="18"/>
@@ -18602,7 +18646,7 @@
       <c r="V657" s="20"/>
     </row>
     <row r="658" ht="19.5" customHeight="1">
-      <c r="A658" s="10"/>
+      <c r="A658" s="8"/>
       <c r="B658" s="18"/>
       <c r="C658" s="18"/>
       <c r="D658" s="18"/>
@@ -18626,7 +18670,7 @@
       <c r="V658" s="20"/>
     </row>
     <row r="659" ht="19.5" customHeight="1">
-      <c r="A659" s="10"/>
+      <c r="A659" s="8"/>
       <c r="B659" s="18"/>
       <c r="C659" s="18"/>
       <c r="D659" s="18"/>
@@ -18650,7 +18694,7 @@
       <c r="V659" s="20"/>
     </row>
     <row r="660" ht="19.5" customHeight="1">
-      <c r="A660" s="10"/>
+      <c r="A660" s="8"/>
       <c r="B660" s="18"/>
       <c r="C660" s="18"/>
       <c r="D660" s="18"/>
@@ -18674,7 +18718,7 @@
       <c r="V660" s="20"/>
     </row>
     <row r="661" ht="19.5" customHeight="1">
-      <c r="A661" s="10"/>
+      <c r="A661" s="8"/>
       <c r="B661" s="18"/>
       <c r="C661" s="18"/>
       <c r="D661" s="18"/>
@@ -18698,7 +18742,7 @@
       <c r="V661" s="20"/>
     </row>
     <row r="662" ht="19.5" customHeight="1">
-      <c r="A662" s="10"/>
+      <c r="A662" s="8"/>
       <c r="B662" s="18"/>
       <c r="C662" s="18"/>
       <c r="D662" s="18"/>
@@ -18722,7 +18766,7 @@
       <c r="V662" s="20"/>
     </row>
     <row r="663" ht="19.5" customHeight="1">
-      <c r="A663" s="10"/>
+      <c r="A663" s="8"/>
       <c r="B663" s="18"/>
       <c r="C663" s="18"/>
       <c r="D663" s="18"/>
@@ -18746,7 +18790,7 @@
       <c r="V663" s="20"/>
     </row>
     <row r="664" ht="19.5" customHeight="1">
-      <c r="A664" s="10"/>
+      <c r="A664" s="8"/>
       <c r="B664" s="18"/>
       <c r="C664" s="18"/>
       <c r="D664" s="18"/>
@@ -18770,7 +18814,7 @@
       <c r="V664" s="20"/>
     </row>
     <row r="665" ht="19.5" customHeight="1">
-      <c r="A665" s="10"/>
+      <c r="A665" s="8"/>
       <c r="B665" s="18"/>
       <c r="C665" s="18"/>
       <c r="D665" s="18"/>
@@ -18794,7 +18838,7 @@
       <c r="V665" s="20"/>
     </row>
     <row r="666" ht="19.5" customHeight="1">
-      <c r="A666" s="10"/>
+      <c r="A666" s="8"/>
       <c r="B666" s="18"/>
       <c r="C666" s="18"/>
       <c r="D666" s="18"/>
@@ -18818,7 +18862,7 @@
       <c r="V666" s="20"/>
     </row>
     <row r="667" ht="19.5" customHeight="1">
-      <c r="A667" s="10"/>
+      <c r="A667" s="8"/>
       <c r="B667" s="18"/>
       <c r="C667" s="18"/>
       <c r="D667" s="18"/>
@@ -18842,7 +18886,7 @@
       <c r="V667" s="20"/>
     </row>
     <row r="668" ht="19.5" customHeight="1">
-      <c r="A668" s="10"/>
+      <c r="A668" s="8"/>
       <c r="B668" s="18"/>
       <c r="C668" s="18"/>
       <c r="D668" s="18"/>
@@ -18866,7 +18910,7 @@
       <c r="V668" s="20"/>
     </row>
     <row r="669" ht="19.5" customHeight="1">
-      <c r="A669" s="10"/>
+      <c r="A669" s="8"/>
       <c r="B669" s="18"/>
       <c r="C669" s="18"/>
       <c r="D669" s="18"/>
@@ -18890,7 +18934,7 @@
       <c r="V669" s="20"/>
     </row>
     <row r="670" ht="19.5" customHeight="1">
-      <c r="A670" s="10"/>
+      <c r="A670" s="8"/>
       <c r="B670" s="18"/>
       <c r="C670" s="18"/>
       <c r="D670" s="18"/>
@@ -18914,7 +18958,7 @@
       <c r="V670" s="20"/>
     </row>
     <row r="671" ht="19.5" customHeight="1">
-      <c r="A671" s="10"/>
+      <c r="A671" s="8"/>
       <c r="B671" s="18"/>
       <c r="C671" s="18"/>
       <c r="D671" s="18"/>
@@ -18938,7 +18982,7 @@
       <c r="V671" s="20"/>
     </row>
     <row r="672" ht="19.5" customHeight="1">
-      <c r="A672" s="10"/>
+      <c r="A672" s="8"/>
       <c r="B672" s="18"/>
       <c r="C672" s="18"/>
       <c r="D672" s="18"/>
@@ -18962,7 +19006,7 @@
       <c r="V672" s="20"/>
     </row>
     <row r="673" ht="19.5" customHeight="1">
-      <c r="A673" s="10"/>
+      <c r="A673" s="8"/>
       <c r="B673" s="18"/>
       <c r="C673" s="18"/>
       <c r="D673" s="18"/>
@@ -18986,7 +19030,7 @@
       <c r="V673" s="20"/>
     </row>
     <row r="674" ht="19.5" customHeight="1">
-      <c r="A674" s="10"/>
+      <c r="A674" s="8"/>
       <c r="B674" s="18"/>
       <c r="C674" s="18"/>
       <c r="D674" s="18"/>
@@ -19010,7 +19054,7 @@
       <c r="V674" s="20"/>
     </row>
     <row r="675" ht="19.5" customHeight="1">
-      <c r="A675" s="10"/>
+      <c r="A675" s="8"/>
       <c r="B675" s="18"/>
       <c r="C675" s="18"/>
       <c r="D675" s="18"/>
@@ -19034,7 +19078,7 @@
       <c r="V675" s="20"/>
     </row>
     <row r="676" ht="19.5" customHeight="1">
-      <c r="A676" s="10"/>
+      <c r="A676" s="8"/>
       <c r="B676" s="18"/>
       <c r="C676" s="18"/>
       <c r="D676" s="18"/>
@@ -19058,7 +19102,7 @@
       <c r="V676" s="20"/>
     </row>
     <row r="677" ht="19.5" customHeight="1">
-      <c r="A677" s="10"/>
+      <c r="A677" s="8"/>
       <c r="B677" s="18"/>
       <c r="C677" s="18"/>
       <c r="D677" s="18"/>
@@ -19082,7 +19126,7 @@
       <c r="V677" s="20"/>
     </row>
     <row r="678" ht="19.5" customHeight="1">
-      <c r="A678" s="10"/>
+      <c r="A678" s="8"/>
       <c r="B678" s="18"/>
       <c r="C678" s="18"/>
       <c r="D678" s="18"/>
@@ -19106,7 +19150,7 @@
       <c r="V678" s="20"/>
     </row>
     <row r="679" ht="19.5" customHeight="1">
-      <c r="A679" s="10"/>
+      <c r="A679" s="8"/>
       <c r="B679" s="18"/>
       <c r="C679" s="18"/>
       <c r="D679" s="18"/>
@@ -19130,7 +19174,7 @@
       <c r="V679" s="20"/>
     </row>
     <row r="680" ht="19.5" customHeight="1">
-      <c r="A680" s="10"/>
+      <c r="A680" s="8"/>
       <c r="B680" s="18"/>
       <c r="C680" s="18"/>
       <c r="D680" s="18"/>
@@ -19154,7 +19198,7 @@
       <c r="V680" s="20"/>
     </row>
     <row r="681" ht="19.5" customHeight="1">
-      <c r="A681" s="10"/>
+      <c r="A681" s="8"/>
       <c r="B681" s="18"/>
       <c r="C681" s="18"/>
       <c r="D681" s="18"/>
@@ -19178,7 +19222,7 @@
       <c r="V681" s="20"/>
     </row>
     <row r="682" ht="19.5" customHeight="1">
-      <c r="A682" s="10"/>
+      <c r="A682" s="8"/>
       <c r="B682" s="18"/>
       <c r="C682" s="18"/>
       <c r="D682" s="18"/>
@@ -19202,7 +19246,7 @@
       <c r="V682" s="20"/>
     </row>
     <row r="683" ht="19.5" customHeight="1">
-      <c r="A683" s="10"/>
+      <c r="A683" s="8"/>
       <c r="B683" s="18"/>
       <c r="C683" s="18"/>
       <c r="D683" s="18"/>
@@ -19226,7 +19270,7 @@
       <c r="V683" s="20"/>
     </row>
     <row r="684" ht="19.5" customHeight="1">
-      <c r="A684" s="10"/>
+      <c r="A684" s="8"/>
       <c r="B684" s="18"/>
       <c r="C684" s="18"/>
       <c r="D684" s="18"/>
@@ -19250,7 +19294,7 @@
       <c r="V684" s="20"/>
     </row>
     <row r="685" ht="19.5" customHeight="1">
-      <c r="A685" s="10"/>
+      <c r="A685" s="8"/>
       <c r="B685" s="18"/>
       <c r="C685" s="18"/>
       <c r="D685" s="18"/>
@@ -19274,7 +19318,7 @@
       <c r="V685" s="20"/>
     </row>
     <row r="686" ht="19.5" customHeight="1">
-      <c r="A686" s="10"/>
+      <c r="A686" s="8"/>
       <c r="B686" s="18"/>
       <c r="C686" s="18"/>
       <c r="D686" s="18"/>
@@ -19298,7 +19342,7 @@
       <c r="V686" s="20"/>
     </row>
     <row r="687" ht="19.5" customHeight="1">
-      <c r="A687" s="10"/>
+      <c r="A687" s="8"/>
       <c r="B687" s="18"/>
       <c r="C687" s="18"/>
       <c r="D687" s="18"/>
@@ -19322,7 +19366,7 @@
       <c r="V687" s="20"/>
     </row>
     <row r="688" ht="19.5" customHeight="1">
-      <c r="A688" s="10"/>
+      <c r="A688" s="8"/>
       <c r="B688" s="18"/>
       <c r="C688" s="18"/>
       <c r="D688" s="18"/>
@@ -19346,7 +19390,7 @@
       <c r="V688" s="20"/>
     </row>
     <row r="689" ht="19.5" customHeight="1">
-      <c r="A689" s="10"/>
+      <c r="A689" s="8"/>
       <c r="B689" s="18"/>
       <c r="C689" s="18"/>
       <c r="D689" s="18"/>
@@ -19370,7 +19414,7 @@
       <c r="V689" s="20"/>
     </row>
     <row r="690" ht="19.5" customHeight="1">
-      <c r="A690" s="10"/>
+      <c r="A690" s="8"/>
       <c r="B690" s="18"/>
       <c r="C690" s="18"/>
       <c r="D690" s="18"/>
@@ -19394,7 +19438,7 @@
       <c r="V690" s="20"/>
     </row>
     <row r="691" ht="19.5" customHeight="1">
-      <c r="A691" s="10"/>
+      <c r="A691" s="8"/>
       <c r="B691" s="18"/>
       <c r="C691" s="18"/>
       <c r="D691" s="18"/>
@@ -19418,7 +19462,7 @@
       <c r="V691" s="20"/>
     </row>
     <row r="692" ht="19.5" customHeight="1">
-      <c r="A692" s="10"/>
+      <c r="A692" s="8"/>
       <c r="B692" s="18"/>
       <c r="C692" s="18"/>
       <c r="D692" s="18"/>
@@ -19442,7 +19486,7 @@
       <c r="V692" s="20"/>
     </row>
     <row r="693" ht="19.5" customHeight="1">
-      <c r="A693" s="10"/>
+      <c r="A693" s="8"/>
       <c r="B693" s="18"/>
       <c r="C693" s="18"/>
       <c r="D693" s="18"/>
@@ -19466,7 +19510,7 @@
       <c r="V693" s="20"/>
     </row>
     <row r="694" ht="19.5" customHeight="1">
-      <c r="A694" s="10"/>
+      <c r="A694" s="8"/>
       <c r="B694" s="18"/>
       <c r="C694" s="18"/>
       <c r="D694" s="18"/>
@@ -19490,7 +19534,7 @@
       <c r="V694" s="20"/>
     </row>
     <row r="695" ht="19.5" customHeight="1">
-      <c r="A695" s="10"/>
+      <c r="A695" s="8"/>
       <c r="B695" s="18"/>
       <c r="C695" s="18"/>
       <c r="D695" s="18"/>
@@ -19514,7 +19558,7 @@
       <c r="V695" s="20"/>
     </row>
     <row r="696" ht="19.5" customHeight="1">
-      <c r="A696" s="10"/>
+      <c r="A696" s="8"/>
       <c r="B696" s="18"/>
       <c r="C696" s="18"/>
       <c r="D696" s="18"/>
@@ -19538,7 +19582,7 @@
       <c r="V696" s="20"/>
     </row>
     <row r="697" ht="19.5" customHeight="1">
-      <c r="A697" s="10"/>
+      <c r="A697" s="8"/>
       <c r="B697" s="18"/>
       <c r="C697" s="18"/>
       <c r="D697" s="18"/>
@@ -19562,7 +19606,7 @@
       <c r="V697" s="20"/>
     </row>
     <row r="698" ht="19.5" customHeight="1">
-      <c r="A698" s="10"/>
+      <c r="A698" s="8"/>
       <c r="B698" s="18"/>
       <c r="C698" s="18"/>
       <c r="D698" s="18"/>
@@ -19586,7 +19630,7 @@
       <c r="V698" s="20"/>
     </row>
     <row r="699" ht="19.5" customHeight="1">
-      <c r="A699" s="10"/>
+      <c r="A699" s="8"/>
       <c r="B699" s="18"/>
       <c r="C699" s="18"/>
       <c r="D699" s="18"/>
@@ -19610,7 +19654,7 @@
       <c r="V699" s="20"/>
     </row>
     <row r="700" ht="19.5" customHeight="1">
-      <c r="A700" s="10"/>
+      <c r="A700" s="8"/>
       <c r="B700" s="18"/>
       <c r="C700" s="18"/>
       <c r="D700" s="18"/>
@@ -19634,7 +19678,7 @@
       <c r="V700" s="20"/>
     </row>
     <row r="701" ht="19.5" customHeight="1">
-      <c r="A701" s="10"/>
+      <c r="A701" s="8"/>
       <c r="B701" s="18"/>
       <c r="C701" s="18"/>
       <c r="D701" s="18"/>
@@ -19658,7 +19702,7 @@
       <c r="V701" s="20"/>
     </row>
     <row r="702" ht="19.5" customHeight="1">
-      <c r="A702" s="10"/>
+      <c r="A702" s="8"/>
       <c r="B702" s="18"/>
       <c r="C702" s="18"/>
       <c r="D702" s="18"/>
@@ -19682,7 +19726,7 @@
       <c r="V702" s="20"/>
     </row>
     <row r="703" ht="19.5" customHeight="1">
-      <c r="A703" s="10"/>
+      <c r="A703" s="8"/>
       <c r="B703" s="18"/>
       <c r="C703" s="18"/>
       <c r="D703" s="18"/>
@@ -19706,7 +19750,7 @@
       <c r="V703" s="20"/>
     </row>
     <row r="704" ht="19.5" customHeight="1">
-      <c r="A704" s="10"/>
+      <c r="A704" s="8"/>
       <c r="B704" s="18"/>
       <c r="C704" s="18"/>
       <c r="D704" s="18"/>
@@ -19730,7 +19774,7 @@
       <c r="V704" s="20"/>
     </row>
     <row r="705" ht="19.5" customHeight="1">
-      <c r="A705" s="10"/>
+      <c r="A705" s="8"/>
       <c r="B705" s="18"/>
       <c r="C705" s="18"/>
       <c r="D705" s="18"/>
@@ -19754,7 +19798,7 @@
       <c r="V705" s="20"/>
     </row>
     <row r="706" ht="19.5" customHeight="1">
-      <c r="A706" s="10"/>
+      <c r="A706" s="8"/>
       <c r="B706" s="18"/>
       <c r="C706" s="18"/>
       <c r="D706" s="18"/>
@@ -19778,7 +19822,7 @@
       <c r="V706" s="20"/>
     </row>
     <row r="707" ht="19.5" customHeight="1">
-      <c r="A707" s="10"/>
+      <c r="A707" s="8"/>
       <c r="B707" s="18"/>
       <c r="C707" s="18"/>
       <c r="D707" s="18"/>
@@ -19802,7 +19846,7 @@
       <c r="V707" s="20"/>
     </row>
     <row r="708" ht="19.5" customHeight="1">
-      <c r="A708" s="10"/>
+      <c r="A708" s="8"/>
       <c r="B708" s="18"/>
       <c r="C708" s="18"/>
       <c r="D708" s="18"/>
@@ -19826,7 +19870,7 @@
       <c r="V708" s="20"/>
     </row>
     <row r="709" ht="19.5" customHeight="1">
-      <c r="A709" s="10"/>
+      <c r="A709" s="8"/>
       <c r="B709" s="18"/>
       <c r="C709" s="18"/>
       <c r="D709" s="18"/>
@@ -19850,7 +19894,7 @@
       <c r="V709" s="20"/>
     </row>
     <row r="710" ht="19.5" customHeight="1">
-      <c r="A710" s="10"/>
+      <c r="A710" s="8"/>
       <c r="B710" s="18"/>
       <c r="C710" s="18"/>
       <c r="D710" s="18"/>
@@ -19874,7 +19918,7 @@
       <c r="V710" s="20"/>
     </row>
     <row r="711" ht="19.5" customHeight="1">
-      <c r="A711" s="10"/>
+      <c r="A711" s="8"/>
       <c r="B711" s="18"/>
       <c r="C711" s="18"/>
       <c r="D711" s="18"/>
@@ -19898,7 +19942,7 @@
       <c r="V711" s="20"/>
     </row>
     <row r="712" ht="19.5" customHeight="1">
-      <c r="A712" s="10"/>
+      <c r="A712" s="8"/>
       <c r="B712" s="18"/>
       <c r="C712" s="18"/>
       <c r="D712" s="18"/>
@@ -19922,7 +19966,7 @@
       <c r="V712" s="20"/>
     </row>
     <row r="713" ht="19.5" customHeight="1">
-      <c r="A713" s="10"/>
+      <c r="A713" s="8"/>
       <c r="B713" s="18"/>
       <c r="C713" s="18"/>
       <c r="D713" s="18"/>
@@ -19946,7 +19990,7 @@
       <c r="V713" s="20"/>
     </row>
     <row r="714" ht="19.5" customHeight="1">
-      <c r="A714" s="10"/>
+      <c r="A714" s="8"/>
       <c r="B714" s="18"/>
       <c r="C714" s="18"/>
       <c r="D714" s="18"/>
@@ -19970,7 +20014,7 @@
       <c r="V714" s="20"/>
     </row>
     <row r="715" ht="19.5" customHeight="1">
-      <c r="A715" s="10"/>
+      <c r="A715" s="8"/>
       <c r="B715" s="18"/>
       <c r="C715" s="18"/>
       <c r="D715" s="18"/>
@@ -19994,7 +20038,7 @@
       <c r="V715" s="20"/>
     </row>
     <row r="716" ht="19.5" customHeight="1">
-      <c r="A716" s="10"/>
+      <c r="A716" s="8"/>
       <c r="B716" s="18"/>
       <c r="C716" s="18"/>
       <c r="D716" s="18"/>
@@ -20018,7 +20062,7 @@
       <c r="V716" s="20"/>
     </row>
     <row r="717" ht="19.5" customHeight="1">
-      <c r="A717" s="10"/>
+      <c r="A717" s="8"/>
       <c r="B717" s="18"/>
       <c r="C717" s="18"/>
       <c r="D717" s="18"/>
@@ -20042,7 +20086,7 @@
       <c r="V717" s="20"/>
     </row>
     <row r="718" ht="19.5" customHeight="1">
-      <c r="A718" s="10"/>
+      <c r="A718" s="8"/>
       <c r="B718" s="18"/>
       <c r="C718" s="18"/>
       <c r="D718" s="18"/>
@@ -20066,7 +20110,7 @@
       <c r="V718" s="20"/>
     </row>
     <row r="719" ht="19.5" customHeight="1">
-      <c r="A719" s="10"/>
+      <c r="A719" s="8"/>
       <c r="B719" s="18"/>
       <c r="C719" s="18"/>
       <c r="D719" s="18"/>
@@ -20090,7 +20134,7 @@
       <c r="V719" s="20"/>
     </row>
     <row r="720" ht="19.5" customHeight="1">
-      <c r="A720" s="10"/>
+      <c r="A720" s="8"/>
       <c r="B720" s="18"/>
       <c r="C720" s="18"/>
       <c r="D720" s="18"/>
@@ -20114,7 +20158,7 @@
       <c r="V720" s="20"/>
     </row>
     <row r="721" ht="19.5" customHeight="1">
-      <c r="A721" s="10"/>
+      <c r="A721" s="8"/>
       <c r="B721" s="18"/>
       <c r="C721" s="18"/>
       <c r="D721" s="18"/>
@@ -20138,7 +20182,7 @@
       <c r="V721" s="20"/>
     </row>
     <row r="722" ht="19.5" customHeight="1">
-      <c r="A722" s="10"/>
+      <c r="A722" s="8"/>
       <c r="B722" s="18"/>
       <c r="C722" s="18"/>
       <c r="D722" s="18"/>
@@ -20162,7 +20206,7 @@
       <c r="V722" s="20"/>
     </row>
     <row r="723" ht="19.5" customHeight="1">
-      <c r="A723" s="10"/>
+      <c r="A723" s="8"/>
       <c r="B723" s="18"/>
       <c r="C723" s="18"/>
       <c r="D723" s="18"/>
@@ -20186,7 +20230,7 @@
       <c r="V723" s="20"/>
     </row>
     <row r="724" ht="19.5" customHeight="1">
-      <c r="A724" s="10"/>
+      <c r="A724" s="8"/>
       <c r="B724" s="18"/>
       <c r="C724" s="18"/>
       <c r="D724" s="18"/>
@@ -20210,7 +20254,7 @@
       <c r="V724" s="20"/>
     </row>
     <row r="725" ht="19.5" customHeight="1">
-      <c r="A725" s="10"/>
+      <c r="A725" s="8"/>
       <c r="B725" s="18"/>
       <c r="C725" s="18"/>
       <c r="D725" s="18"/>
@@ -20234,7 +20278,7 @@
       <c r="V725" s="20"/>
     </row>
     <row r="726" ht="19.5" customHeight="1">
-      <c r="A726" s="10"/>
+      <c r="A726" s="8"/>
       <c r="B726" s="18"/>
       <c r="C726" s="18"/>
       <c r="D726" s="18"/>
@@ -20258,7 +20302,7 @@
       <c r="V726" s="20"/>
     </row>
     <row r="727" ht="19.5" customHeight="1">
-      <c r="A727" s="10"/>
+      <c r="A727" s="8"/>
       <c r="B727" s="18"/>
       <c r="C727" s="18"/>
       <c r="D727" s="18"/>
@@ -20282,7 +20326,7 @@
       <c r="V727" s="20"/>
     </row>
     <row r="728" ht="19.5" customHeight="1">
-      <c r="A728" s="10"/>
+      <c r="A728" s="8"/>
       <c r="B728" s="18"/>
       <c r="C728" s="18"/>
       <c r="D728" s="18"/>
@@ -20306,7 +20350,7 @@
       <c r="V728" s="20"/>
     </row>
     <row r="729" ht="19.5" customHeight="1">
-      <c r="A729" s="10"/>
+      <c r="A729" s="8"/>
       <c r="B729" s="18"/>
       <c r="C729" s="18"/>
       <c r="D729" s="18"/>
@@ -20330,7 +20374,7 @@
       <c r="V729" s="20"/>
     </row>
     <row r="730" ht="19.5" customHeight="1">
-      <c r="A730" s="10"/>
+      <c r="A730" s="8"/>
       <c r="B730" s="18"/>
       <c r="C730" s="18"/>
       <c r="D730" s="18"/>
@@ -20354,7 +20398,7 @@
       <c r="V730" s="20"/>
     </row>
     <row r="731" ht="19.5" customHeight="1">
-      <c r="A731" s="10"/>
+      <c r="A731" s="8"/>
       <c r="B731" s="18"/>
       <c r="C731" s="18"/>
       <c r="D731" s="18"/>
@@ -20378,7 +20422,7 @@
       <c r="V731" s="20"/>
     </row>
     <row r="732" ht="19.5" customHeight="1">
-      <c r="A732" s="10"/>
+      <c r="A732" s="8"/>
       <c r="B732" s="18"/>
       <c r="C732" s="18"/>
       <c r="D732" s="18"/>
@@ -20402,7 +20446,7 @@
       <c r="V732" s="20"/>
     </row>
     <row r="733" ht="19.5" customHeight="1">
-      <c r="A733" s="10"/>
+      <c r="A733" s="8"/>
       <c r="B733" s="18"/>
       <c r="C733" s="18"/>
       <c r="D733" s="18"/>
@@ -20426,7 +20470,7 @@
       <c r="V733" s="20"/>
     </row>
     <row r="734" ht="19.5" customHeight="1">
-      <c r="A734" s="10"/>
+      <c r="A734" s="8"/>
       <c r="B734" s="18"/>
       <c r="C734" s="18"/>
       <c r="D734" s="18"/>
@@ -20450,7 +20494,7 @@
       <c r="V734" s="20"/>
     </row>
     <row r="735" ht="19.5" customHeight="1">
-      <c r="A735" s="10"/>
+      <c r="A735" s="8"/>
       <c r="B735" s="18"/>
       <c r="C735" s="18"/>
       <c r="D735" s="18"/>
@@ -20474,7 +20518,7 @@
       <c r="V735" s="20"/>
     </row>
     <row r="736" ht="19.5" customHeight="1">
-      <c r="A736" s="10"/>
+      <c r="A736" s="8"/>
       <c r="B736" s="18"/>
       <c r="C736" s="18"/>
       <c r="D736" s="18"/>
@@ -20498,7 +20542,7 @@
       <c r="V736" s="20"/>
     </row>
     <row r="737" ht="19.5" customHeight="1">
-      <c r="A737" s="10"/>
+      <c r="A737" s="8"/>
       <c r="B737" s="18"/>
       <c r="C737" s="18"/>
       <c r="D737" s="18"/>
@@ -20522,7 +20566,7 @@
       <c r="V737" s="20"/>
     </row>
     <row r="738" ht="19.5" customHeight="1">
-      <c r="A738" s="10"/>
+      <c r="A738" s="8"/>
       <c r="B738" s="18"/>
       <c r="C738" s="18"/>
       <c r="D738" s="18"/>
@@ -20546,7 +20590,7 @@
       <c r="V738" s="20"/>
     </row>
     <row r="739" ht="19.5" customHeight="1">
-      <c r="A739" s="10"/>
+      <c r="A739" s="8"/>
       <c r="B739" s="18"/>
       <c r="C739" s="18"/>
       <c r="D739" s="18"/>
@@ -20570,7 +20614,7 @@
       <c r="V739" s="20"/>
     </row>
     <row r="740" ht="19.5" customHeight="1">
-      <c r="A740" s="10"/>
+      <c r="A740" s="8"/>
       <c r="B740" s="18"/>
       <c r="C740" s="18"/>
       <c r="D740" s="18"/>
@@ -20594,7 +20638,7 @@
       <c r="V740" s="20"/>
     </row>
     <row r="741" ht="19.5" customHeight="1">
-      <c r="A741" s="10"/>
+      <c r="A741" s="8"/>
       <c r="B741" s="18"/>
       <c r="C741" s="18"/>
       <c r="D741" s="18"/>
@@ -20618,7 +20662,7 @@
       <c r="V741" s="20"/>
     </row>
     <row r="742" ht="19.5" customHeight="1">
-      <c r="A742" s="10"/>
+      <c r="A742" s="8"/>
       <c r="B742" s="18"/>
       <c r="C742" s="18"/>
       <c r="D742" s="18"/>
@@ -20642,7 +20686,7 @@
       <c r="V742" s="20"/>
     </row>
     <row r="743" ht="19.5" customHeight="1">
-      <c r="A743" s="10"/>
+      <c r="A743" s="8"/>
       <c r="B743" s="18"/>
       <c r="C743" s="18"/>
       <c r="D743" s="18"/>
@@ -20666,7 +20710,7 @@
       <c r="V743" s="20"/>
     </row>
     <row r="744" ht="19.5" customHeight="1">
-      <c r="A744" s="10"/>
+      <c r="A744" s="8"/>
       <c r="B744" s="18"/>
       <c r="C744" s="18"/>
       <c r="D744" s="18"/>
@@ -20690,7 +20734,7 @@
       <c r="V744" s="20"/>
     </row>
     <row r="745" ht="19.5" customHeight="1">
-      <c r="A745" s="10"/>
+      <c r="A745" s="8"/>
       <c r="B745" s="18"/>
       <c r="C745" s="18"/>
       <c r="D745" s="18"/>
@@ -20714,7 +20758,7 @@
       <c r="V745" s="20"/>
     </row>
     <row r="746" ht="19.5" customHeight="1">
-      <c r="A746" s="10"/>
+      <c r="A746" s="8"/>
       <c r="B746" s="18"/>
       <c r="C746" s="18"/>
       <c r="D746" s="18"/>
@@ -20738,7 +20782,7 @@
       <c r="V746" s="20"/>
     </row>
     <row r="747" ht="19.5" customHeight="1">
-      <c r="A747" s="10"/>
+      <c r="A747" s="8"/>
       <c r="B747" s="18"/>
       <c r="C747" s="18"/>
       <c r="D747" s="18"/>
@@ -20762,7 +20806,7 @@
       <c r="V747" s="20"/>
     </row>
     <row r="748" ht="19.5" customHeight="1">
-      <c r="A748" s="10"/>
+      <c r="A748" s="8"/>
       <c r="B748" s="18"/>
       <c r="C748" s="18"/>
       <c r="D748" s="18"/>
@@ -20786,7 +20830,7 @@
       <c r="V748" s="20"/>
     </row>
     <row r="749" ht="19.5" customHeight="1">
-      <c r="A749" s="10"/>
+      <c r="A749" s="8"/>
       <c r="B749" s="18"/>
       <c r="C749" s="18"/>
       <c r="D749" s="18"/>
@@ -20810,7 +20854,7 @@
       <c r="V749" s="20"/>
     </row>
     <row r="750" ht="19.5" customHeight="1">
-      <c r="A750" s="10"/>
+      <c r="A750" s="8"/>
       <c r="B750" s="18"/>
       <c r="C750" s="18"/>
       <c r="D750" s="18"/>
@@ -20834,7 +20878,7 @@
       <c r="V750" s="20"/>
     </row>
     <row r="751" ht="19.5" customHeight="1">
-      <c r="A751" s="10"/>
+      <c r="A751" s="8"/>
       <c r="B751" s="18"/>
       <c r="C751" s="18"/>
       <c r="D751" s="18"/>
@@ -20858,7 +20902,7 @@
       <c r="V751" s="20"/>
     </row>
     <row r="752" ht="19.5" customHeight="1">
-      <c r="A752" s="10"/>
+      <c r="A752" s="8"/>
       <c r="B752" s="18"/>
       <c r="C752" s="18"/>
       <c r="D752" s="18"/>
@@ -20882,7 +20926,7 @@
       <c r="V752" s="20"/>
     </row>
     <row r="753" ht="19.5" customHeight="1">
-      <c r="A753" s="10"/>
+      <c r="A753" s="8"/>
       <c r="B753" s="18"/>
       <c r="C753" s="18"/>
       <c r="D753" s="18"/>
@@ -20906,7 +20950,7 @@
       <c r="V753" s="20"/>
     </row>
     <row r="754" ht="19.5" customHeight="1">
-      <c r="A754" s="10"/>
+      <c r="A754" s="8"/>
       <c r="B754" s="18"/>
       <c r="C754" s="18"/>
       <c r="D754" s="18"/>
@@ -20930,7 +20974,7 @@
       <c r="V754" s="20"/>
     </row>
     <row r="755" ht="19.5" customHeight="1">
-      <c r="A755" s="10"/>
+      <c r="A755" s="8"/>
       <c r="B755" s="18"/>
       <c r="C755" s="18"/>
       <c r="D755" s="18"/>
@@ -20954,7 +20998,7 @@
       <c r="V755" s="20"/>
     </row>
     <row r="756" ht="19.5" customHeight="1">
-      <c r="A756" s="10"/>
+      <c r="A756" s="8"/>
       <c r="B756" s="18"/>
       <c r="C756" s="18"/>
       <c r="D756" s="18"/>
@@ -20978,7 +21022,7 @@
       <c r="V756" s="20"/>
     </row>
     <row r="757" ht="19.5" customHeight="1">
-      <c r="A757" s="10"/>
+      <c r="A757" s="8"/>
       <c r="B757" s="18"/>
       <c r="C757" s="18"/>
       <c r="D757" s="18"/>
@@ -21002,7 +21046,7 @@
       <c r="V757" s="20"/>
     </row>
     <row r="758" ht="19.5" customHeight="1">
-      <c r="A758" s="10"/>
+      <c r="A758" s="8"/>
       <c r="B758" s="18"/>
       <c r="C758" s="18"/>
       <c r="D758" s="18"/>
@@ -21026,7 +21070,7 @@
       <c r="V758" s="20"/>
     </row>
     <row r="759" ht="19.5" customHeight="1">
-      <c r="A759" s="10"/>
+      <c r="A759" s="8"/>
       <c r="B759" s="18"/>
       <c r="C759" s="18"/>
       <c r="D759" s="18"/>
@@ -21050,7 +21094,7 @@
       <c r="V759" s="20"/>
     </row>
     <row r="760" ht="19.5" customHeight="1">
-      <c r="A760" s="10"/>
+      <c r="A760" s="8"/>
       <c r="B760" s="18"/>
       <c r="C760" s="18"/>
       <c r="D760" s="18"/>
@@ -21074,7 +21118,7 @@
       <c r="V760" s="20"/>
     </row>
     <row r="761" ht="19.5" customHeight="1">
-      <c r="A761" s="10"/>
+      <c r="A761" s="8"/>
       <c r="B761" s="18"/>
       <c r="C761" s="18"/>
       <c r="D761" s="18"/>
@@ -21098,7 +21142,7 @@
       <c r="V761" s="20"/>
     </row>
     <row r="762" ht="19.5" customHeight="1">
-      <c r="A762" s="10"/>
+      <c r="A762" s="8"/>
       <c r="B762" s="18"/>
       <c r="C762" s="18"/>
       <c r="D762" s="18"/>
@@ -21122,7 +21166,7 @@
       <c r="V762" s="20"/>
     </row>
     <row r="763" ht="19.5" customHeight="1">
-      <c r="A763" s="10"/>
+      <c r="A763" s="8"/>
       <c r="B763" s="18"/>
       <c r="C763" s="18"/>
       <c r="D763" s="18"/>
@@ -21146,7 +21190,7 @@
       <c r="V763" s="20"/>
     </row>
     <row r="764" ht="19.5" customHeight="1">
-      <c r="A764" s="10"/>
+      <c r="A764" s="8"/>
       <c r="B764" s="18"/>
       <c r="C764" s="18"/>
       <c r="D764" s="18"/>
@@ -21170,7 +21214,7 @@
       <c r="V764" s="20"/>
     </row>
     <row r="765" ht="19.5" customHeight="1">
-      <c r="A765" s="10"/>
+      <c r="A765" s="8"/>
       <c r="B765" s="18"/>
       <c r="C765" s="18"/>
       <c r="D765" s="18"/>
@@ -21194,7 +21238,7 @@
       <c r="V765" s="20"/>
     </row>
     <row r="766" ht="19.5" customHeight="1">
-      <c r="A766" s="10"/>
+      <c r="A766" s="8"/>
       <c r="B766" s="18"/>
       <c r="C766" s="18"/>
       <c r="D766" s="18"/>
@@ -21218,7 +21262,7 @@
       <c r="V766" s="20"/>
     </row>
     <row r="767" ht="19.5" customHeight="1">
-      <c r="A767" s="10"/>
+      <c r="A767" s="8"/>
       <c r="B767" s="18"/>
       <c r="C767" s="18"/>
       <c r="D767" s="18"/>
@@ -21242,7 +21286,7 @@
       <c r="V767" s="20"/>
     </row>
     <row r="768" ht="19.5" customHeight="1">
-      <c r="A768" s="10"/>
+      <c r="A768" s="8"/>
       <c r="B768" s="18"/>
       <c r="C768" s="18"/>
       <c r="D768" s="18"/>
@@ -21266,7 +21310,7 @@
       <c r="V768" s="20"/>
     </row>
     <row r="769" ht="19.5" customHeight="1">
-      <c r="A769" s="10"/>
+      <c r="A769" s="8"/>
       <c r="B769" s="18"/>
       <c r="C769" s="18"/>
       <c r="D769" s="18"/>
@@ -21290,7 +21334,7 @@
       <c r="V769" s="20"/>
     </row>
     <row r="770" ht="19.5" customHeight="1">
-      <c r="A770" s="10"/>
+      <c r="A770" s="8"/>
       <c r="B770" s="18"/>
       <c r="C770" s="18"/>
       <c r="D770" s="18"/>
@@ -21314,7 +21358,7 @@
       <c r="V770" s="20"/>
     </row>
     <row r="771" ht="19.5" customHeight="1">
-      <c r="A771" s="10"/>
+      <c r="A771" s="8"/>
       <c r="B771" s="18"/>
       <c r="C771" s="18"/>
       <c r="D771" s="18"/>
@@ -21338,7 +21382,7 @@
       <c r="V771" s="20"/>
     </row>
     <row r="772" ht="19.5" customHeight="1">
-      <c r="A772" s="10"/>
+      <c r="A772" s="8"/>
       <c r="B772" s="18"/>
       <c r="C772" s="18"/>
       <c r="D772" s="18"/>
@@ -21362,7 +21406,7 @@
       <c r="V772" s="20"/>
     </row>
     <row r="773" ht="19.5" customHeight="1">
-      <c r="A773" s="10"/>
+      <c r="A773" s="8"/>
       <c r="B773" s="18"/>
       <c r="C773" s="18"/>
       <c r="D773" s="18"/>
@@ -21386,7 +21430,7 @@
       <c r="V773" s="20"/>
     </row>
     <row r="774" ht="19.5" customHeight="1">
-      <c r="A774" s="10"/>
+      <c r="A774" s="8"/>
       <c r="B774" s="18"/>
       <c r="C774" s="18"/>
       <c r="D774" s="18"/>
@@ -21410,7 +21454,7 @@
       <c r="V774" s="20"/>
     </row>
     <row r="775" ht="19.5" customHeight="1">
-      <c r="A775" s="10"/>
+      <c r="A775" s="8"/>
       <c r="B775" s="18"/>
       <c r="C775" s="18"/>
       <c r="D775" s="18"/>
@@ -21434,7 +21478,7 @@
       <c r="V775" s="20"/>
     </row>
     <row r="776" ht="19.5" customHeight="1">
-      <c r="A776" s="10"/>
+      <c r="A776" s="8"/>
       <c r="B776" s="18"/>
       <c r="C776" s="18"/>
       <c r="D776" s="18"/>
@@ -21458,7 +21502,7 @@
       <c r="V776" s="20"/>
     </row>
     <row r="777" ht="19.5" customHeight="1">
-      <c r="A777" s="10"/>
+      <c r="A777" s="8"/>
       <c r="B777" s="18"/>
       <c r="C777" s="18"/>
       <c r="D777" s="18"/>
@@ -21482,7 +21526,7 @@
       <c r="V777" s="20"/>
     </row>
     <row r="778" ht="19.5" customHeight="1">
-      <c r="A778" s="10"/>
+      <c r="A778" s="8"/>
       <c r="B778" s="18"/>
       <c r="C778" s="18"/>
       <c r="D778" s="18"/>
@@ -21506,7 +21550,7 @@
       <c r="V778" s="20"/>
     </row>
     <row r="779" ht="19.5" customHeight="1">
-      <c r="A779" s="10"/>
+      <c r="A779" s="8"/>
       <c r="B779" s="18"/>
       <c r="C779" s="18"/>
       <c r="D779" s="18"/>
@@ -21530,7 +21574,7 @@
       <c r="V779" s="20"/>
     </row>
     <row r="780" ht="19.5" customHeight="1">
-      <c r="A780" s="10"/>
+      <c r="A780" s="8"/>
       <c r="B780" s="18"/>
       <c r="C780" s="18"/>
       <c r="D780" s="18"/>
@@ -21554,7 +21598,7 @@
       <c r="V780" s="20"/>
     </row>
     <row r="781" ht="19.5" customHeight="1">
-      <c r="A781" s="10"/>
+      <c r="A781" s="8"/>
       <c r="B781" s="18"/>
       <c r="C781" s="18"/>
       <c r="D781" s="18"/>
@@ -21578,7 +21622,7 @@
       <c r="V781" s="20"/>
     </row>
     <row r="782" ht="19.5" customHeight="1">
-      <c r="A782" s="10"/>
+      <c r="A782" s="8"/>
       <c r="B782" s="18"/>
       <c r="C782" s="18"/>
       <c r="D782" s="18"/>
@@ -21602,7 +21646,7 @@
       <c r="V782" s="20"/>
     </row>
     <row r="783" ht="19.5" customHeight="1">
-      <c r="A783" s="10"/>
+      <c r="A783" s="8"/>
       <c r="B783" s="18"/>
       <c r="C783" s="18"/>
       <c r="D783" s="18"/>
@@ -21626,7 +21670,7 @@
       <c r="V783" s="20"/>
     </row>
     <row r="784" ht="19.5" customHeight="1">
-      <c r="A784" s="10"/>
+      <c r="A784" s="8"/>
       <c r="B784" s="18"/>
       <c r="C784" s="18"/>
       <c r="D784" s="18"/>
@@ -21650,7 +21694,7 @@
       <c r="V784" s="20"/>
     </row>
     <row r="785" ht="19.5" customHeight="1">
-      <c r="A785" s="10"/>
+      <c r="A785" s="8"/>
       <c r="B785" s="18"/>
       <c r="C785" s="18"/>
       <c r="D785" s="18"/>
@@ -21674,7 +21718,7 @@
       <c r="V785" s="20"/>
     </row>
     <row r="786" ht="19.5" customHeight="1">
-      <c r="A786" s="10"/>
+      <c r="A786" s="8"/>
       <c r="B786" s="18"/>
       <c r="C786" s="18"/>
       <c r="D786" s="18"/>
@@ -21698,7 +21742,7 @@
       <c r="V786" s="20"/>
     </row>
     <row r="787" ht="19.5" customHeight="1">
-      <c r="A787" s="10"/>
+      <c r="A787" s="8"/>
       <c r="B787" s="18"/>
       <c r="C787" s="18"/>
       <c r="D787" s="18"/>
@@ -21722,7 +21766,7 @@
       <c r="V787" s="20"/>
     </row>
     <row r="788" ht="19.5" customHeight="1">
-      <c r="A788" s="10"/>
+      <c r="A788" s="8"/>
       <c r="B788" s="18"/>
       <c r="C788" s="18"/>
       <c r="D788" s="18"/>
@@ -21746,7 +21790,7 @@
       <c r="V788" s="20"/>
     </row>
     <row r="789" ht="19.5" customHeight="1">
-      <c r="A789" s="10"/>
+      <c r="A789" s="8"/>
       <c r="B789" s="18"/>
       <c r="C789" s="18"/>
       <c r="D789" s="18"/>
@@ -21770,7 +21814,7 @@
       <c r="V789" s="20"/>
     </row>
     <row r="790" ht="19.5" customHeight="1">
-      <c r="A790" s="10"/>
+      <c r="A790" s="8"/>
       <c r="B790" s="18"/>
       <c r="C790" s="18"/>
       <c r="D790" s="18"/>
@@ -21794,7 +21838,7 @@
       <c r="V790" s="20"/>
     </row>
     <row r="791" ht="19.5" customHeight="1">
-      <c r="A791" s="10"/>
+      <c r="A791" s="8"/>
       <c r="B791" s="18"/>
       <c r="C791" s="18"/>
       <c r="D791" s="18"/>
@@ -21818,7 +21862,7 @@
       <c r="V791" s="20"/>
     </row>
     <row r="792" ht="19.5" customHeight="1">
-      <c r="A792" s="10"/>
+      <c r="A792" s="8"/>
       <c r="B792" s="18"/>
       <c r="C792" s="18"/>
       <c r="D792" s="18"/>
@@ -21842,7 +21886,7 @@
       <c r="V792" s="20"/>
     </row>
     <row r="793" ht="19.5" customHeight="1">
-      <c r="A793" s="10"/>
+      <c r="A793" s="8"/>
       <c r="B793" s="18"/>
       <c r="C793" s="18"/>
       <c r="D793" s="18"/>
@@ -21866,7 +21910,7 @@
       <c r="V793" s="20"/>
     </row>
     <row r="794" ht="19.5" customHeight="1">
-      <c r="A794" s="10"/>
+      <c r="A794" s="8"/>
       <c r="B794" s="18"/>
       <c r="C794" s="18"/>
       <c r="D794" s="18"/>
@@ -21890,7 +21934,7 @@
       <c r="V794" s="20"/>
     </row>
     <row r="795" ht="19.5" customHeight="1">
-      <c r="A795" s="10"/>
+      <c r="A795" s="8"/>
       <c r="B795" s="18"/>
       <c r="C795" s="18"/>
       <c r="D795" s="18"/>
@@ -21914,7 +21958,7 @@
       <c r="V795" s="20"/>
     </row>
     <row r="796" ht="19.5" customHeight="1">
-      <c r="A796" s="10"/>
+      <c r="A796" s="8"/>
       <c r="B796" s="18"/>
       <c r="C796" s="18"/>
       <c r="D796" s="18"/>
@@ -21938,7 +21982,7 @@
       <c r="V796" s="20"/>
     </row>
     <row r="797" ht="19.5" customHeight="1">
-      <c r="A797" s="10"/>
+      <c r="A797" s="8"/>
       <c r="B797" s="18"/>
       <c r="C797" s="18"/>
       <c r="D797" s="18"/>
@@ -21962,7 +22006,7 @@
       <c r="V797" s="20"/>
     </row>
     <row r="798" ht="19.5" customHeight="1">
-      <c r="A798" s="10"/>
+      <c r="A798" s="8"/>
       <c r="B798" s="18"/>
       <c r="C798" s="18"/>
       <c r="D798" s="18"/>
@@ -21986,7 +22030,7 @@
       <c r="V798" s="20"/>
     </row>
     <row r="799" ht="19.5" customHeight="1">
-      <c r="A799" s="10"/>
+      <c r="A799" s="8"/>
       <c r="B799" s="18"/>
       <c r="C799" s="18"/>
       <c r="D799" s="18"/>
@@ -22010,7 +22054,7 @@
       <c r="V799" s="20"/>
     </row>
     <row r="800" ht="19.5" customHeight="1">
-      <c r="A800" s="10"/>
+      <c r="A800" s="8"/>
       <c r="B800" s="18"/>
       <c r="C800" s="18"/>
       <c r="D800" s="18"/>
@@ -22034,7 +22078,7 @@
       <c r="V800" s="20"/>
     </row>
     <row r="801" ht="19.5" customHeight="1">
-      <c r="A801" s="10"/>
+      <c r="A801" s="8"/>
       <c r="B801" s="18"/>
       <c r="C801" s="18"/>
       <c r="D801" s="18"/>
@@ -22058,7 +22102,7 @@
       <c r="V801" s="20"/>
     </row>
     <row r="802" ht="19.5" customHeight="1">
-      <c r="A802" s="10"/>
+      <c r="A802" s="8"/>
       <c r="B802" s="18"/>
       <c r="C802" s="18"/>
       <c r="D802" s="18"/>
@@ -22082,7 +22126,7 @@
       <c r="V802" s="20"/>
     </row>
     <row r="803" ht="19.5" customHeight="1">
-      <c r="A803" s="10"/>
+      <c r="A803" s="8"/>
       <c r="B803" s="18"/>
       <c r="C803" s="18"/>
       <c r="D803" s="18"/>
@@ -22106,7 +22150,7 @@
       <c r="V803" s="20"/>
     </row>
     <row r="804" ht="19.5" customHeight="1">
-      <c r="A804" s="10"/>
+      <c r="A804" s="8"/>
       <c r="B804" s="18"/>
       <c r="C804" s="18"/>
       <c r="D804" s="18"/>
@@ -22130,7 +22174,7 @@
       <c r="V804" s="20"/>
     </row>
     <row r="805" ht="19.5" customHeight="1">
-      <c r="A805" s="10"/>
+      <c r="A805" s="8"/>
       <c r="B805" s="18"/>
       <c r="C805" s="18"/>
       <c r="D805" s="18"/>
@@ -22154,7 +22198,7 @@
       <c r="V805" s="20"/>
     </row>
     <row r="806" ht="19.5" customHeight="1">
-      <c r="A806" s="10"/>
+      <c r="A806" s="8"/>
       <c r="B806" s="18"/>
       <c r="C806" s="18"/>
       <c r="D806" s="18"/>
@@ -22178,7 +22222,7 @@
       <c r="V806" s="20"/>
     </row>
     <row r="807" ht="19.5" customHeight="1">
-      <c r="A807" s="10"/>
+      <c r="A807" s="8"/>
       <c r="B807" s="18"/>
       <c r="C807" s="18"/>
       <c r="D807" s="18"/>
@@ -22202,7 +22246,7 @@
       <c r="V807" s="20"/>
     </row>
     <row r="808" ht="19.5" customHeight="1">
-      <c r="A808" s="10"/>
+      <c r="A808" s="8"/>
       <c r="B808" s="18"/>
       <c r="C808" s="18"/>
       <c r="D808" s="18"/>
@@ -22226,7 +22270,7 @@
       <c r="V808" s="20"/>
     </row>
     <row r="809" ht="19.5" customHeight="1">
-      <c r="A809" s="10"/>
+      <c r="A809" s="8"/>
       <c r="B809" s="18"/>
       <c r="C809" s="18"/>
       <c r="D809" s="18"/>
@@ -22250,7 +22294,7 @@
       <c r="V809" s="20"/>
     </row>
     <row r="810" ht="19.5" customHeight="1">
-      <c r="A810" s="10"/>
+      <c r="A810" s="8"/>
       <c r="B810" s="18"/>
       <c r="C810" s="18"/>
       <c r="D810" s="18"/>
@@ -22274,7 +22318,7 @@
       <c r="V810" s="20"/>
     </row>
     <row r="811" ht="19.5" customHeight="1">
-      <c r="A811" s="10"/>
+      <c r="A811" s="8"/>
       <c r="B811" s="18"/>
       <c r="C811" s="18"/>
       <c r="D811" s="18"/>
@@ -22298,7 +22342,7 @@
       <c r="V811" s="20"/>
     </row>
     <row r="812" ht="19.5" customHeight="1">
-      <c r="A812" s="10"/>
+      <c r="A812" s="8"/>
       <c r="B812" s="18"/>
       <c r="C812" s="18"/>
       <c r="D812" s="18"/>
@@ -22322,7 +22366,7 @@
       <c r="V812" s="20"/>
     </row>
     <row r="813" ht="19.5" customHeight="1">
-      <c r="A813" s="10"/>
+      <c r="A813" s="8"/>
       <c r="B813" s="18"/>
       <c r="C813" s="18"/>
       <c r="D813" s="18"/>
@@ -22346,7 +22390,7 @@
       <c r="V813" s="20"/>
     </row>
     <row r="814" ht="19.5" customHeight="1">
-      <c r="A814" s="10"/>
+      <c r="A814" s="8"/>
       <c r="B814" s="18"/>
       <c r="C814" s="18"/>
       <c r="D814" s="18"/>
@@ -22370,7 +22414,7 @@
       <c r="V814" s="20"/>
     </row>
     <row r="815" ht="19.5" customHeight="1">
-      <c r="A815" s="10"/>
+      <c r="A815" s="8"/>
       <c r="B815" s="18"/>
       <c r="C815" s="18"/>
       <c r="D815" s="18"/>
@@ -22394,7 +22438,7 @@
       <c r="V815" s="20"/>
     </row>
     <row r="816" ht="19.5" customHeight="1">
-      <c r="A816" s="10"/>
+      <c r="A816" s="8"/>
       <c r="B816" s="18"/>
       <c r="C816" s="18"/>
       <c r="D816" s="18"/>
@@ -22418,7 +22462,7 @@
       <c r="V816" s="20"/>
     </row>
     <row r="817" ht="19.5" customHeight="1">
-      <c r="A817" s="10"/>
+      <c r="A817" s="8"/>
       <c r="B817" s="18"/>
       <c r="C817" s="18"/>
       <c r="D817" s="18"/>
@@ -22442,7 +22486,7 @@
       <c r="V817" s="20"/>
     </row>
     <row r="818" ht="19.5" customHeight="1">
-      <c r="A818" s="10"/>
+      <c r="A818" s="8"/>
       <c r="B818" s="18"/>
       <c r="C818" s="18"/>
       <c r="D818" s="18"/>
@@ -22466,7 +22510,7 @@
       <c r="V818" s="20"/>
     </row>
     <row r="819" ht="19.5" customHeight="1">
-      <c r="A819" s="10"/>
+      <c r="A819" s="8"/>
       <c r="B819" s="18"/>
       <c r="C819" s="18"/>
       <c r="D819" s="18"/>
@@ -22490,7 +22534,7 @@
       <c r="V819" s="20"/>
     </row>
     <row r="820" ht="19.5" customHeight="1">
-      <c r="A820" s="10"/>
+      <c r="A820" s="8"/>
       <c r="B820" s="18"/>
       <c r="C820" s="18"/>
       <c r="D820" s="18"/>
@@ -22514,7 +22558,7 @@
       <c r="V820" s="20"/>
     </row>
     <row r="821" ht="19.5" customHeight="1">
-      <c r="A821" s="10"/>
+      <c r="A821" s="8"/>
       <c r="B821" s="18"/>
       <c r="C821" s="18"/>
       <c r="D821" s="18"/>
@@ -22538,7 +22582,7 @@
       <c r="V821" s="20"/>
     </row>
     <row r="822" ht="19.5" customHeight="1">
-      <c r="A822" s="10"/>
+      <c r="A822" s="8"/>
       <c r="B822" s="18"/>
       <c r="C822" s="18"/>
       <c r="D822" s="18"/>
@@ -22562,7 +22606,7 @@
       <c r="V822" s="20"/>
     </row>
     <row r="823" ht="19.5" customHeight="1">
-      <c r="A823" s="10"/>
+      <c r="A823" s="8"/>
       <c r="B823" s="18"/>
       <c r="C823" s="18"/>
       <c r="D823" s="18"/>
@@ -22586,7 +22630,7 @@
       <c r="V823" s="20"/>
     </row>
     <row r="824" ht="19.5" customHeight="1">
-      <c r="A824" s="10"/>
+      <c r="A824" s="8"/>
       <c r="B824" s="18"/>
       <c r="C824" s="18"/>
       <c r="D824" s="18"/>
@@ -22610,7 +22654,7 @@
       <c r="V824" s="20"/>
     </row>
     <row r="825" ht="19.5" customHeight="1">
-      <c r="A825" s="10"/>
+      <c r="A825" s="8"/>
       <c r="B825" s="18"/>
       <c r="C825" s="18"/>
       <c r="D825" s="18"/>
@@ -22634,7 +22678,7 @@
       <c r="V825" s="20"/>
     </row>
     <row r="826" ht="19.5" customHeight="1">
-      <c r="A826" s="10"/>
+      <c r="A826" s="8"/>
       <c r="B826" s="18"/>
       <c r="C826" s="18"/>
       <c r="D826" s="18"/>
@@ -22658,7 +22702,7 @@
       <c r="V826" s="20"/>
     </row>
     <row r="827" ht="19.5" customHeight="1">
-      <c r="A827" s="10"/>
+      <c r="A827" s="8"/>
       <c r="B827" s="18"/>
       <c r="C827" s="18"/>
       <c r="D827" s="18"/>
@@ -22682,7 +22726,7 @@
       <c r="V827" s="20"/>
     </row>
     <row r="828" ht="19.5" customHeight="1">
-      <c r="A828" s="10"/>
+      <c r="A828" s="8"/>
       <c r="B828" s="18"/>
       <c r="C828" s="18"/>
       <c r="D828" s="18"/>
@@ -22706,7 +22750,7 @@
       <c r="V828" s="20"/>
     </row>
     <row r="829" ht="19.5" customHeight="1">
-      <c r="A829" s="10"/>
+      <c r="A829" s="8"/>
       <c r="B829" s="18"/>
       <c r="C829" s="18"/>
       <c r="D829" s="18"/>
@@ -22730,7 +22774,7 @@
       <c r="V829" s="20"/>
     </row>
     <row r="830" ht="19.5" customHeight="1">
-      <c r="A830" s="10"/>
+      <c r="A830" s="8"/>
       <c r="B830" s="18"/>
       <c r="C830" s="18"/>
       <c r="D830" s="18"/>
@@ -22754,7 +22798,7 @@
       <c r="V830" s="20"/>
     </row>
     <row r="831" ht="19.5" customHeight="1">
-      <c r="A831" s="10"/>
+      <c r="A831" s="8"/>
       <c r="B831" s="18"/>
       <c r="C831" s="18"/>
       <c r="D831" s="18"/>
@@ -22778,7 +22822,7 @@
       <c r="V831" s="20"/>
     </row>
     <row r="832" ht="19.5" customHeight="1">
-      <c r="A832" s="10"/>
+      <c r="A832" s="8"/>
       <c r="B832" s="18"/>
       <c r="C832" s="18"/>
       <c r="D832" s="18"/>
@@ -22802,7 +22846,7 @@
       <c r="V832" s="20"/>
     </row>
     <row r="833" ht="19.5" customHeight="1">
-      <c r="A833" s="10"/>
+      <c r="A833" s="8"/>
       <c r="B833" s="18"/>
       <c r="C833" s="18"/>
       <c r="D833" s="18"/>
@@ -22826,7 +22870,7 @@
       <c r="V833" s="20"/>
     </row>
     <row r="834" ht="19.5" customHeight="1">
-      <c r="A834" s="10"/>
+      <c r="A834" s="8"/>
       <c r="B834" s="18"/>
       <c r="C834" s="18"/>
       <c r="D834" s="18"/>
@@ -22850,7 +22894,7 @@
       <c r="V834" s="20"/>
     </row>
     <row r="835" ht="19.5" customHeight="1">
-      <c r="A835" s="10"/>
+      <c r="A835" s="8"/>
       <c r="B835" s="18"/>
       <c r="C835" s="18"/>
       <c r="D835" s="18"/>
@@ -22874,7 +22918,7 @@
       <c r="V835" s="20"/>
     </row>
     <row r="836" ht="19.5" customHeight="1">
-      <c r="A836" s="10"/>
+      <c r="A836" s="8"/>
       <c r="B836" s="18"/>
       <c r="C836" s="18"/>
       <c r="D836" s="18"/>
@@ -22898,7 +22942,7 @@
       <c r="V836" s="20"/>
     </row>
     <row r="837" ht="19.5" customHeight="1">
-      <c r="A837" s="10"/>
+      <c r="A837" s="8"/>
       <c r="B837" s="18"/>
       <c r="C837" s="18"/>
       <c r="D837" s="18"/>
@@ -22922,7 +22966,7 @@
       <c r="V837" s="20"/>
     </row>
     <row r="838" ht="19.5" customHeight="1">
-      <c r="A838" s="10"/>
+      <c r="A838" s="8"/>
       <c r="B838" s="18"/>
       <c r="C838" s="18"/>
       <c r="D838" s="18"/>
@@ -22946,7 +22990,7 @@
       <c r="V838" s="20"/>
     </row>
     <row r="839" ht="19.5" customHeight="1">
-      <c r="A839" s="10"/>
+      <c r="A839" s="8"/>
       <c r="B839" s="18"/>
       <c r="C839" s="18"/>
       <c r="D839" s="18"/>
@@ -22970,7 +23014,7 @@
       <c r="V839" s="20"/>
     </row>
     <row r="840" ht="19.5" customHeight="1">
-      <c r="A840" s="10"/>
+      <c r="A840" s="8"/>
       <c r="B840" s="18"/>
       <c r="C840" s="18"/>
       <c r="D840" s="18"/>
@@ -22994,7 +23038,7 @@
       <c r="V840" s="20"/>
     </row>
     <row r="841" ht="19.5" customHeight="1">
-      <c r="A841" s="10"/>
+      <c r="A841" s="8"/>
       <c r="B841" s="18"/>
       <c r="C841" s="18"/>
       <c r="D841" s="18"/>
@@ -23018,7 +23062,7 @@
       <c r="V841" s="20"/>
     </row>
     <row r="842" ht="19.5" customHeight="1">
-      <c r="A842" s="10"/>
+      <c r="A842" s="8"/>
       <c r="B842" s="18"/>
       <c r="C842" s="18"/>
       <c r="D842" s="18"/>
@@ -23042,7 +23086,7 @@
       <c r="V842" s="20"/>
     </row>
     <row r="843" ht="19.5" customHeight="1">
-      <c r="A843" s="10"/>
+      <c r="A843" s="8"/>
       <c r="B843" s="18"/>
       <c r="C843" s="18"/>
       <c r="D843" s="18"/>
@@ -23066,7 +23110,7 @@
       <c r="V843" s="20"/>
     </row>
     <row r="844" ht="19.5" customHeight="1">
-      <c r="A844" s="10"/>
+      <c r="A844" s="8"/>
       <c r="B844" s="18"/>
       <c r="C844" s="18"/>
       <c r="D844" s="18"/>
@@ -23090,7 +23134,7 @@
       <c r="V844" s="20"/>
     </row>
     <row r="845" ht="19.5" customHeight="1">
-      <c r="A845" s="10"/>
+      <c r="A845" s="8"/>
       <c r="B845" s="18"/>
       <c r="C845" s="18"/>
       <c r="D845" s="18"/>
@@ -23114,7 +23158,7 @@
       <c r="V845" s="20"/>
     </row>
     <row r="846" ht="19.5" customHeight="1">
-      <c r="A846" s="10"/>
+      <c r="A846" s="8"/>
       <c r="B846" s="18"/>
       <c r="C846" s="18"/>
       <c r="D846" s="18"/>
@@ -23138,7 +23182,7 @@
       <c r="V846" s="20"/>
     </row>
     <row r="847" ht="19.5" customHeight="1">
-      <c r="A847" s="10"/>
+      <c r="A847" s="8"/>
       <c r="B847" s="18"/>
       <c r="C847" s="18"/>
       <c r="D847" s="18"/>
@@ -23162,7 +23206,7 @@
       <c r="V847" s="20"/>
     </row>
     <row r="848" ht="19.5" customHeight="1">
-      <c r="A848" s="10"/>
+      <c r="A848" s="8"/>
       <c r="B848" s="18"/>
       <c r="C848" s="18"/>
       <c r="D848" s="18"/>
@@ -23186,7 +23230,7 @@
       <c r="V848" s="20"/>
     </row>
     <row r="849" ht="19.5" customHeight="1">
-      <c r="A849" s="10"/>
+      <c r="A849" s="8"/>
       <c r="B849" s="18"/>
       <c r="C849" s="18"/>
       <c r="D849" s="18"/>
@@ -23210,7 +23254,7 @@
       <c r="V849" s="20"/>
     </row>
     <row r="850" ht="19.5" customHeight="1">
-      <c r="A850" s="10"/>
+      <c r="A850" s="8"/>
       <c r="B850" s="18"/>
       <c r="C850" s="18"/>
       <c r="D850" s="18"/>
@@ -23234,7 +23278,7 @@
       <c r="V850" s="20"/>
     </row>
     <row r="851" ht="19.5" customHeight="1">
-      <c r="A851" s="10"/>
+      <c r="A851" s="8"/>
       <c r="B851" s="18"/>
       <c r="C851" s="18"/>
       <c r="D851" s="18"/>
@@ -23258,7 +23302,7 @@
       <c r="V851" s="20"/>
     </row>
     <row r="852" ht="19.5" customHeight="1">
-      <c r="A852" s="10"/>
+      <c r="A852" s="8"/>
       <c r="B852" s="18"/>
       <c r="C852" s="18"/>
       <c r="D852" s="18"/>
@@ -23282,7 +23326,7 @@
       <c r="V852" s="20"/>
     </row>
     <row r="853" ht="19.5" customHeight="1">
-      <c r="A853" s="10"/>
+      <c r="A853" s="8"/>
       <c r="B853" s="18"/>
       <c r="C853" s="18"/>
       <c r="D853" s="18"/>
@@ -23306,7 +23350,7 @@
       <c r="V853" s="20"/>
     </row>
     <row r="854" ht="19.5" customHeight="1">
-      <c r="A854" s="10"/>
+      <c r="A854" s="8"/>
       <c r="B854" s="18"/>
       <c r="C854" s="18"/>
       <c r="D854" s="18"/>
@@ -23330,7 +23374,7 @@
       <c r="V854" s="20"/>
     </row>
     <row r="855" ht="19.5" customHeight="1">
-      <c r="A855" s="10"/>
+      <c r="A855" s="8"/>
       <c r="B855" s="18"/>
       <c r="C855" s="18"/>
       <c r="D855" s="18"/>
@@ -23354,7 +23398,7 @@
       <c r="V855" s="20"/>
     </row>
     <row r="856" ht="19.5" customHeight="1">
-      <c r="A856" s="10"/>
+      <c r="A856" s="8"/>
       <c r="B856" s="18"/>
       <c r="C856" s="18"/>
       <c r="D856" s="18"/>
@@ -23378,7 +23422,7 @@
       <c r="V856" s="20"/>
     </row>
     <row r="857" ht="19.5" customHeight="1">
-      <c r="A857" s="10"/>
+      <c r="A857" s="8"/>
       <c r="B857" s="18"/>
       <c r="C857" s="18"/>
       <c r="D857" s="18"/>
@@ -23402,7 +23446,7 @@
       <c r="V857" s="20"/>
     </row>
     <row r="858" ht="19.5" customHeight="1">
-      <c r="A858" s="10"/>
+      <c r="A858" s="8"/>
       <c r="B858" s="18"/>
       <c r="C858" s="18"/>
       <c r="D858" s="18"/>
@@ -23426,7 +23470,7 @@
       <c r="V858" s="20"/>
     </row>
     <row r="859" ht="19.5" customHeight="1">
-      <c r="A859" s="10"/>
+      <c r="A859" s="8"/>
       <c r="B859" s="18"/>
       <c r="C859" s="18"/>
       <c r="D859" s="18"/>
@@ -23450,7 +23494,7 @@
       <c r="V859" s="20"/>
     </row>
     <row r="860" ht="19.5" customHeight="1">
-      <c r="A860" s="10"/>
+      <c r="A860" s="8"/>
       <c r="B860" s="18"/>
       <c r="C860" s="18"/>
       <c r="D860" s="18"/>
@@ -23474,7 +23518,7 @@
       <c r="V860" s="20"/>
     </row>
     <row r="861" ht="19.5" customHeight="1">
-      <c r="A861" s="10"/>
+      <c r="A861" s="8"/>
       <c r="B861" s="18"/>
       <c r="C861" s="18"/>
       <c r="D861" s="18"/>
@@ -23498,7 +23542,7 @@
       <c r="V861" s="20"/>
     </row>
     <row r="862" ht="19.5" customHeight="1">
-      <c r="A862" s="10"/>
+      <c r="A862" s="8"/>
       <c r="B862" s="18"/>
       <c r="C862" s="18"/>
       <c r="D862" s="18"/>
@@ -23522,7 +23566,7 @@
       <c r="V862" s="20"/>
     </row>
     <row r="863" ht="19.5" customHeight="1">
-      <c r="A863" s="10"/>
+      <c r="A863" s="8"/>
       <c r="B863" s="18"/>
       <c r="C863" s="18"/>
       <c r="D863" s="18"/>
@@ -23546,7 +23590,7 @@
       <c r="V863" s="20"/>
     </row>
     <row r="864" ht="19.5" customHeight="1">
-      <c r="A864" s="10"/>
+      <c r="A864" s="8"/>
       <c r="B864" s="18"/>
       <c r="C864" s="18"/>
       <c r="D864" s="18"/>
@@ -23570,7 +23614,7 @@
       <c r="V864" s="20"/>
     </row>
     <row r="865" ht="19.5" customHeight="1">
-      <c r="A865" s="10"/>
+      <c r="A865" s="8"/>
       <c r="B865" s="18"/>
       <c r="C865" s="18"/>
       <c r="D865" s="18"/>
@@ -23594,7 +23638,7 @@
       <c r="V865" s="20"/>
     </row>
     <row r="866" ht="19.5" customHeight="1">
-      <c r="A866" s="10"/>
+      <c r="A866" s="8"/>
       <c r="B866" s="18"/>
       <c r="C866" s="18"/>
       <c r="D866" s="18"/>
@@ -23618,7 +23662,7 @@
       <c r="V866" s="20"/>
     </row>
     <row r="867" ht="19.5" customHeight="1">
-      <c r="A867" s="10"/>
+      <c r="A867" s="8"/>
       <c r="B867" s="18"/>
       <c r="C867" s="18"/>
       <c r="D867" s="18"/>
@@ -23642,7 +23686,7 @@
       <c r="V867" s="20"/>
     </row>
     <row r="868" ht="19.5" customHeight="1">
-      <c r="A868" s="10"/>
+      <c r="A868" s="8"/>
       <c r="B868" s="18"/>
       <c r="C868" s="18"/>
       <c r="D868" s="18"/>
@@ -23666,7 +23710,7 @@
       <c r="V868" s="20"/>
     </row>
     <row r="869" ht="19.5" customHeight="1">
-      <c r="A869" s="10"/>
+      <c r="A869" s="8"/>
       <c r="B869" s="18"/>
       <c r="C869" s="18"/>
       <c r="D869" s="18"/>
@@ -23690,7 +23734,7 @@
       <c r="V869" s="20"/>
     </row>
     <row r="870" ht="19.5" customHeight="1">
-      <c r="A870" s="10"/>
+      <c r="A870" s="8"/>
       <c r="B870" s="18"/>
       <c r="C870" s="18"/>
       <c r="D870" s="18"/>
@@ -23714,7 +23758,7 @@
       <c r="V870" s="20"/>
     </row>
     <row r="871" ht="19.5" customHeight="1">
-      <c r="A871" s="10"/>
+      <c r="A871" s="8"/>
       <c r="B871" s="18"/>
       <c r="C871" s="18"/>
       <c r="D871" s="18"/>
@@ -23738,7 +23782,7 @@
       <c r="V871" s="20"/>
     </row>
     <row r="872" ht="19.5" customHeight="1">
-      <c r="A872" s="10"/>
+      <c r="A872" s="8"/>
       <c r="B872" s="18"/>
       <c r="C872" s="18"/>
       <c r="D872" s="18"/>
@@ -23762,7 +23806,7 @@
       <c r="V872" s="20"/>
     </row>
     <row r="873" ht="19.5" customHeight="1">
-      <c r="A873" s="10"/>
+      <c r="A873" s="8"/>
       <c r="B873" s="18"/>
       <c r="C873" s="18"/>
       <c r="D873" s="18"/>
@@ -23786,7 +23830,7 @@
       <c r="V873" s="20"/>
     </row>
     <row r="874" ht="19.5" customHeight="1">
-      <c r="A874" s="10"/>
+      <c r="A874" s="8"/>
       <c r="B874" s="18"/>
       <c r="C874" s="18"/>
       <c r="D874" s="18"/>
@@ -23810,7 +23854,7 @@
       <c r="V874" s="20"/>
     </row>
     <row r="875" ht="19.5" customHeight="1">
-      <c r="A875" s="10"/>
+      <c r="A875" s="8"/>
       <c r="B875" s="18"/>
       <c r="C875" s="18"/>
       <c r="D875" s="18"/>
@@ -23834,7 +23878,7 @@
       <c r="V875" s="20"/>
     </row>
     <row r="876" ht="19.5" customHeight="1">
-      <c r="A876" s="10"/>
+      <c r="A876" s="8"/>
       <c r="B876" s="18"/>
       <c r="C876" s="18"/>
       <c r="D876" s="18"/>
@@ -23858,7 +23902,7 @@
       <c r="V876" s="20"/>
     </row>
     <row r="877" ht="19.5" customHeight="1">
-      <c r="A877" s="10"/>
+      <c r="A877" s="8"/>
       <c r="B877" s="18"/>
       <c r="C877" s="18"/>
       <c r="D877" s="18"/>
@@ -23882,7 +23926,7 @@
       <c r="V877" s="20"/>
     </row>
     <row r="878" ht="19.5" customHeight="1">
-      <c r="A878" s="10"/>
+      <c r="A878" s="8"/>
       <c r="B878" s="18"/>
       <c r="C878" s="18"/>
       <c r="D878" s="18"/>
@@ -23906,7 +23950,7 @@
       <c r="V878" s="20"/>
     </row>
     <row r="879" ht="19.5" customHeight="1">
-      <c r="A879" s="10"/>
+      <c r="A879" s="8"/>
       <c r="B879" s="18"/>
       <c r="C879" s="18"/>
       <c r="D879" s="18"/>
@@ -23930,7 +23974,7 @@
       <c r="V879" s="20"/>
     </row>
     <row r="880" ht="19.5" customHeight="1">
-      <c r="A880" s="10"/>
+      <c r="A880" s="8"/>
       <c r="B880" s="18"/>
       <c r="C880" s="18"/>
       <c r="D880" s="18"/>
@@ -23954,7 +23998,7 @@
       <c r="V880" s="20"/>
     </row>
     <row r="881" ht="19.5" customHeight="1">
-      <c r="A881" s="10"/>
+      <c r="A881" s="8"/>
       <c r="B881" s="18"/>
       <c r="C881" s="18"/>
       <c r="D881" s="18"/>
@@ -23978,7 +24022,7 @@
       <c r="V881" s="20"/>
     </row>
     <row r="882" ht="19.5" customHeight="1">
-      <c r="A882" s="10"/>
+      <c r="A882" s="8"/>
       <c r="B882" s="18"/>
       <c r="C882" s="18"/>
       <c r="D882" s="18"/>
@@ -24002,7 +24046,7 @@
       <c r="V882" s="20"/>
     </row>
     <row r="883" ht="19.5" customHeight="1">
-      <c r="A883" s="10"/>
+      <c r="A883" s="8"/>
       <c r="B883" s="18"/>
       <c r="C883" s="18"/>
       <c r="D883" s="18"/>
@@ -24026,7 +24070,7 @@
       <c r="V883" s="20"/>
     </row>
     <row r="884" ht="19.5" customHeight="1">
-      <c r="A884" s="10"/>
+      <c r="A884" s="8"/>
       <c r="B884" s="18"/>
       <c r="C884" s="18"/>
       <c r="D884" s="18"/>
@@ -24050,7 +24094,7 @@
       <c r="V884" s="20"/>
     </row>
     <row r="885" ht="19.5" customHeight="1">
-      <c r="A885" s="10"/>
+      <c r="A885" s="8"/>
       <c r="B885" s="18"/>
       <c r="C885" s="18"/>
       <c r="D885" s="18"/>
@@ -24074,7 +24118,7 @@
       <c r="V885" s="20"/>
     </row>
     <row r="886" ht="19.5" customHeight="1">
-      <c r="A886" s="10"/>
+      <c r="A886" s="8"/>
       <c r="B886" s="18"/>
       <c r="C886" s="18"/>
       <c r="D886" s="18"/>
@@ -24098,7 +24142,7 @@
       <c r="V886" s="20"/>
     </row>
     <row r="887" ht="19.5" customHeight="1">
-      <c r="A887" s="10"/>
+      <c r="A887" s="8"/>
       <c r="B887" s="18"/>
       <c r="C887" s="18"/>
       <c r="D887" s="18"/>
@@ -24122,7 +24166,7 @@
       <c r="V887" s="20"/>
     </row>
     <row r="888" ht="19.5" customHeight="1">
-      <c r="A888" s="10"/>
+      <c r="A888" s="8"/>
       <c r="B888" s="18"/>
       <c r="C888" s="18"/>
       <c r="D888" s="18"/>
@@ -24146,7 +24190,7 @@
       <c r="V888" s="20"/>
     </row>
     <row r="889" ht="19.5" customHeight="1">
-      <c r="A889" s="10"/>
+      <c r="A889" s="8"/>
       <c r="B889" s="18"/>
       <c r="C889" s="18"/>
       <c r="D889" s="18"/>
@@ -24170,7 +24214,7 @@
       <c r="V889" s="20"/>
     </row>
     <row r="890" ht="19.5" customHeight="1">
-      <c r="A890" s="10"/>
+      <c r="A890" s="8"/>
       <c r="B890" s="18"/>
       <c r="C890" s="18"/>
       <c r="D890" s="18"/>
@@ -24194,7 +24238,7 @@
       <c r="V890" s="20"/>
     </row>
     <row r="891" ht="19.5" customHeight="1">
-      <c r="A891" s="10"/>
+      <c r="A891" s="8"/>
       <c r="B891" s="18"/>
       <c r="C891" s="18"/>
       <c r="D891" s="18"/>
@@ -24218,7 +24262,7 @@
       <c r="V891" s="20"/>
     </row>
     <row r="892" ht="19.5" customHeight="1">
-      <c r="A892" s="10"/>
+      <c r="A892" s="8"/>
       <c r="B892" s="18"/>
       <c r="C892" s="18"/>
       <c r="D892" s="18"/>
@@ -24242,7 +24286,7 @@
       <c r="V892" s="20"/>
     </row>
     <row r="893" ht="19.5" customHeight="1">
-      <c r="A893" s="10"/>
+      <c r="A893" s="8"/>
       <c r="B893" s="18"/>
       <c r="C893" s="18"/>
       <c r="D893" s="18"/>
@@ -24266,7 +24310,7 @@
       <c r="V893" s="20"/>
     </row>
     <row r="894" ht="19.5" customHeight="1">
-      <c r="A894" s="10"/>
+      <c r="A894" s="8"/>
       <c r="B894" s="18"/>
       <c r="C894" s="18"/>
       <c r="D894" s="18"/>
@@ -24290,7 +24334,7 @@
       <c r="V894" s="20"/>
     </row>
     <row r="895" ht="19.5" customHeight="1">
-      <c r="A895" s="10"/>
+      <c r="A895" s="8"/>
       <c r="B895" s="18"/>
       <c r="C895" s="18"/>
       <c r="D895" s="18"/>
@@ -24314,7 +24358,7 @@
       <c r="V895" s="20"/>
     </row>
     <row r="896" ht="19.5" customHeight="1">
-      <c r="A896" s="10"/>
+      <c r="A896" s="8"/>
       <c r="B896" s="18"/>
       <c r="C896" s="18"/>
       <c r="D896" s="18"/>
@@ -24338,7 +24382,7 @@
       <c r="V896" s="20"/>
     </row>
     <row r="897" ht="19.5" customHeight="1">
-      <c r="A897" s="10"/>
+      <c r="A897" s="8"/>
       <c r="B897" s="18"/>
       <c r="C897" s="18"/>
       <c r="D897" s="18"/>
@@ -24362,7 +24406,7 @@
       <c r="V897" s="20"/>
     </row>
     <row r="898" ht="19.5" customHeight="1">
-      <c r="A898" s="10"/>
+      <c r="A898" s="8"/>
       <c r="B898" s="18"/>
       <c r="C898" s="18"/>
       <c r="D898" s="18"/>
@@ -24386,7 +24430,7 @@
       <c r="V898" s="20"/>
     </row>
     <row r="899" ht="19.5" customHeight="1">
-      <c r="A899" s="10"/>
+      <c r="A899" s="8"/>
       <c r="B899" s="18"/>
       <c r="C899" s="18"/>
       <c r="D899" s="18"/>
@@ -24410,7 +24454,7 @@
       <c r="V899" s="20"/>
     </row>
     <row r="900" ht="19.5" customHeight="1">
-      <c r="A900" s="10"/>
+      <c r="A900" s="8"/>
       <c r="B900" s="18"/>
       <c r="C900" s="18"/>
       <c r="D900" s="18"/>
@@ -24434,7 +24478,7 @@
       <c r="V900" s="20"/>
     </row>
     <row r="901" ht="19.5" customHeight="1">
-      <c r="A901" s="10"/>
+      <c r="A901" s="8"/>
       <c r="B901" s="18"/>
       <c r="C901" s="18"/>
       <c r="D901" s="18"/>
@@ -24458,7 +24502,7 @@
       <c r="V901" s="20"/>
     </row>
     <row r="902" ht="19.5" customHeight="1">
-      <c r="A902" s="10"/>
+      <c r="A902" s="8"/>
       <c r="B902" s="18"/>
       <c r="C902" s="18"/>
       <c r="D902" s="18"/>
@@ -24482,7 +24526,7 @@
       <c r="V902" s="20"/>
     </row>
     <row r="903" ht="19.5" customHeight="1">
-      <c r="A903" s="10"/>
+      <c r="A903" s="8"/>
       <c r="B903" s="18"/>
       <c r="C903" s="18"/>
       <c r="D903" s="18"/>
@@ -24506,7 +24550,7 @@
       <c r="V903" s="20"/>
     </row>
     <row r="904" ht="19.5" customHeight="1">
-      <c r="A904" s="10"/>
+      <c r="A904" s="8"/>
       <c r="B904" s="18"/>
       <c r="C904" s="18"/>
       <c r="D904" s="18"/>
@@ -24530,7 +24574,7 @@
       <c r="V904" s="20"/>
     </row>
     <row r="905" ht="19.5" customHeight="1">
-      <c r="A905" s="10"/>
+      <c r="A905" s="8"/>
       <c r="B905" s="18"/>
       <c r="C905" s="18"/>
       <c r="D905" s="18"/>
@@ -24554,7 +24598,7 @@
       <c r="V905" s="20"/>
     </row>
     <row r="906" ht="19.5" customHeight="1">
-      <c r="A906" s="10"/>
+      <c r="A906" s="8"/>
       <c r="B906" s="18"/>
       <c r="C906" s="18"/>
       <c r="D906" s="18"/>
@@ -24578,7 +24622,7 @@
       <c r="V906" s="20"/>
     </row>
     <row r="907" ht="19.5" customHeight="1">
-      <c r="A907" s="10"/>
+      <c r="A907" s="8"/>
       <c r="B907" s="18"/>
       <c r="C907" s="18"/>
       <c r="D907" s="18"/>
@@ -24602,7 +24646,7 @@
       <c r="V907" s="20"/>
     </row>
     <row r="908" ht="19.5" customHeight="1">
-      <c r="A908" s="10"/>
+      <c r="A908" s="8"/>
       <c r="B908" s="18"/>
       <c r="C908" s="18"/>
       <c r="D908" s="18"/>
@@ -24626,7 +24670,7 @@
       <c r="V908" s="20"/>
     </row>
     <row r="909" ht="19.5" customHeight="1">
-      <c r="A909" s="10"/>
+      <c r="A909" s="8"/>
       <c r="B909" s="18"/>
       <c r="C909" s="18"/>
       <c r="D909" s="18"/>
@@ -24650,7 +24694,7 @@
       <c r="V909" s="20"/>
     </row>
     <row r="910" ht="19.5" customHeight="1">
-      <c r="A910" s="10"/>
+      <c r="A910" s="8"/>
       <c r="B910" s="18"/>
       <c r="C910" s="18"/>
       <c r="D910" s="18"/>
@@ -24674,7 +24718,7 @@
       <c r="V910" s="20"/>
     </row>
     <row r="911" ht="19.5" customHeight="1">
-      <c r="A911" s="10"/>
+      <c r="A911" s="8"/>
       <c r="B911" s="18"/>
       <c r="C911" s="18"/>
       <c r="D911" s="18"/>
@@ -24698,7 +24742,7 @@
       <c r="V911" s="20"/>
     </row>
     <row r="912" ht="19.5" customHeight="1">
-      <c r="A912" s="10"/>
+      <c r="A912" s="8"/>
       <c r="B912" s="18"/>
       <c r="C912" s="18"/>
       <c r="D912" s="18"/>
@@ -24722,7 +24766,7 @@
       <c r="V912" s="20"/>
     </row>
     <row r="913" ht="19.5" customHeight="1">
-      <c r="A913" s="10"/>
+      <c r="A913" s="8"/>
       <c r="B913" s="18"/>
       <c r="C913" s="18"/>
       <c r="D913" s="18"/>
@@ -24746,7 +24790,7 @@
       <c r="V913" s="20"/>
     </row>
     <row r="914" ht="19.5" customHeight="1">
-      <c r="A914" s="10"/>
+      <c r="A914" s="8"/>
       <c r="B914" s="18"/>
       <c r="C914" s="18"/>
       <c r="D914" s="18"/>
@@ -24770,7 +24814,7 @@
       <c r="V914" s="20"/>
     </row>
     <row r="915" ht="19.5" customHeight="1">
-      <c r="A915" s="10"/>
+      <c r="A915" s="8"/>
       <c r="B915" s="18"/>
       <c r="C915" s="18"/>
       <c r="D915" s="18"/>
@@ -24794,7 +24838,7 @@
       <c r="V915" s="20"/>
     </row>
     <row r="916" ht="19.5" customHeight="1">
-      <c r="A916" s="10"/>
+      <c r="A916" s="8"/>
       <c r="B916" s="18"/>
       <c r="C916" s="18"/>
       <c r="D916" s="18"/>
@@ -24818,7 +24862,7 @@
       <c r="V916" s="20"/>
     </row>
     <row r="917" ht="19.5" customHeight="1">
-      <c r="A917" s="10"/>
+      <c r="A917" s="8"/>
       <c r="B917" s="18"/>
       <c r="C917" s="18"/>
       <c r="D917" s="18"/>
@@ -24842,7 +24886,7 @@
       <c r="V917" s="20"/>
     </row>
     <row r="918" ht="19.5" customHeight="1">
-      <c r="A918" s="10"/>
+      <c r="A918" s="8"/>
       <c r="B918" s="18"/>
       <c r="C918" s="18"/>
       <c r="D918" s="18"/>
@@ -24866,7 +24910,7 @@
       <c r="V918" s="20"/>
     </row>
     <row r="919" ht="19.5" customHeight="1">
-      <c r="A919" s="10"/>
+      <c r="A919" s="8"/>
       <c r="B919" s="18"/>
       <c r="C919" s="18"/>
       <c r="D919" s="18"/>
@@ -24890,7 +24934,7 @@
       <c r="V919" s="20"/>
     </row>
     <row r="920" ht="19.5" customHeight="1">
-      <c r="A920" s="10"/>
+      <c r="A920" s="8"/>
       <c r="B920" s="18"/>
       <c r="C920" s="18"/>
       <c r="D920" s="18"/>
@@ -24914,7 +24958,7 @@
       <c r="V920" s="20"/>
     </row>
     <row r="921" ht="19.5" customHeight="1">
-      <c r="A921" s="10"/>
+      <c r="A921" s="8"/>
       <c r="B921" s="18"/>
       <c r="C921" s="18"/>
       <c r="D921" s="18"/>
@@ -24938,7 +24982,7 @@
       <c r="V921" s="20"/>
     </row>
     <row r="922" ht="19.5" customHeight="1">
-      <c r="A922" s="10"/>
+      <c r="A922" s="8"/>
       <c r="B922" s="18"/>
       <c r="C922" s="18"/>
       <c r="D922" s="18"/>
@@ -24962,7 +25006,7 @@
       <c r="V922" s="20"/>
     </row>
     <row r="923" ht="19.5" customHeight="1">
-      <c r="A923" s="10"/>
+      <c r="A923" s="8"/>
       <c r="B923" s="18"/>
       <c r="C923" s="18"/>
       <c r="D923" s="18"/>
@@ -24986,7 +25030,7 @@
       <c r="V923" s="20"/>
     </row>
     <row r="924" ht="19.5" customHeight="1">
-      <c r="A924" s="10"/>
+      <c r="A924" s="8"/>
       <c r="B924" s="18"/>
       <c r="C924" s="18"/>
       <c r="D924" s="18"/>
@@ -25010,7 +25054,7 @@
       <c r="V924" s="20"/>
     </row>
     <row r="925" ht="19.5" customHeight="1">
-      <c r="A925" s="10"/>
+      <c r="A925" s="8"/>
       <c r="B925" s="18"/>
       <c r="C925" s="18"/>
       <c r="D925" s="18"/>
@@ -25034,7 +25078,7 @@
       <c r="V925" s="20"/>
     </row>
     <row r="926" ht="19.5" customHeight="1">
-      <c r="A926" s="10"/>
+      <c r="A926" s="8"/>
       <c r="B926" s="18"/>
       <c r="C926" s="18"/>
       <c r="D926" s="18"/>
@@ -25058,7 +25102,7 @@
       <c r="V926" s="20"/>
     </row>
     <row r="927" ht="19.5" customHeight="1">
-      <c r="A927" s="10"/>
+      <c r="A927" s="8"/>
       <c r="B927" s="18"/>
       <c r="C927" s="18"/>
       <c r="D927" s="18"/>
@@ -25082,7 +25126,7 @@
       <c r="V927" s="20"/>
     </row>
     <row r="928" ht="19.5" customHeight="1">
-      <c r="A928" s="10"/>
+      <c r="A928" s="8"/>
       <c r="B928" s="18"/>
       <c r="C928" s="18"/>
       <c r="D928" s="18"/>
@@ -25106,7 +25150,7 @@
       <c r="V928" s="20"/>
     </row>
     <row r="929" ht="19.5" customHeight="1">
-      <c r="A929" s="10"/>
+      <c r="A929" s="8"/>
       <c r="B929" s="18"/>
       <c r="C929" s="18"/>
       <c r="D929" s="18"/>
@@ -25130,7 +25174,7 @@
       <c r="V929" s="20"/>
     </row>
     <row r="930" ht="19.5" customHeight="1">
-      <c r="A930" s="10"/>
+      <c r="A930" s="8"/>
       <c r="B930" s="18"/>
       <c r="C930" s="18"/>
       <c r="D930" s="18"/>
@@ -25154,7 +25198,7 @@
       <c r="V930" s="20"/>
     </row>
     <row r="931" ht="19.5" customHeight="1">
-      <c r="A931" s="10"/>
+      <c r="A931" s="8"/>
       <c r="B931" s="18"/>
       <c r="C931" s="18"/>
       <c r="D931" s="18"/>
@@ -25178,7 +25222,7 @@
       <c r="V931" s="20"/>
     </row>
     <row r="932" ht="19.5" customHeight="1">
-      <c r="A932" s="10"/>
+      <c r="A932" s="8"/>
       <c r="B932" s="18"/>
       <c r="C932" s="18"/>
       <c r="D932" s="18"/>
@@ -25202,7 +25246,7 @@
       <c r="V932" s="20"/>
     </row>
     <row r="933" ht="19.5" customHeight="1">
-      <c r="A933" s="10"/>
+      <c r="A933" s="8"/>
       <c r="B933" s="18"/>
       <c r="C933" s="18"/>
       <c r="D933" s="18"/>
@@ -25226,7 +25270,7 @@
       <c r="V933" s="20"/>
     </row>
     <row r="934" ht="19.5" customHeight="1">
-      <c r="A934" s="10"/>
+      <c r="A934" s="8"/>
       <c r="B934" s="18"/>
       <c r="C934" s="18"/>
       <c r="D934" s="18"/>
@@ -25250,7 +25294,7 @@
       <c r="V934" s="20"/>
     </row>
     <row r="935" ht="19.5" customHeight="1">
-      <c r="A935" s="10"/>
+      <c r="A935" s="8"/>
       <c r="B935" s="18"/>
       <c r="C935" s="18"/>
       <c r="D935" s="18"/>
@@ -25274,7 +25318,7 @@
       <c r="V935" s="20"/>
     </row>
     <row r="936" ht="19.5" customHeight="1">
-      <c r="A936" s="10"/>
+      <c r="A936" s="8"/>
       <c r="B936" s="18"/>
       <c r="C936" s="18"/>
       <c r="D936" s="18"/>
@@ -25298,7 +25342,7 @@
       <c r="V936" s="20"/>
     </row>
     <row r="937" ht="19.5" customHeight="1">
-      <c r="A937" s="10"/>
+      <c r="A937" s="8"/>
       <c r="B937" s="18"/>
       <c r="C937" s="18"/>
       <c r="D937" s="18"/>
@@ -25322,7 +25366,7 @@
       <c r="V937" s="20"/>
     </row>
     <row r="938" ht="19.5" customHeight="1">
-      <c r="A938" s="10"/>
+      <c r="A938" s="8"/>
       <c r="B938" s="18"/>
       <c r="C938" s="18"/>
       <c r="D938" s="18"/>
@@ -25346,7 +25390,7 @@
       <c r="V938" s="20"/>
     </row>
     <row r="939" ht="19.5" customHeight="1">
-      <c r="A939" s="10"/>
+      <c r="A939" s="8"/>
       <c r="B939" s="18"/>
       <c r="C939" s="18"/>
       <c r="D939" s="18"/>
@@ -25370,7 +25414,7 @@
       <c r="V939" s="20"/>
     </row>
     <row r="940" ht="19.5" customHeight="1">
-      <c r="A940" s="10"/>
+      <c r="A940" s="8"/>
       <c r="B940" s="18"/>
       <c r="C940" s="18"/>
       <c r="D940" s="18"/>
@@ -25394,7 +25438,7 @@
       <c r="V940" s="20"/>
     </row>
     <row r="941" ht="19.5" customHeight="1">
-      <c r="A941" s="10"/>
+      <c r="A941" s="8"/>
       <c r="B941" s="18"/>
       <c r="C941" s="18"/>
       <c r="D941" s="18"/>
@@ -25418,7 +25462,7 @@
       <c r="V941" s="20"/>
     </row>
     <row r="942" ht="19.5" customHeight="1">
-      <c r="A942" s="10"/>
+      <c r="A942" s="8"/>
       <c r="B942" s="18"/>
       <c r="C942" s="18"/>
       <c r="D942" s="18"/>
@@ -25442,7 +25486,7 @@
       <c r="V942" s="20"/>
     </row>
     <row r="943" ht="19.5" customHeight="1">
-      <c r="A943" s="10"/>
+      <c r="A943" s="8"/>
       <c r="B943" s="18"/>
       <c r="C943" s="18"/>
       <c r="D943" s="18"/>
@@ -25466,7 +25510,7 @@
       <c r="V943" s="20"/>
     </row>
     <row r="944" ht="19.5" customHeight="1">
-      <c r="A944" s="10"/>
+      <c r="A944" s="8"/>
       <c r="B944" s="18"/>
       <c r="C944" s="18"/>
       <c r="D944" s="18"/>
@@ -25490,7 +25534,7 @@
       <c r="V944" s="20"/>
     </row>
     <row r="945" ht="19.5" customHeight="1">
-      <c r="A945" s="10"/>
+      <c r="A945" s="8"/>
       <c r="B945" s="18"/>
       <c r="C945" s="18"/>
       <c r="D945" s="18"/>
@@ -25514,7 +25558,7 @@
       <c r="V945" s="20"/>
     </row>
     <row r="946" ht="19.5" customHeight="1">
-      <c r="A946" s="10"/>
+      <c r="A946" s="8"/>
       <c r="B946" s="18"/>
       <c r="C946" s="18"/>
       <c r="D946" s="18"/>
@@ -25538,7 +25582,7 @@
       <c r="V946" s="20"/>
     </row>
     <row r="947" ht="19.5" customHeight="1">
-      <c r="A947" s="10"/>
+      <c r="A947" s="8"/>
       <c r="B947" s="18"/>
       <c r="C947" s="18"/>
       <c r="D947" s="18"/>
@@ -25562,7 +25606,7 @@
       <c r="V947" s="20"/>
     </row>
     <row r="948" ht="19.5" customHeight="1">
-      <c r="A948" s="10"/>
+      <c r="A948" s="8"/>
       <c r="B948" s="18"/>
       <c r="C948" s="18"/>
       <c r="D948" s="18"/>
@@ -25586,7 +25630,7 @@
       <c r="V948" s="20"/>
     </row>
     <row r="949" ht="19.5" customHeight="1">
-      <c r="A949" s="10"/>
+      <c r="A949" s="8"/>
       <c r="B949" s="18"/>
       <c r="C949" s="18"/>
       <c r="D949" s="18"/>
@@ -25610,7 +25654,7 @@
       <c r="V949" s="20"/>
     </row>
     <row r="950" ht="19.5" customHeight="1">
-      <c r="A950" s="10"/>
+      <c r="A950" s="8"/>
       <c r="B950" s="18"/>
       <c r="C950" s="18"/>
       <c r="D950" s="18"/>
@@ -25634,7 +25678,7 @@
       <c r="V950" s="20"/>
     </row>
     <row r="951" ht="19.5" customHeight="1">
-      <c r="A951" s="10"/>
+      <c r="A951" s="8"/>
       <c r="B951" s="18"/>
       <c r="C951" s="18"/>
       <c r="D951" s="18"/>
@@ -25658,7 +25702,7 @@
       <c r="V951" s="20"/>
     </row>
     <row r="952" ht="19.5" customHeight="1">
-      <c r="A952" s="10"/>
+      <c r="A952" s="8"/>
       <c r="B952" s="18"/>
       <c r="C952" s="18"/>
       <c r="D952" s="18"/>
@@ -25682,7 +25726,7 @@
       <c r="V952" s="20"/>
     </row>
     <row r="953" ht="19.5" customHeight="1">
-      <c r="A953" s="10"/>
+      <c r="A953" s="8"/>
       <c r="B953" s="18"/>
       <c r="C953" s="18"/>
       <c r="D953" s="18"/>
@@ -25706,7 +25750,7 @@
       <c r="V953" s="20"/>
     </row>
     <row r="954" ht="19.5" customHeight="1">
-      <c r="A954" s="10"/>
+      <c r="A954" s="8"/>
       <c r="B954" s="18"/>
       <c r="C954" s="18"/>
       <c r="D954" s="18"/>
@@ -25730,7 +25774,7 @@
       <c r="V954" s="20"/>
     </row>
     <row r="955" ht="19.5" customHeight="1">
-      <c r="A955" s="10"/>
+      <c r="A955" s="8"/>
       <c r="B955" s="18"/>
       <c r="C955" s="18"/>
       <c r="D955" s="18"/>
@@ -25754,7 +25798,7 @@
       <c r="V955" s="20"/>
     </row>
     <row r="956" ht="19.5" customHeight="1">
-      <c r="A956" s="10"/>
+      <c r="A956" s="8"/>
       <c r="B956" s="18"/>
       <c r="C956" s="18"/>
       <c r="D956" s="18"/>
@@ -25778,7 +25822,7 @@
       <c r="V956" s="20"/>
     </row>
     <row r="957" ht="19.5" customHeight="1">
-      <c r="A957" s="10"/>
+      <c r="A957" s="8"/>
       <c r="B957" s="18"/>
       <c r="C957" s="18"/>
       <c r="D957" s="18"/>
@@ -25802,7 +25846,7 @@
       <c r="V957" s="20"/>
     </row>
     <row r="958" ht="19.5" customHeight="1">
-      <c r="A958" s="10"/>
+      <c r="A958" s="8"/>
       <c r="B958" s="18"/>
       <c r="C958" s="18"/>
       <c r="D958" s="18"/>
@@ -25826,7 +25870,7 @@
       <c r="V958" s="20"/>
     </row>
     <row r="959" ht="19.5" customHeight="1">
-      <c r="A959" s="10"/>
+      <c r="A959" s="8"/>
       <c r="B959" s="18"/>
       <c r="C959" s="18"/>
       <c r="D959" s="18"/>
@@ -25850,7 +25894,7 @@
       <c r="V959" s="20"/>
     </row>
     <row r="960" ht="19.5" customHeight="1">
-      <c r="A960" s="10"/>
+      <c r="A960" s="8"/>
       <c r="B960" s="18"/>
       <c r="C960" s="18"/>
       <c r="D960" s="18"/>
@@ -25874,7 +25918,7 @@
       <c r="V960" s="20"/>
     </row>
     <row r="961" ht="19.5" customHeight="1">
-      <c r="A961" s="10"/>
+      <c r="A961" s="8"/>
       <c r="B961" s="18"/>
       <c r="C961" s="18"/>
       <c r="D961" s="18"/>
@@ -25898,7 +25942,7 @@
       <c r="V961" s="20"/>
     </row>
     <row r="962" ht="19.5" customHeight="1">
-      <c r="A962" s="10"/>
+      <c r="A962" s="8"/>
       <c r="B962" s="18"/>
       <c r="C962" s="18"/>
       <c r="D962" s="18"/>
@@ -25922,7 +25966,7 @@
       <c r="V962" s="20"/>
     </row>
     <row r="963" ht="19.5" customHeight="1">
-      <c r="A963" s="10"/>
+      <c r="A963" s="8"/>
       <c r="B963" s="18"/>
       <c r="C963" s="18"/>
       <c r="D963" s="18"/>
@@ -25946,7 +25990,7 @@
       <c r="V963" s="20"/>
     </row>
     <row r="964" ht="19.5" customHeight="1">
-      <c r="A964" s="10"/>
+      <c r="A964" s="8"/>
       <c r="B964" s="18"/>
       <c r="C964" s="18"/>
       <c r="D964" s="18"/>
@@ -25970,7 +26014,7 @@
       <c r="V964" s="20"/>
     </row>
     <row r="965" ht="19.5" customHeight="1">
-      <c r="A965" s="10"/>
+      <c r="A965" s="8"/>
       <c r="B965" s="18"/>
       <c r="C965" s="18"/>
       <c r="D965" s="18"/>
@@ -25994,7 +26038,7 @@
       <c r="V965" s="20"/>
     </row>
     <row r="966" ht="19.5" customHeight="1">
-      <c r="A966" s="10"/>
+      <c r="A966" s="8"/>
       <c r="B966" s="18"/>
       <c r="C966" s="18"/>
       <c r="D966" s="18"/>
@@ -26018,7 +26062,7 @@
       <c r="V966" s="20"/>
     </row>
     <row r="967" ht="19.5" customHeight="1">
-      <c r="A967" s="10"/>
+      <c r="A967" s="8"/>
       <c r="B967" s="18"/>
       <c r="C967" s="18"/>
       <c r="D967" s="18"/>
@@ -26042,7 +26086,7 @@
       <c r="V967" s="20"/>
     </row>
     <row r="968" ht="19.5" customHeight="1">
-      <c r="A968" s="10"/>
+      <c r="A968" s="8"/>
       <c r="B968" s="18"/>
       <c r="C968" s="18"/>
       <c r="D968" s="18"/>
@@ -26066,7 +26110,7 @@
       <c r="V968" s="20"/>
     </row>
     <row r="969" ht="19.5" customHeight="1">
-      <c r="A969" s="10"/>
+      <c r="A969" s="8"/>
       <c r="B969" s="18"/>
       <c r="C969" s="18"/>
       <c r="D969" s="18"/>
@@ -26090,7 +26134,7 @@
       <c r="V969" s="20"/>
     </row>
     <row r="970" ht="19.5" customHeight="1">
-      <c r="A970" s="10"/>
+      <c r="A970" s="8"/>
       <c r="B970" s="18"/>
       <c r="C970" s="18"/>
       <c r="D970" s="18"/>
@@ -26114,7 +26158,7 @@
       <c r="V970" s="20"/>
     </row>
     <row r="971" ht="19.5" customHeight="1">
-      <c r="A971" s="10"/>
+      <c r="A971" s="8"/>
       <c r="B971" s="18"/>
       <c r="C971" s="18"/>
       <c r="D971" s="18"/>
@@ -26138,7 +26182,7 @@
       <c r="V971" s="20"/>
     </row>
     <row r="972" ht="19.5" customHeight="1">
-      <c r="A972" s="10"/>
+      <c r="A972" s="8"/>
       <c r="B972" s="18"/>
       <c r="C972" s="18"/>
       <c r="D972" s="18"/>
@@ -26162,7 +26206,7 @@
       <c r="V972" s="20"/>
     </row>
     <row r="973" ht="19.5" customHeight="1">
-      <c r="A973" s="10"/>
+      <c r="A973" s="8"/>
       <c r="B973" s="18"/>
       <c r="C973" s="18"/>
       <c r="D973" s="18"/>
@@ -26186,7 +26230,7 @@
       <c r="V973" s="20"/>
     </row>
     <row r="974" ht="19.5" customHeight="1">
-      <c r="A974" s="10"/>
+      <c r="A974" s="8"/>
       <c r="B974" s="18"/>
       <c r="C974" s="18"/>
       <c r="D974" s="18"/>
@@ -26210,7 +26254,7 @@
       <c r="V974" s="20"/>
     </row>
     <row r="975" ht="19.5" customHeight="1">
-      <c r="A975" s="10"/>
+      <c r="A975" s="8"/>
       <c r="B975" s="18"/>
       <c r="C975" s="18"/>
       <c r="D975" s="18"/>
@@ -26234,7 +26278,7 @@
       <c r="V975" s="20"/>
     </row>
     <row r="976" ht="19.5" customHeight="1">
-      <c r="A976" s="10"/>
+      <c r="A976" s="8"/>
       <c r="B976" s="18"/>
       <c r="C976" s="18"/>
       <c r="D976" s="18"/>
@@ -26258,7 +26302,7 @@
       <c r="V976" s="20"/>
     </row>
     <row r="977" ht="19.5" customHeight="1">
-      <c r="A977" s="10"/>
+      <c r="A977" s="8"/>
       <c r="B977" s="18"/>
       <c r="C977" s="18"/>
       <c r="D977" s="18"/>
@@ -26282,7 +26326,7 @@
       <c r="V977" s="20"/>
     </row>
     <row r="978" ht="19.5" customHeight="1">
-      <c r="A978" s="10"/>
+      <c r="A978" s="8"/>
       <c r="B978" s="18"/>
       <c r="C978" s="18"/>
       <c r="D978" s="18"/>
@@ -26306,7 +26350,7 @@
       <c r="V978" s="20"/>
     </row>
     <row r="979" ht="19.5" customHeight="1">
-      <c r="A979" s="10"/>
+      <c r="A979" s="8"/>
       <c r="B979" s="18"/>
       <c r="C979" s="18"/>
       <c r="D979" s="18"/>
@@ -26330,7 +26374,7 @@
       <c r="V979" s="20"/>
     </row>
     <row r="980" ht="19.5" customHeight="1">
-      <c r="A980" s="10"/>
+      <c r="A980" s="8"/>
       <c r="B980" s="18"/>
       <c r="C980" s="18"/>
       <c r="D980" s="18"/>
@@ -26354,7 +26398,7 @@
       <c r="V980" s="20"/>
     </row>
     <row r="981" ht="19.5" customHeight="1">
-      <c r="A981" s="10"/>
+      <c r="A981" s="8"/>
       <c r="B981" s="18"/>
       <c r="C981" s="18"/>
       <c r="D981" s="18"/>
@@ -26378,7 +26422,7 @@
       <c r="V981" s="20"/>
     </row>
     <row r="982" ht="19.5" customHeight="1">
-      <c r="A982" s="10"/>
+      <c r="A982" s="8"/>
       <c r="B982" s="18"/>
       <c r="C982" s="18"/>
       <c r="D982" s="18"/>
@@ -26402,7 +26446,7 @@
       <c r="V982" s="20"/>
     </row>
     <row r="983" ht="19.5" customHeight="1">
-      <c r="A983" s="10"/>
+      <c r="A983" s="8"/>
       <c r="B983" s="18"/>
       <c r="C983" s="18"/>
       <c r="D983" s="18"/>
@@ -26426,7 +26470,7 @@
       <c r="V983" s="20"/>
     </row>
     <row r="984" ht="19.5" customHeight="1">
-      <c r="A984" s="10"/>
+      <c r="A984" s="8"/>
       <c r="B984" s="18"/>
       <c r="C984" s="18"/>
       <c r="D984" s="18"/>
@@ -26450,7 +26494,7 @@
       <c r="V984" s="20"/>
     </row>
     <row r="985" ht="19.5" customHeight="1">
-      <c r="A985" s="10"/>
+      <c r="A985" s="8"/>
       <c r="B985" s="18"/>
       <c r="C985" s="18"/>
       <c r="D985" s="18"/>
@@ -26474,7 +26518,7 @@
       <c r="V985" s="20"/>
     </row>
     <row r="986" ht="19.5" customHeight="1">
-      <c r="A986" s="10"/>
+      <c r="A986" s="8"/>
       <c r="B986" s="18"/>
       <c r="C986" s="18"/>
       <c r="D986" s="18"/>
@@ -26498,7 +26542,7 @@
       <c r="V986" s="20"/>
     </row>
     <row r="987" ht="19.5" customHeight="1">
-      <c r="A987" s="10"/>
+      <c r="A987" s="8"/>
       <c r="B987" s="18"/>
       <c r="C987" s="18"/>
       <c r="D987" s="18"/>
@@ -26522,7 +26566,7 @@
       <c r="V987" s="20"/>
     </row>
     <row r="988" ht="19.5" customHeight="1">
-      <c r="A988" s="10"/>
+      <c r="A988" s="8"/>
       <c r="B988" s="18"/>
       <c r="C988" s="18"/>
       <c r="D988" s="18"/>
@@ -26546,7 +26590,7 @@
       <c r="V988" s="20"/>
     </row>
     <row r="989" ht="19.5" customHeight="1">
-      <c r="A989" s="10"/>
+      <c r="A989" s="8"/>
       <c r="B989" s="18"/>
       <c r="C989" s="18"/>
       <c r="D989" s="18"/>
@@ -26570,7 +26614,7 @@
       <c r="V989" s="20"/>
     </row>
     <row r="990" ht="19.5" customHeight="1">
-      <c r="A990" s="10"/>
+      <c r="A990" s="8"/>
       <c r="B990" s="18"/>
       <c r="C990" s="18"/>
       <c r="D990" s="18"/>
@@ -26594,7 +26638,7 @@
       <c r="V990" s="20"/>
     </row>
     <row r="991" ht="19.5" customHeight="1">
-      <c r="A991" s="10"/>
+      <c r="A991" s="8"/>
       <c r="B991" s="18"/>
       <c r="C991" s="18"/>
       <c r="D991" s="18"/>
@@ -26618,7 +26662,7 @@
       <c r="V991" s="20"/>
     </row>
     <row r="992" ht="19.5" customHeight="1">
-      <c r="A992" s="10"/>
+      <c r="A992" s="8"/>
       <c r="B992" s="18"/>
       <c r="C992" s="18"/>
       <c r="D992" s="18"/>
@@ -26642,7 +26686,7 @@
       <c r="V992" s="20"/>
     </row>
     <row r="993" ht="19.5" customHeight="1">
-      <c r="A993" s="10"/>
+      <c r="A993" s="8"/>
       <c r="B993" s="18"/>
       <c r="C993" s="18"/>
       <c r="D993" s="18"/>
@@ -26666,7 +26710,7 @@
       <c r="V993" s="20"/>
     </row>
     <row r="994" ht="19.5" customHeight="1">
-      <c r="A994" s="10"/>
+      <c r="A994" s="8"/>
       <c r="B994" s="18"/>
       <c r="C994" s="18"/>
       <c r="D994" s="18"/>
@@ -26690,7 +26734,7 @@
       <c r="V994" s="20"/>
     </row>
     <row r="995" ht="19.5" customHeight="1">
-      <c r="A995" s="10"/>
+      <c r="A995" s="8"/>
       <c r="B995" s="18"/>
       <c r="C995" s="18"/>
       <c r="D995" s="18"/>
@@ -26714,7 +26758,7 @@
       <c r="V995" s="20"/>
     </row>
     <row r="996" ht="19.5" customHeight="1">
-      <c r="A996" s="10"/>
+      <c r="A996" s="8"/>
       <c r="B996" s="18"/>
       <c r="C996" s="18"/>
       <c r="D996" s="18"/>
@@ -26738,7 +26782,7 @@
       <c r="V996" s="20"/>
     </row>
     <row r="997" ht="19.5" customHeight="1">
-      <c r="A997" s="10"/>
+      <c r="A997" s="8"/>
       <c r="B997" s="18"/>
       <c r="C997" s="18"/>
       <c r="D997" s="18"/>
@@ -26762,7 +26806,7 @@
       <c r="V997" s="20"/>
     </row>
     <row r="998" ht="19.5" customHeight="1">
-      <c r="A998" s="10"/>
+      <c r="A998" s="8"/>
       <c r="B998" s="18"/>
       <c r="C998" s="18"/>
       <c r="D998" s="18"/>
@@ -26786,7 +26830,7 @@
       <c r="V998" s="20"/>
     </row>
     <row r="999" ht="19.5" customHeight="1">
-      <c r="A999" s="10"/>
+      <c r="A999" s="8"/>
       <c r="B999" s="18"/>
       <c r="C999" s="18"/>
       <c r="D999" s="18"/>
@@ -26853,32 +26897,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
+      <c r="A1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="5">
         <v>6.75</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="A3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="5">
         <v>0.86</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
-        <v>10</v>
+      <c r="A7" s="10" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -27880,105 +27924,105 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="5">
         <v>3200.0</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="5">
         <v>2.01</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="9">
         <f t="shared" ref="D2:D15" si="1">B2*C2</f>
         <v>6432</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="A3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="5">
         <v>1900.0</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="5">
         <v>2.63</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="9">
         <f t="shared" si="1"/>
         <v>4997</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="5">
         <v>1100.0</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="5">
         <v>5.14</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="9">
         <f t="shared" si="1"/>
         <v>5654</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="5">
         <v>800.0</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="5">
         <v>4.7</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="9">
         <f t="shared" si="1"/>
         <v>3760</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="5">
         <v>3400.0</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="5">
         <v>1.0</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="9">
         <f t="shared" si="1"/>
         <v>3400</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="5">
         <v>1200.0</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="5">
         <v>1.38</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="9">
         <f t="shared" si="1"/>
         <v>1656</v>
       </c>
@@ -28058,13 +28102,13 @@
       <c r="Z9" s="15"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="5">
         <v>200.0</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="5">
         <v>2.65</v>
       </c>
       <c r="D10" s="17">
@@ -28073,82 +28117,82 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="5">
         <v>7200.0</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="5">
         <v>2.0</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="9">
         <f t="shared" si="1"/>
         <v>14400</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="5">
         <v>6300.0</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="5">
         <v>0.7</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="9">
         <f t="shared" si="1"/>
         <v>4410</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="5">
         <v>1600.0</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="5">
         <v>4.4</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="9">
         <f t="shared" si="1"/>
         <v>7040</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="5">
         <v>2400.0</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="5">
         <v>0.8</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="9">
         <f t="shared" si="1"/>
         <v>1920</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="5">
         <v>4400.0</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="5">
         <v>0.6</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="9">
         <f t="shared" si="1"/>
         <v>2640</v>
       </c>
     </row>
     <row r="16">
-      <c r="D16" s="6">
+      <c r="D16" s="9">
         <f>SUM(D2:D15)</f>
         <v>57619</v>
       </c>
